--- a/database/event/3985/event_3985_evp_summary.xlsx
+++ b/database/event/3985/event_3985_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.0244</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7161</v>
+        <v>2.6503</v>
       </c>
       <c r="E2" t="n">
         <v>7.7665</v>
@@ -548,7 +548,7 @@
         <v>1.9436</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5909</v>
+        <v>2.5268</v>
       </c>
       <c r="E3" t="n">
         <v>7.4565</v>
@@ -594,7 +594,7 @@
         <v>1.1519</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3639</v>
+        <v>1.3167</v>
       </c>
       <c r="E4" t="n">
         <v>4.4191</v>
@@ -640,7 +640,7 @@
         <v>1.1187</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3125</v>
+        <v>1.266</v>
       </c>
       <c r="E5" t="n">
         <v>4.2919</v>
@@ -686,7 +686,7 @@
         <v>1.0492</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2048</v>
+        <v>1.1598</v>
       </c>
       <c r="E6" t="n">
         <v>4.0254</v>
@@ -732,7 +732,7 @@
         <v>1.0444</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1973</v>
+        <v>1.1524</v>
       </c>
       <c r="E7" t="n">
         <v>4.0067</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7189</v>
+        <v>3.7076</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9664</v>
       </c>
       <c r="D8" t="n">
-        <v>1.081</v>
+        <v>1.0332</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7189</v>
+        <v>3.7076</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0132</v>
+        <v>3.0019</v>
       </c>
       <c r="G8" t="n">
         <v>0.7057</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0132</v>
+        <v>3.0019</v>
       </c>
       <c r="I8" t="n">
         <v>3.0272</v>
@@ -824,7 +824,7 @@
         <v>0.9034</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9788</v>
+        <v>0.9369</v>
       </c>
       <c r="E9" t="n">
         <v>3.4659</v>
@@ -870,7 +870,7 @@
         <v>0.8415</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8828</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="E10" t="n">
         <v>3.2283</v>
@@ -916,7 +916,7 @@
         <v>0.8168</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8445</v>
+        <v>0.8045</v>
       </c>
       <c r="E11" t="n">
         <v>3.1336</v>
@@ -962,7 +962,7 @@
         <v>0.6246</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5466</v>
+        <v>0.5107</v>
       </c>
       <c r="E12" t="n">
         <v>2.3962</v>
@@ -1008,7 +1008,7 @@
         <v>0.5819</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4806</v>
+        <v>0.4456</v>
       </c>
       <c r="E13" t="n">
         <v>2.2326</v>
@@ -1054,7 +1054,7 @@
         <v>0.5754</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4705</v>
+        <v>0.4356</v>
       </c>
       <c r="E14" t="n">
         <v>2.2077</v>
@@ -1100,7 +1100,7 @@
         <v>0.3833</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1727</v>
+        <v>0.1419</v>
       </c>
       <c r="E15" t="n">
         <v>1.4705</v>
@@ -1146,7 +1146,7 @@
         <v>0.3585</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1342</v>
+        <v>0.104</v>
       </c>
       <c r="E16" t="n">
         <v>1.3753</v>
@@ -1192,7 +1192,7 @@
         <v>0.3379</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1023</v>
+        <v>0.0725</v>
       </c>
       <c r="E17" t="n">
         <v>1.2963</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0512</v>
+        <v>1.0465</v>
       </c>
       <c r="C18" t="n">
-        <v>0.274</v>
+        <v>0.2728</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0033</v>
+        <v>-0.027</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0512</v>
+        <v>1.0465</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2448</v>
+        <v>1.2401</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1936</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2448</v>
+        <v>1.2401</v>
       </c>
       <c r="I18" t="n">
         <v>1.2506</v>
@@ -1284,7 +1284,7 @@
         <v>0.2694</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0038</v>
+        <v>-0.0321</v>
       </c>
       <c r="E19" t="n">
         <v>1.0336</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9502</v>
+        <v>0.9466</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2477</v>
+        <v>0.2467</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0375</v>
+        <v>-0.0668</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9502</v>
+        <v>0.9466</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9564</v>
+        <v>0.9528</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0062</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9564</v>
+        <v>0.9528</v>
       </c>
       <c r="I20" t="n">
         <v>0.9608</v>
@@ -1376,7 +1376,7 @@
         <v>0.2039</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1053</v>
+        <v>-0.1322</v>
       </c>
       <c r="E21" t="n">
         <v>0.7824</v>
@@ -1422,7 +1422,7 @@
         <v>0.172</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1547</v>
+        <v>-0.181</v>
       </c>
       <c r="E22" t="n">
         <v>0.66</v>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4216</v>
+        <v>0.417</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1099</v>
+        <v>0.1087</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.251</v>
+        <v>-0.2778</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4216</v>
+        <v>0.417</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2331</v>
+        <v>1.2285</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8115</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2331</v>
+        <v>1.2285</v>
       </c>
       <c r="I23" t="n">
         <v>1.2388</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0794</v>
+        <v>0.0765</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0207</v>
+        <v>0.0199</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3893</v>
+        <v>-0.4134</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0794</v>
+        <v>0.0765</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7927</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7133</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7927</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>0.7964</v>
@@ -1554,25 +1554,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0378</v>
+        <v>-0.0409</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0107</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4366</v>
+        <v>-0.4602</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0378</v>
+        <v>-0.0409</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8242</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-0.862</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8242</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>0.828</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0479</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4957</v>
+        <v>-0.5172</v>
       </c>
       <c r="E26" t="n">
         <v>-0.1839</v>
@@ -1652,7 +1652,7 @@
         <v>-0.057</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5097</v>
+        <v>-0.531</v>
       </c>
       <c r="E27" t="n">
         <v>-0.2187</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3588</v>
+        <v>-0.3584</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0935</v>
+        <v>-0.0934</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5663</v>
+        <v>-0.5867</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3588</v>
+        <v>-0.3584</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0936</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>-0.2652</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0936</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="I28" t="n">
         <v>-0.094</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4263</v>
+        <v>-0.4233</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1111</v>
+        <v>-0.1103</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5936</v>
+        <v>-0.6126</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4263</v>
+        <v>-0.4233</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0.3716</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>-0.8016</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1328</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6272</v>
+        <v>-0.6469</v>
       </c>
       <c r="E30" t="n">
         <v>-0.5096000000000001</v>
@@ -1836,7 +1836,7 @@
         <v>-0.2007</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-0.7507</v>
       </c>
       <c r="E31" t="n">
         <v>-0.77</v>
@@ -1882,7 +1882,7 @@
         <v>-0.2021</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7346</v>
+        <v>-0.7528</v>
       </c>
       <c r="E32" t="n">
         <v>-0.7753</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2094</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7458</v>
+        <v>-0.7639</v>
       </c>
       <c r="E33" t="n">
         <v>-0.8032</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2336</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7834</v>
+        <v>-0.801</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8962</v>
@@ -2020,7 +2020,7 @@
         <v>-0.257</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8197</v>
+        <v>-0.8367</v>
       </c>
       <c r="E35" t="n">
         <v>-0.986</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2934</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.876</v>
+        <v>-0.8923</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1255</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3262</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9268999999999999</v>
+        <v>-0.9425</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2514</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3429</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9528</v>
+        <v>-0.968</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3155</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5184</v>
+        <v>-1.5151</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3958</v>
+        <v>-0.3949</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0348</v>
+        <v>-1.0475</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5184</v>
+        <v>-1.5151</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8784</v>
+        <v>-0.8751</v>
       </c>
       <c r="G39" t="n">
         <v>-0.64</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8784</v>
+        <v>-0.8751</v>
       </c>
       <c r="I39" t="n">
         <v>-0.8825</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9833</v>
+        <v>-1.9797</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.517</v>
+        <v>-0.516</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2226</v>
+        <v>-1.2326</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9833</v>
+        <v>-1.9797</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9833</v>
+        <v>-0.9797</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9833</v>
+        <v>-0.9797</v>
       </c>
       <c r="I40" t="n">
         <v>-0.9879</v>
@@ -2296,7 +2296,7 @@
         <v>-0.6695</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.459</v>
+        <v>-1.4672</v>
       </c>
       <c r="E41" t="n">
         <v>-2.5686</v>

--- a/database/event/3985/event_3985_evp_summary.xlsx
+++ b/database/event/3985/event_3985_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7665</v>
+        <v>7.6094</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0244</v>
+        <v>1.9834</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6503</v>
+        <v>2.7973</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7665</v>
+        <v>7.6094</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2012</v>
+        <v>2.8335</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5654</v>
+        <v>4.7759</v>
       </c>
       <c r="H2" t="n">
-        <v>2.2012</v>
+        <v>2.8621</v>
       </c>
       <c r="I2" t="n">
-        <v>2.2012</v>
+        <v>2.8621</v>
       </c>
       <c r="J2" t="n">
-        <v>5.5654</v>
+        <v>4.7759</v>
       </c>
       <c r="K2" t="n">
         <v>127</v>
@@ -529,7 +529,7 @@
         <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>7.7666</v>
+        <v>7.638</v>
       </c>
       <c r="N2" t="n">
         <v>278</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.4565</v>
+        <v>6.9498</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9436</v>
+        <v>1.8115</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5268</v>
+        <v>2.4995</v>
       </c>
       <c r="E3" t="n">
-        <v>7.4565</v>
+        <v>6.9498</v>
       </c>
       <c r="F3" t="n">
-        <v>4.6416</v>
+        <v>4.4518</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8149</v>
+        <v>2.498</v>
       </c>
       <c r="H3" t="n">
-        <v>6.1136</v>
+        <v>10.8107</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9552</v>
+        <v>5.6211</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8149</v>
+        <v>2.498</v>
       </c>
       <c r="K3" t="n">
         <v>122</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>7.770099999999999</v>
+        <v>8.1191</v>
       </c>
       <c r="N3" t="n">
         <v>224</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4191</v>
+        <v>4.0106</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1519</v>
+        <v>1.0454</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3167</v>
+        <v>1.1726</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4191</v>
+        <v>4.0106</v>
       </c>
       <c r="F4" t="n">
-        <v>4.165</v>
+        <v>3.7276</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2541</v>
+        <v>0.283</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1961</v>
+        <v>7.6474</v>
       </c>
       <c r="I4" t="n">
-        <v>3.401</v>
+        <v>3.9763</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2541</v>
+        <v>0.283</v>
       </c>
       <c r="K4" t="n">
         <v>87</v>
@@ -621,7 +621,7 @@
         <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6551</v>
+        <v>4.259300000000001</v>
       </c>
       <c r="N4" t="n">
         <v>140</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2919</v>
+        <v>3.7038</v>
       </c>
       <c r="C5" t="n">
-        <v>1.1187</v>
+        <v>0.9654</v>
       </c>
       <c r="D5" t="n">
-        <v>1.266</v>
+        <v>1.0341</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2919</v>
+        <v>3.7038</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2168</v>
+        <v>0.4544</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0751</v>
+        <v>3.2494</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2168</v>
+        <v>0.4544</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2168</v>
+        <v>0.4544</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0751</v>
+        <v>3.2494</v>
       </c>
       <c r="K5" t="n">
         <v>127</v>
@@ -667,7 +667,7 @@
         <v>151</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2919</v>
+        <v>3.7038</v>
       </c>
       <c r="N5" t="n">
         <v>278</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0254</v>
+        <v>3.5738</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0492</v>
+        <v>0.9315</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1598</v>
+        <v>0.9754</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0254</v>
+        <v>3.5738</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2327</v>
+        <v>2.9546</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2073</v>
+        <v>0.6192</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4686</v>
+        <v>3.1281</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6219</v>
+        <v>3.2567</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2073</v>
+        <v>0.6192</v>
       </c>
       <c r="K6" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4146</v>
+        <v>3.8759</v>
       </c>
       <c r="N6" t="n">
-        <v>140</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0067</v>
+        <v>3.5462</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0444</v>
+        <v>0.9243</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1524</v>
+        <v>0.9629</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0067</v>
+        <v>3.5462</v>
       </c>
       <c r="F7" t="n">
-        <v>4.1545</v>
+        <v>3.6638</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1478</v>
+        <v>-0.1176</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1545</v>
+        <v>7.4228</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3673</v>
+        <v>3.8595</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1478</v>
+        <v>-0.1176</v>
       </c>
       <c r="K7" t="n">
         <v>87</v>
@@ -759,7 +759,7 @@
         <v>53</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2195</v>
+        <v>3.7419</v>
       </c>
       <c r="N7" t="n">
         <v>140</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7076</v>
+        <v>3.4303</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9664</v>
+        <v>0.8941</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0332</v>
+        <v>0.9106</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7076</v>
+        <v>3.4303</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0019</v>
+        <v>3.482</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7057</v>
+        <v>-0.0517</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0019</v>
+        <v>6.7821</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0272</v>
+        <v>3.5264</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7057</v>
+        <v>-0.0517</v>
       </c>
       <c r="K8" t="n">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="L8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7329</v>
+        <v>3.4747</v>
       </c>
       <c r="N8" t="n">
-        <v>201</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4659</v>
+        <v>3.3507</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9034</v>
+        <v>0.8734</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9369</v>
+        <v>0.8747</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4659</v>
+        <v>3.3507</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1807</v>
+        <v>3.6831</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7148</v>
+        <v>-0.3324</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2593</v>
+        <v>7.4905</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4523</v>
+        <v>3.8947</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7148</v>
+        <v>-0.3324</v>
       </c>
       <c r="K9" t="n">
         <v>122</v>
@@ -851,7 +851,7 @@
         <v>102</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7375</v>
+        <v>3.5623</v>
       </c>
       <c r="N9" t="n">
         <v>224</v>
@@ -860,357 +860,357 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jame</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.2283</v>
+        <v>3.1383</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8415</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.7788</v>
       </c>
       <c r="E10" t="n">
-        <v>3.2283</v>
+        <v>3.1383</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7786</v>
+        <v>2.7936</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4497</v>
+        <v>0.3447</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7786</v>
+        <v>4.3565</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7786</v>
+        <v>2.2652</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4497</v>
+        <v>0.3447</v>
       </c>
       <c r="K10" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="L10" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2283</v>
+        <v>2.6099</v>
       </c>
       <c r="N10" t="n">
-        <v>233</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Jame</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1336</v>
+        <v>2.8343</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8168</v>
+        <v>0.7388</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8045</v>
+        <v>0.6415</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1336</v>
+        <v>2.8343</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7874</v>
+        <v>0.7889</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3462</v>
+        <v>2.0454</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7874</v>
+        <v>0.7889</v>
       </c>
       <c r="I11" t="n">
-        <v>2.2593</v>
+        <v>0.7889</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3462</v>
+        <v>2.0454</v>
       </c>
       <c r="K11" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="L11" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6055</v>
+        <v>2.8343</v>
       </c>
       <c r="N11" t="n">
-        <v>140</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>buster</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3962</v>
+        <v>2.5611</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6246</v>
+        <v>0.6676</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5107</v>
+        <v>0.5182</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3962</v>
+        <v>2.5611</v>
       </c>
       <c r="F12" t="n">
-        <v>1.201</v>
+        <v>3.088</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1952</v>
+        <v>-0.5269</v>
       </c>
       <c r="H12" t="n">
-        <v>1.201</v>
+        <v>5.3937</v>
       </c>
       <c r="I12" t="n">
-        <v>1.201</v>
+        <v>2.8045</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1952</v>
+        <v>-0.5269</v>
       </c>
       <c r="K12" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="L12" t="n">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3962</v>
+        <v>2.2776</v>
       </c>
       <c r="N12" t="n">
-        <v>233</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2326</v>
+        <v>2.453</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5819</v>
+        <v>0.6394</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4456</v>
+        <v>0.4694</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2326</v>
+        <v>2.453</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0588</v>
+        <v>1.071</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8262</v>
+        <v>1.382</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0588</v>
+        <v>1.071</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4793</v>
+        <v>1.071</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.8262</v>
+        <v>1.382</v>
       </c>
       <c r="K13" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="L13" t="n">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6531</v>
+        <v>2.453</v>
       </c>
       <c r="N13" t="n">
-        <v>140</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2077</v>
+        <v>2.3579</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5754</v>
+        <v>0.6146</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4356</v>
+        <v>0.4265</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2077</v>
+        <v>2.3579</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8089</v>
+        <v>2.5183</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3988</v>
+        <v>-0.1604</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8089</v>
+        <v>3.3866</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8089</v>
+        <v>1.7609</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3988</v>
+        <v>-0.1604</v>
       </c>
       <c r="K14" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="L14" t="n">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2077</v>
+        <v>1.6005</v>
       </c>
       <c r="N14" t="n">
-        <v>278</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>buster</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4705</v>
+        <v>2.2169</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3833</v>
+        <v>0.5778</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1419</v>
+        <v>0.3628</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4705</v>
+        <v>2.2169</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6463</v>
+        <v>1.1741</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1758</v>
+        <v>1.0428</v>
       </c>
       <c r="H15" t="n">
-        <v>2.6463</v>
+        <v>1.1741</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1449</v>
+        <v>1.1741</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.1758</v>
+        <v>1.0428</v>
       </c>
       <c r="K15" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L15" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9690999999999999</v>
+        <v>2.2169</v>
       </c>
       <c r="N15" t="n">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3753</v>
+        <v>2.0583</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3585</v>
+        <v>0.5365</v>
       </c>
       <c r="D16" t="n">
-        <v>0.104</v>
+        <v>0.2912</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3753</v>
+        <v>2.0583</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2517</v>
+        <v>2.2356</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1236</v>
+        <v>-0.1773</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2517</v>
+        <v>2.2356</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2517</v>
+        <v>2.3275</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1236</v>
+        <v>-0.1773</v>
       </c>
       <c r="K16" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="L16" t="n">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3753</v>
+        <v>2.1502</v>
       </c>
       <c r="N16" t="n">
-        <v>233</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2963</v>
+        <v>1.8204</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3379</v>
+        <v>0.4745</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0725</v>
+        <v>0.1838</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2963</v>
+        <v>1.8204</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7082</v>
+        <v>2.7737</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4119</v>
+        <v>-0.9533</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7082</v>
+        <v>4.2863</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3845</v>
+        <v>2.2287</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4119</v>
+        <v>-0.9533</v>
       </c>
       <c r="K17" t="n">
         <v>122</v>
@@ -1219,7 +1219,7 @@
         <v>102</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9726000000000001</v>
+        <v>1.2754</v>
       </c>
       <c r="N17" t="n">
         <v>224</v>
@@ -1228,231 +1228,231 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0465</v>
+        <v>1.4399</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2728</v>
+        <v>0.3753</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.027</v>
+        <v>0.012</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0465</v>
+        <v>1.4399</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2401</v>
+        <v>1.3367</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1936</v>
+        <v>0.1032</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2401</v>
+        <v>1.3367</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2506</v>
+        <v>1.3917</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1936</v>
+        <v>0.1032</v>
       </c>
       <c r="K18" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="L18" t="n">
         <v>51</v>
       </c>
       <c r="M18" t="n">
-        <v>1.057</v>
+        <v>1.4949</v>
       </c>
       <c r="N18" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0336</v>
+        <v>1.3443</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2694</v>
+        <v>0.3504</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0321</v>
+        <v>-0.0311</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0336</v>
+        <v>1.3443</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8649</v>
+        <v>0.3315</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8985</v>
+        <v>1.0128</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8649</v>
+        <v>0.3315</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8649</v>
+        <v>0.3315</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8985</v>
+        <v>1.0128</v>
       </c>
       <c r="K19" t="n">
         <v>127</v>
       </c>
       <c r="L19" t="n">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0336</v>
+        <v>1.3443</v>
       </c>
       <c r="N19" t="n">
-        <v>278</v>
+        <v>233</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9466</v>
+        <v>1.192</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2467</v>
+        <v>0.3107</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0668</v>
+        <v>-0.0999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9466</v>
+        <v>1.192</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9528</v>
+        <v>-0.5627</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0062</v>
+        <v>1.7547</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9528</v>
+        <v>-0.5627</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9608</v>
+        <v>-0.5627</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0062</v>
+        <v>1.7547</v>
       </c>
       <c r="K20" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>151</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9546</v>
+        <v>1.192</v>
       </c>
       <c r="N20" t="n">
-        <v>201</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7824</v>
+        <v>1.0452</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2039</v>
+        <v>0.2724</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1322</v>
+        <v>-0.1662</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7824</v>
+        <v>1.0452</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7824</v>
+        <v>-0.2368</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1.282</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7824</v>
+        <v>-0.2368</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7824</v>
+        <v>-0.2368</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1.282</v>
       </c>
       <c r="K21" t="n">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7824</v>
+        <v>1.0452</v>
       </c>
       <c r="N21" t="n">
-        <v>155</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.66</v>
+        <v>0.8403</v>
       </c>
       <c r="C22" t="n">
-        <v>0.172</v>
+        <v>0.219</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.181</v>
+        <v>-0.2587</v>
       </c>
       <c r="E22" t="n">
-        <v>0.66</v>
+        <v>0.8403</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7312</v>
+        <v>0.8403</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3912</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7312</v>
+        <v>0.8403</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7312</v>
+        <v>0.8403</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3912</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="L22" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.66</v>
+        <v>0.8403</v>
       </c>
       <c r="N22" t="n">
-        <v>278</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.417</v>
+        <v>0.7105</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1087</v>
+        <v>0.1852</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2778</v>
+        <v>-0.3173</v>
       </c>
       <c r="E23" t="n">
-        <v>0.417</v>
+        <v>0.7105</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2285</v>
+        <v>1.2775</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8115</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2285</v>
+        <v>1.2775</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2388</v>
+        <v>1.33</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8115</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="K23" t="n">
         <v>134</v>
@@ -1495,7 +1495,7 @@
         <v>51</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4272999999999999</v>
+        <v>0.7630000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>185</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0765</v>
+        <v>0.4313</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0199</v>
+        <v>0.1124</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4134</v>
+        <v>-0.4433</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0765</v>
+        <v>0.4313</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7897999999999999</v>
+        <v>1.2291</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7133</v>
+        <v>-0.7978</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7897999999999999</v>
+        <v>1.2291</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7964</v>
+        <v>0.6391</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7133</v>
+        <v>-0.7978</v>
       </c>
       <c r="K24" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="L24" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="M24" t="n">
-        <v>0.08309999999999995</v>
+        <v>-0.1587</v>
       </c>
       <c r="N24" t="n">
-        <v>185</v>
+        <v>224</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0409</v>
+        <v>0.2918</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0107</v>
+        <v>0.0761</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4602</v>
+        <v>-0.5063</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0409</v>
+        <v>0.2918</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8565</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.862</v>
+        <v>-0.5647</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8565</v>
       </c>
       <c r="I25" t="n">
-        <v>0.828</v>
+        <v>0.8917</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.862</v>
+        <v>-0.5647</v>
       </c>
       <c r="K25" t="n">
         <v>134</v>
@@ -1587,7 +1587,7 @@
         <v>51</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.03400000000000003</v>
+        <v>0.3270000000000001</v>
       </c>
       <c r="N25" t="n">
         <v>185</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1839</v>
+        <v>0.2565</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0479</v>
+        <v>0.0669</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5172</v>
+        <v>-0.5222</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1839</v>
+        <v>0.2565</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1839</v>
+        <v>0.7664</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.5099</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1839</v>
+        <v>0.7664</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1839</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.5099</v>
       </c>
       <c r="K26" t="n">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1839</v>
+        <v>0.288</v>
       </c>
       <c r="N26" t="n">
-        <v>155</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>swag</t>
+          <t>bondik</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2187</v>
+        <v>0.2152</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.057</v>
+        <v>0.0561</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.531</v>
+        <v>-0.5409</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2187</v>
+        <v>0.2152</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2187</v>
+        <v>0.304</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.0888</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2187</v>
+        <v>0.304</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2187</v>
+        <v>0.3165</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.0888</v>
       </c>
       <c r="K27" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2187</v>
+        <v>0.2277</v>
       </c>
       <c r="N27" t="n">
-        <v>94</v>
+        <v>201</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bondik</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3584</v>
+        <v>0.0238</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0934</v>
+        <v>0.0062</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5867</v>
+        <v>-0.6273</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3584</v>
+        <v>0.0238</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.0238</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2652</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0.0238</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.094</v>
+        <v>0.0238</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2652</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="L28" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3592</v>
+        <v>0.0238</v>
       </c>
       <c r="N28" t="n">
-        <v>201</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29">
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4233</v>
+        <v>-0.0776</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1103</v>
+        <v>-0.0202</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6126</v>
+        <v>-0.673</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4233</v>
+        <v>-0.0776</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.4433</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3716</v>
+        <v>0.3657</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.4433</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8016</v>
+        <v>-0.4615</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3716</v>
+        <v>0.3657</v>
       </c>
       <c r="K29" t="n">
         <v>134</v>
@@ -1771,7 +1771,7 @@
         <v>51</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.43</v>
+        <v>-0.0958</v>
       </c>
       <c r="N29" t="n">
         <v>185</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.1607</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1328</v>
+        <v>-0.0419</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6469</v>
+        <v>-0.7106</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.1607</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4108</v>
+        <v>-0.1607</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.9204</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4108</v>
+        <v>-0.1607</v>
       </c>
       <c r="I30" t="n">
-        <v>0.333</v>
+        <v>-0.1607</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9204</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="L30" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5873999999999999</v>
+        <v>-0.1607</v>
       </c>
       <c r="N30" t="n">
-        <v>224</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>swag</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.77</v>
+        <v>-0.2175</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2007</v>
+        <v>-0.0567</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7507</v>
+        <v>-0.7362</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.77</v>
+        <v>-0.2175</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.77</v>
+        <v>-0.2175</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.77</v>
+        <v>-0.2175</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.77</v>
+        <v>-0.2175</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>155</v>
+        <v>94</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.77</v>
+        <v>-0.2175</v>
       </c>
       <c r="N31" t="n">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.7753</v>
+        <v>-0.4133</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2021</v>
+        <v>-0.1077</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7528</v>
+        <v>-0.8246</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7753</v>
+        <v>-0.4133</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.7753</v>
+        <v>-0.4133</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7753</v>
+        <v>-0.4133</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7753</v>
+        <v>-0.4133</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.7753</v>
+        <v>-0.4133</v>
       </c>
       <c r="N32" t="n">
         <v>155</v>
@@ -1918,124 +1918,124 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>KrizzeN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8032</v>
+        <v>-0.4815</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2094</v>
+        <v>-0.1255</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7639</v>
+        <v>-0.8554</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8032</v>
+        <v>-0.4815</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8032</v>
+        <v>0.303</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-0.7845</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8032</v>
+        <v>0.303</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8032</v>
+        <v>0.303</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>-0.7845</v>
       </c>
       <c r="K33" t="n">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8032</v>
+        <v>-0.4815</v>
       </c>
       <c r="N33" t="n">
-        <v>155</v>
+        <v>233</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cooper</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8962</v>
+        <v>-0.4878</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2336</v>
+        <v>-0.1271</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.801</v>
+        <v>-0.8582</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8962</v>
+        <v>-0.4878</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.8962</v>
+        <v>-0.4878</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8962</v>
+        <v>-0.4878</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.8962</v>
+        <v>-0.4878</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8962</v>
+        <v>-0.4878</v>
       </c>
       <c r="N34" t="n">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Zellsis</t>
+          <t>Cooper</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.986</v>
+        <v>-0.7045</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.257</v>
+        <v>-0.1836</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8367</v>
+        <v>-0.9560999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.986</v>
+        <v>-0.7045</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.986</v>
+        <v>-0.7045</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.986</v>
+        <v>-0.7045</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.986</v>
+        <v>-0.7045</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.986</v>
+        <v>-0.7045</v>
       </c>
       <c r="N35" t="n">
         <v>94</v>
@@ -2056,78 +2056,78 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>KrizzeN</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1255</v>
+        <v>-0.747</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2934</v>
+        <v>-0.1947</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8923</v>
+        <v>-0.9752</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1255</v>
+        <v>-0.747</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.2028</v>
+        <v>-0.747</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.9227</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2028</v>
+        <v>-0.747</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2028</v>
+        <v>-0.747</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9227</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="L36" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1255</v>
+        <v>-0.747</v>
       </c>
       <c r="N36" t="n">
-        <v>233</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>Zellsis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2514</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3262</v>
+        <v>-0.2006</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9425</v>
+        <v>-0.9855</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2514</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.2514</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.2514</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.2514</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2514</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>94</v>
@@ -2148,32 +2148,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3155</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3429</v>
+        <v>-0.2505</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.968</v>
+        <v>-1.0719</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3155</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3155</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3155</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3155</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3155</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>94</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5151</v>
+        <v>-1.1463</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3949</v>
+        <v>-0.2988</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0475</v>
+        <v>-1.1555</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5151</v>
+        <v>-1.1463</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.8751</v>
+        <v>-0.7094</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.64</v>
+        <v>-0.4369</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.8751</v>
+        <v>-0.7094</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8825</v>
+        <v>-0.7386</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.64</v>
+        <v>-0.4369</v>
       </c>
       <c r="K39" t="n">
         <v>150</v>
@@ -2231,7 +2231,7 @@
         <v>51</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5225</v>
+        <v>-1.1755</v>
       </c>
       <c r="N39" t="n">
         <v>201</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9797</v>
+        <v>-1.3623</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.516</v>
+        <v>-0.3551</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2326</v>
+        <v>-1.253</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9797</v>
+        <v>-1.3623</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.9797</v>
+        <v>-0.6203</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.742</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.9797</v>
+        <v>-0.6203</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9879</v>
+        <v>-0.6458</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.742</v>
       </c>
       <c r="K40" t="n">
         <v>150</v>
@@ -2277,7 +2277,7 @@
         <v>51</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9879</v>
+        <v>-1.3878</v>
       </c>
       <c r="N40" t="n">
         <v>201</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5686</v>
+        <v>-1.965</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6695</v>
+        <v>-0.5122</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4672</v>
+        <v>-1.5251</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5686</v>
+        <v>-1.965</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.7013</v>
+        <v>-1.2516</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8673</v>
+        <v>-0.7134</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.7013</v>
+        <v>-1.2516</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.7013</v>
+        <v>-1.2516</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8673</v>
+        <v>-0.7134</v>
       </c>
       <c r="K41" t="n">
         <v>127</v>
@@ -2323,7 +2323,7 @@
         <v>106</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.5686</v>
+        <v>-1.965</v>
       </c>
       <c r="N41" t="n">
         <v>233</v>
@@ -2429,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>0.736</v>
+        <v>0.9133</v>
       </c>
       <c r="J2" t="n">
-        <v>20.608</v>
+        <v>25.5724</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0118</v>
+        <v>-0.0008</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3304</v>
+        <v>-0.0224</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2322</v>
+        <v>-0.1358</v>
       </c>
       <c r="J4" t="n">
-        <v>-6.5016</v>
+        <v>-3.8024</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.9</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2322</v>
+        <v>-0.1358</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.5016</v>
+        <v>-3.8024</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.401</v>
+        <v>-0.2506</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.228</v>
+        <v>-7.0168</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.25</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7623</v>
+        <v>0.7279</v>
       </c>
       <c r="J7" t="n">
-        <v>21.3444</v>
+        <v>20.3812</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5355</v>
+        <v>0.4979</v>
       </c>
       <c r="J8" t="n">
-        <v>14.994</v>
+        <v>13.9412</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4527</v>
+        <v>0.4175</v>
       </c>
       <c r="J9" t="n">
-        <v>12.6756</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.86</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.531</v>
+        <v>-0.4747</v>
       </c>
       <c r="J10" t="n">
-        <v>-14.868</v>
+        <v>-13.2916</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.83</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6095</v>
+        <v>-0.5558</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.066</v>
+        <v>-15.5624</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.68</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3329</v>
+        <v>-0.2792</v>
       </c>
       <c r="J12" t="n">
-        <v>-6.3251</v>
+        <v>-5.3048</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5238</v>
+        <v>-0.3995</v>
       </c>
       <c r="J13" t="n">
-        <v>-9.952199999999999</v>
+        <v>-7.5905</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.54</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5627</v>
+        <v>-0.4172</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.6913</v>
+        <v>-7.9268</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.49</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6607</v>
+        <v>-0.4615</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.5533</v>
+        <v>-8.7685</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.41</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7798</v>
+        <v>-0.5376</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.8162</v>
+        <v>-10.2144</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.84</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6981</v>
+        <v>1.4735</v>
       </c>
       <c r="J17" t="n">
-        <v>32.2639</v>
+        <v>27.9965</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.82</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6629</v>
+        <v>1.4512</v>
       </c>
       <c r="J18" t="n">
-        <v>31.5951</v>
+        <v>27.5728</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.74</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5187</v>
+        <v>1.3616</v>
       </c>
       <c r="J19" t="n">
-        <v>28.8553</v>
+        <v>25.8704</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.35</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7004</v>
+        <v>0.8363</v>
       </c>
       <c r="J20" t="n">
-        <v>13.3076</v>
+        <v>15.8897</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.05</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0165</v>
+        <v>0.0741</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3135</v>
+        <v>1.4079</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3047</v>
+        <v>0.3365</v>
       </c>
       <c r="J22" t="n">
-        <v>7.6175</v>
+        <v>8.4125</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2568</v>
+        <v>0.2835</v>
       </c>
       <c r="J23" t="n">
-        <v>6.42</v>
+        <v>7.0875</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1086</v>
+        <v>0.1139</v>
       </c>
       <c r="J24" t="n">
-        <v>2.715</v>
+        <v>2.8475</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.89</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2484</v>
+        <v>-0.1466</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.21</v>
+        <v>-3.665</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2967</v>
+        <v>-0.1788</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.4175</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7923</v>
+        <v>0.5876</v>
       </c>
       <c r="J27" t="n">
-        <v>19.8075</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.15</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4886</v>
+        <v>0.4094</v>
       </c>
       <c r="J28" t="n">
-        <v>12.215</v>
+        <v>10.235</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1162</v>
+        <v>0.1494</v>
       </c>
       <c r="J29" t="n">
-        <v>2.905</v>
+        <v>3.735</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1267</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.1675</v>
+        <v>-1.785</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.93</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3436</v>
+        <v>-0.281</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.59</v>
+        <v>-7.025</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.01</v>
       </c>
       <c r="I32" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0612</v>
       </c>
       <c r="J32" t="n">
-        <v>2.5032</v>
+        <v>1.7136</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0612</v>
       </c>
       <c r="J33" t="n">
-        <v>2.5032</v>
+        <v>1.7136</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0506</v>
+        <v>-0.0535</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.4168</v>
+        <v>-1.498</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.86</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2564</v>
+        <v>-0.1656</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.1792</v>
+        <v>-4.6368</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.64</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5778</v>
+        <v>-0.3803</v>
       </c>
       <c r="J36" t="n">
-        <v>-16.1784</v>
+        <v>-10.6484</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.56</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3249</v>
+        <v>0.9359</v>
       </c>
       <c r="J37" t="n">
-        <v>37.0972</v>
+        <v>26.2052</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.37</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9336</v>
+        <v>0.6926</v>
       </c>
       <c r="J38" t="n">
-        <v>26.1408</v>
+        <v>19.3928</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6725</v>
+        <v>0.5461</v>
       </c>
       <c r="J39" t="n">
-        <v>18.83</v>
+        <v>15.2908</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.03</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0027</v>
+        <v>0.0766</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0756</v>
+        <v>2.1448</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3699</v>
+        <v>-0.2906</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.3572</v>
+        <v>-8.136799999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8889</v>
+        <v>0.6663</v>
       </c>
       <c r="J42" t="n">
-        <v>24.0003</v>
+        <v>17.9901</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.34</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8662</v>
+        <v>0.6531</v>
       </c>
       <c r="J43" t="n">
-        <v>23.3874</v>
+        <v>17.6337</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.522</v>
+        <v>0.4785</v>
       </c>
       <c r="J44" t="n">
-        <v>14.094</v>
+        <v>12.9195</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.2</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4945</v>
+        <v>0.4644</v>
       </c>
       <c r="J45" t="n">
-        <v>13.3515</v>
+        <v>12.5388</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.06</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1025</v>
+        <v>0.1763</v>
       </c>
       <c r="J46" t="n">
-        <v>2.7675</v>
+        <v>4.7601</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3921</v>
+        <v>0.3952</v>
       </c>
       <c r="J47" t="n">
-        <v>10.5867</v>
+        <v>10.6704</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.02</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1458</v>
+        <v>0.1187</v>
       </c>
       <c r="J48" t="n">
-        <v>3.9366</v>
+        <v>3.2049</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.77</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3711</v>
+        <v>-0.2462</v>
       </c>
       <c r="J49" t="n">
-        <v>-10.0197</v>
+        <v>-6.6474</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.58</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6384</v>
+        <v>-0.4262</v>
       </c>
       <c r="J50" t="n">
-        <v>-17.2368</v>
+        <v>-11.5074</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6512</v>
+        <v>-0.4355</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.5824</v>
+        <v>-11.7585</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1.7032</v>
+        <v>1.1977</v>
       </c>
       <c r="J52" t="n">
-        <v>47.6896</v>
+        <v>33.5356</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0756</v>
+        <v>0.0886</v>
       </c>
       <c r="J53" t="n">
-        <v>2.1168</v>
+        <v>2.4808</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.98</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1423</v>
+        <v>-0.1005</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.9844</v>
+        <v>-2.814</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8229</v>
+        <v>-0.7831</v>
       </c>
       <c r="J55" t="n">
-        <v>-23.0412</v>
+        <v>-21.9268</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.9143</v>
+        <v>-0.8824</v>
       </c>
       <c r="J56" t="n">
-        <v>-25.6004</v>
+        <v>-24.7072</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3594</v>
+        <v>0.3765</v>
       </c>
       <c r="J57" t="n">
-        <v>10.0632</v>
+        <v>10.542</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.08</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1983</v>
+        <v>0.2083</v>
       </c>
       <c r="J58" t="n">
-        <v>5.5524</v>
+        <v>5.8324</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1877</v>
+        <v>-0.1102</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.2556</v>
+        <v>-3.0856</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.88</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2571</v>
+        <v>-0.1545</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.1988</v>
+        <v>-4.326</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2734</v>
+        <v>-0.1653</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.6552</v>
+        <v>-4.6284</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.98</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0149</v>
+        <v>-0.0175</v>
       </c>
       <c r="J62" t="n">
-        <v>0.3576</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0149</v>
+        <v>-0.0175</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3576</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.1216</v>
+        <v>-2.0184</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3674</v>
+        <v>-0.2401</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.817600000000001</v>
+        <v>-5.7624</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.57</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6571</v>
+        <v>-0.4392</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.7704</v>
+        <v>-10.5408</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.94</v>
       </c>
       <c r="I67" t="n">
-        <v>1.8707</v>
+        <v>1.3859</v>
       </c>
       <c r="J67" t="n">
-        <v>44.8968</v>
+        <v>33.2616</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.57</v>
       </c>
       <c r="I68" t="n">
-        <v>1.3282</v>
+        <v>0.9403</v>
       </c>
       <c r="J68" t="n">
-        <v>31.8768</v>
+        <v>22.5672</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.11</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2353</v>
+        <v>0.3143</v>
       </c>
       <c r="J69" t="n">
-        <v>5.6472</v>
+        <v>7.5432</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5478</v>
+        <v>-0.4763</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.1472</v>
+        <v>-11.4312</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.83</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6735</v>
+        <v>-0.612</v>
       </c>
       <c r="J71" t="n">
-        <v>-16.164</v>
+        <v>-14.688</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.21</v>
       </c>
       <c r="I72" t="n">
-        <v>0.46</v>
+        <v>0.4498</v>
       </c>
       <c r="J72" t="n">
-        <v>12.42</v>
+        <v>12.1446</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.89</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1544</v>
+        <v>-0.1278</v>
       </c>
       <c r="J73" t="n">
-        <v>-4.1688</v>
+        <v>-3.4506</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.86</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2085</v>
+        <v>-0.1598</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.6295</v>
+        <v>-4.3146</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4946</v>
+        <v>-0.3246</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.3542</v>
+        <v>-8.764200000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.51</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7282</v>
+        <v>-0.4924</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.6614</v>
+        <v>-13.2948</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.7</v>
       </c>
       <c r="I77" t="n">
-        <v>1.5604</v>
+        <v>1.0928</v>
       </c>
       <c r="J77" t="n">
-        <v>42.1308</v>
+        <v>29.5056</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.44</v>
       </c>
       <c r="I78" t="n">
-        <v>1.0534</v>
+        <v>0.7724</v>
       </c>
       <c r="J78" t="n">
-        <v>28.4418</v>
+        <v>20.8548</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.3</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7286</v>
+        <v>0.5931</v>
       </c>
       <c r="J79" t="n">
-        <v>19.6722</v>
+        <v>16.0137</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.09</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1694</v>
+        <v>0.2522</v>
       </c>
       <c r="J80" t="n">
-        <v>4.5738</v>
+        <v>6.8094</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4164</v>
+        <v>-0.336</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.2428</v>
+        <v>-9.071999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7088</v>
+        <v>0.6531</v>
       </c>
       <c r="J82" t="n">
-        <v>18.4288</v>
+        <v>16.9806</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.14</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2839</v>
+        <v>0.3178</v>
       </c>
       <c r="J83" t="n">
-        <v>7.3814</v>
+        <v>8.2628</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.09</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="J84" t="n">
-        <v>5.2</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4036</v>
+        <v>-0.252</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.4936</v>
+        <v>-6.552</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.65</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5881999999999999</v>
+        <v>-0.3859</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.2932</v>
+        <v>-10.0334</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.42</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1284</v>
+        <v>0.7994</v>
       </c>
       <c r="J87" t="n">
-        <v>29.3384</v>
+        <v>20.7844</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.89</v>
+        <v>0.6471</v>
       </c>
       <c r="J88" t="n">
-        <v>23.14</v>
+        <v>16.8246</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.16</v>
       </c>
       <c r="I89" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.4267</v>
       </c>
       <c r="J89" t="n">
-        <v>13.5902</v>
+        <v>11.0942</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.74</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.834</v>
+        <v>-0.7932</v>
       </c>
       <c r="J90" t="n">
-        <v>-21.684</v>
+        <v>-20.6232</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.7</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.9244</v>
+        <v>-0.8922</v>
       </c>
       <c r="J91" t="n">
-        <v>-24.0344</v>
+        <v>-23.1972</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.96</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0031</v>
+        <v>-0.0339</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.0775</v>
+        <v>-0.8475</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.83</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.2364</v>
+        <v>-0.1849</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.91</v>
+        <v>-4.6225</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2901</v>
+        <v>-0.2146</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.2525</v>
+        <v>-5.365</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.7</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4652</v>
+        <v>-0.3088</v>
       </c>
       <c r="J95" t="n">
-        <v>-11.63</v>
+        <v>-7.72</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5367</v>
+        <v>-0.3561</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.4175</v>
+        <v>-8.9025</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>1.1755</v>
+        <v>0.847</v>
       </c>
       <c r="J97" t="n">
-        <v>29.3875</v>
+        <v>21.175</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.36</v>
       </c>
       <c r="I98" t="n">
-        <v>0.875</v>
+        <v>0.6698</v>
       </c>
       <c r="J98" t="n">
-        <v>21.875</v>
+        <v>16.745</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.34</v>
       </c>
       <c r="I99" t="n">
-        <v>0.8278</v>
+        <v>0.6441</v>
       </c>
       <c r="J99" t="n">
-        <v>20.695</v>
+        <v>16.1025</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4328</v>
+        <v>0.4423</v>
       </c>
       <c r="J100" t="n">
-        <v>10.82</v>
+        <v>11.0575</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.09</v>
       </c>
       <c r="I101" t="n">
-        <v>0.168</v>
+        <v>0.2513</v>
       </c>
       <c r="J101" t="n">
-        <v>4.2</v>
+        <v>6.2825</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.89</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0718</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.5078</v>
+        <v>-1.8354</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.68</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.412</v>
+        <v>-0.3108</v>
       </c>
       <c r="J103" t="n">
-        <v>-8.651999999999999</v>
+        <v>-6.5268</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.68</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.412</v>
+        <v>-0.3108</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.651999999999999</v>
+        <v>-6.5268</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5432</v>
+        <v>-0.3734</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.4072</v>
+        <v>-7.8414</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.44</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7789</v>
+        <v>-0.5325</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.3569</v>
+        <v>-11.1825</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.59</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2923</v>
+        <v>1.2078</v>
       </c>
       <c r="J107" t="n">
-        <v>27.1383</v>
+        <v>25.3638</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.52</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1513</v>
+        <v>1.1245</v>
       </c>
       <c r="J108" t="n">
-        <v>24.1773</v>
+        <v>23.6145</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.48</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0661</v>
+        <v>1.0766</v>
       </c>
       <c r="J109" t="n">
-        <v>22.3881</v>
+        <v>22.6086</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.33</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7057</v>
+        <v>0.8176</v>
       </c>
       <c r="J110" t="n">
-        <v>14.8197</v>
+        <v>17.1696</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.22</v>
       </c>
       <c r="I111" t="n">
-        <v>0.4545</v>
+        <v>0.5631</v>
       </c>
       <c r="J111" t="n">
-        <v>9.544499999999999</v>
+        <v>11.8251</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.12</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3318</v>
+        <v>0.3569</v>
       </c>
       <c r="J112" t="n">
-        <v>7.9632</v>
+        <v>8.5656</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2352</v>
+        <v>-0.1784</v>
       </c>
       <c r="J113" t="n">
-        <v>-5.6448</v>
+        <v>-4.2816</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.84</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2352</v>
+        <v>-0.1784</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.6448</v>
+        <v>-4.2816</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4163</v>
+        <v>-0.2746</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.991199999999999</v>
+        <v>-6.5904</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6882</v>
+        <v>-0.4627</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.5168</v>
+        <v>-11.1048</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1378</v>
+        <v>1.0924</v>
       </c>
       <c r="J117" t="n">
-        <v>27.3072</v>
+        <v>26.2176</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7125</v>
+        <v>0.7365</v>
       </c>
       <c r="J118" t="n">
-        <v>17.1</v>
+        <v>17.676</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5933</v>
+        <v>0.6466</v>
       </c>
       <c r="J119" t="n">
-        <v>14.2392</v>
+        <v>15.5184</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.13</v>
       </c>
       <c r="I120" t="n">
-        <v>0.2977</v>
+        <v>0.3738</v>
       </c>
       <c r="J120" t="n">
-        <v>7.1448</v>
+        <v>8.9712</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.12</v>
       </c>
       <c r="I121" t="n">
-        <v>0.2704</v>
+        <v>0.3468</v>
       </c>
       <c r="J121" t="n">
-        <v>6.4896</v>
+        <v>8.3232</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.45</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7236</v>
+        <v>0.8973</v>
       </c>
       <c r="J122" t="n">
-        <v>20.9844</v>
+        <v>26.0217</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.1512</v>
+        <v>-0.0949</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.3848</v>
+        <v>-2.7521</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.82</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3404</v>
+        <v>-0.2127</v>
       </c>
       <c r="J124" t="n">
-        <v>-9.871600000000001</v>
+        <v>-6.1683</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.8</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3704</v>
+        <v>-0.2328</v>
       </c>
       <c r="J125" t="n">
-        <v>-10.7416</v>
+        <v>-6.7512</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.74</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.456</v>
+        <v>-0.2918</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.224</v>
+        <v>-8.462199999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3806</v>
+        <v>1.2424</v>
       </c>
       <c r="J127" t="n">
-        <v>40.0374</v>
+        <v>36.0296</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.56</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3613</v>
+        <v>1.2296</v>
       </c>
       <c r="J128" t="n">
-        <v>39.4777</v>
+        <v>35.6584</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0328</v>
+        <v>0.095</v>
       </c>
       <c r="J129" t="n">
-        <v>0.9512</v>
+        <v>2.755</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.95</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.3139</v>
+        <v>-0.2397</v>
       </c>
       <c r="J130" t="n">
-        <v>-9.1031</v>
+        <v>-6.9513</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9898</v>
+        <v>-0.9634</v>
       </c>
       <c r="J131" t="n">
-        <v>-28.7042</v>
+        <v>-27.9386</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.83</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.2152</v>
+        <v>-0.1783</v>
       </c>
       <c r="J132" t="n">
-        <v>-4.5192</v>
+        <v>-3.7443</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.8</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.265</v>
+        <v>-0.2092</v>
       </c>
       <c r="J133" t="n">
-        <v>-5.565</v>
+        <v>-4.3932</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.73</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.398</v>
+        <v>-0.2753</v>
       </c>
       <c r="J134" t="n">
-        <v>-8.358000000000001</v>
+        <v>-5.7813</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4634</v>
+        <v>-0.3125</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.731400000000001</v>
+        <v>-6.5625</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4634</v>
+        <v>-0.3125</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.731400000000001</v>
+        <v>-6.5625</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.4565</v>
+        <v>1.3067</v>
       </c>
       <c r="J137" t="n">
-        <v>30.5865</v>
+        <v>27.4407</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.56</v>
       </c>
       <c r="I138" t="n">
-        <v>1.2453</v>
+        <v>1.176</v>
       </c>
       <c r="J138" t="n">
-        <v>26.1513</v>
+        <v>24.696</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.36</v>
       </c>
       <c r="I139" t="n">
-        <v>0.7877</v>
+        <v>0.8875</v>
       </c>
       <c r="J139" t="n">
-        <v>16.5417</v>
+        <v>18.6375</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.32</v>
       </c>
       <c r="I140" t="n">
-        <v>0.695</v>
+        <v>0.8004</v>
       </c>
       <c r="J140" t="n">
-        <v>14.595</v>
+        <v>16.8084</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.1</v>
       </c>
       <c r="I141" t="n">
-        <v>0.1628</v>
+        <v>0.2562</v>
       </c>
       <c r="J141" t="n">
-        <v>3.4188</v>
+        <v>5.3802</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.78</v>
       </c>
       <c r="I142" t="n">
-        <v>1.6971</v>
+        <v>1.458</v>
       </c>
       <c r="J142" t="n">
-        <v>37.3362</v>
+        <v>32.076</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.62</v>
       </c>
       <c r="I143" t="n">
-        <v>1.4045</v>
+        <v>1.266</v>
       </c>
       <c r="J143" t="n">
-        <v>30.899</v>
+        <v>27.852</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.34</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8196</v>
+        <v>0.8582</v>
       </c>
       <c r="J144" t="n">
-        <v>18.0312</v>
+        <v>18.8804</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.91</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.4773</v>
+        <v>-0.3998</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.5006</v>
+        <v>-8.7956</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5315</v>
+        <v>-0.4575</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.693</v>
+        <v>-10.065</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.93</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0587</v>
+        <v>-0.0718</v>
       </c>
       <c r="J147" t="n">
-        <v>-1.2914</v>
+        <v>-1.5796</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.92</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.0771</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.6962</v>
+        <v>-1.8502</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.78</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3291</v>
+        <v>-0.2326</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.2402</v>
+        <v>-5.1172</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.74</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.401</v>
+        <v>-0.2701</v>
       </c>
       <c r="J150" t="n">
-        <v>-8.821999999999999</v>
+        <v>-5.9422</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.54</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6808999999999999</v>
+        <v>-0.458</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.9798</v>
+        <v>-10.076</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.46</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1758</v>
+        <v>1.1072</v>
       </c>
       <c r="J152" t="n">
-        <v>35.274</v>
+        <v>33.216</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.32</v>
       </c>
       <c r="I153" t="n">
-        <v>0.8761</v>
+        <v>0.862</v>
       </c>
       <c r="J153" t="n">
-        <v>26.283</v>
+        <v>25.86</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2138</v>
+        <v>0.2608</v>
       </c>
       <c r="J154" t="n">
-        <v>6.414</v>
+        <v>7.824</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4258</v>
+        <v>-0.3566</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.774</v>
+        <v>-10.698</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.482</v>
+        <v>-0.4147</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.46</v>
+        <v>-12.441</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4295</v>
+        <v>0.4968</v>
       </c>
       <c r="J157" t="n">
-        <v>12.885</v>
+        <v>14.904</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3431</v>
+        <v>0.386</v>
       </c>
       <c r="J158" t="n">
-        <v>10.293</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.01</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0466</v>
+        <v>0.0392</v>
       </c>
       <c r="J159" t="n">
-        <v>1.398</v>
+        <v>1.176</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.87</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2746</v>
+        <v>-0.1657</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.238</v>
+        <v>-4.971</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.67</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5572</v>
+        <v>-0.3634</v>
       </c>
       <c r="J161" t="n">
-        <v>-16.716</v>
+        <v>-10.902</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.98</v>
       </c>
       <c r="I162" t="n">
-        <v>1.9568</v>
+        <v>1.6559</v>
       </c>
       <c r="J162" t="n">
-        <v>41.0928</v>
+        <v>34.7739</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.94</v>
       </c>
       <c r="I163" t="n">
-        <v>1.9086</v>
+        <v>1.6108</v>
       </c>
       <c r="J163" t="n">
-        <v>40.0806</v>
+        <v>33.8268</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.32</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6798</v>
+        <v>0.7938</v>
       </c>
       <c r="J164" t="n">
-        <v>14.2758</v>
+        <v>16.6698</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5671</v>
+        <v>0.6801</v>
       </c>
       <c r="J165" t="n">
-        <v>11.9091</v>
+        <v>14.2821</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.67</v>
       </c>
       <c r="I166" t="n">
-        <v>-1.0556</v>
+        <v>-1.0397</v>
       </c>
       <c r="J166" t="n">
-        <v>-22.1676</v>
+        <v>-21.8337</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.97</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0934</v>
+        <v>0.0599</v>
       </c>
       <c r="J167" t="n">
-        <v>1.9614</v>
+        <v>1.2579</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2496</v>
+        <v>-0.2141</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.2416</v>
+        <v>-4.4961</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.67</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.4076</v>
+        <v>-0.3152</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.5596</v>
+        <v>-6.6192</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.51</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6763</v>
+        <v>-0.4612</v>
       </c>
       <c r="J170" t="n">
-        <v>-14.2023</v>
+        <v>-9.6852</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.23</v>
       </c>
       <c r="I171" t="n">
-        <v>-1.029</v>
+        <v>-0.7271</v>
       </c>
       <c r="J171" t="n">
-        <v>-21.609</v>
+        <v>-15.2691</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.76</v>
       </c>
       <c r="I172" t="n">
-        <v>1.5833</v>
+        <v>1.3949</v>
       </c>
       <c r="J172" t="n">
-        <v>33.2493</v>
+        <v>29.2929</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.75</v>
       </c>
       <c r="I173" t="n">
-        <v>1.5653</v>
+        <v>1.3835</v>
       </c>
       <c r="J173" t="n">
-        <v>32.8713</v>
+        <v>29.0535</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.67</v>
       </c>
       <c r="I174" t="n">
-        <v>1.4174</v>
+        <v>1.2917</v>
       </c>
       <c r="J174" t="n">
-        <v>29.7654</v>
+        <v>27.1257</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.21</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4118</v>
+        <v>0.5255</v>
       </c>
       <c r="J175" t="n">
-        <v>8.6478</v>
+        <v>11.0355</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.07</v>
       </c>
       <c r="I176" t="n">
-        <v>0.0568</v>
+        <v>0.1497</v>
       </c>
       <c r="J176" t="n">
-        <v>1.1928</v>
+        <v>3.1437</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.07</v>
       </c>
       <c r="I177" t="n">
-        <v>0.319</v>
+        <v>0.3477</v>
       </c>
       <c r="J177" t="n">
-        <v>6.699</v>
+        <v>7.3017</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.76</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2816</v>
+        <v>-0.2325</v>
       </c>
       <c r="J178" t="n">
-        <v>-5.9136</v>
+        <v>-4.8825</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.74</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3133</v>
+        <v>-0.2529</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.5793</v>
+        <v>-5.3109</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.37</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.8666</v>
+        <v>-0.5984</v>
       </c>
       <c r="J180" t="n">
-        <v>-18.1986</v>
+        <v>-12.5664</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.36</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.8788</v>
+        <v>-0.6079</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.4548</v>
+        <v>-12.7659</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.02</v>
       </c>
       <c r="I182" t="n">
-        <v>0.1014</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="J182" t="n">
-        <v>2.9406</v>
+        <v>2.3664</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0409</v>
+        <v>0.0133</v>
       </c>
       <c r="J183" t="n">
-        <v>1.1861</v>
+        <v>0.3857</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.95</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0882</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.5578</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.91</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1801</v>
+        <v>-0.1156</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.2229</v>
+        <v>-3.3524</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.423</v>
+        <v>-0.2699</v>
       </c>
       <c r="J186" t="n">
-        <v>-12.267</v>
+        <v>-7.8271</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.56</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3326</v>
+        <v>1.2136</v>
       </c>
       <c r="J187" t="n">
-        <v>38.6454</v>
+        <v>35.1944</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.29</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7585</v>
+        <v>0.7663</v>
       </c>
       <c r="J188" t="n">
-        <v>21.9965</v>
+        <v>22.2227</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.29</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7585</v>
+        <v>0.7663</v>
       </c>
       <c r="J189" t="n">
-        <v>21.9965</v>
+        <v>22.2227</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.04</v>
       </c>
       <c r="I190" t="n">
-        <v>0.0436</v>
+        <v>0.1153</v>
       </c>
       <c r="J190" t="n">
-        <v>1.2644</v>
+        <v>3.3437</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4809</v>
+        <v>-0.4074</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.9461</v>
+        <v>-11.8146</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.4</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5807</v>
+        <v>0.5112</v>
       </c>
       <c r="J192" t="n">
-        <v>15.0982</v>
+        <v>13.2912</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.24</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3658</v>
+        <v>0.3279</v>
       </c>
       <c r="J193" t="n">
-        <v>9.5108</v>
+        <v>8.525399999999999</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.18</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2615</v>
+        <v>0.2568</v>
       </c>
       <c r="J194" t="n">
-        <v>6.799</v>
+        <v>6.6768</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.18</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2615</v>
+        <v>0.2568</v>
       </c>
       <c r="J195" t="n">
-        <v>6.799</v>
+        <v>6.6768</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>0.0456</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>1.1856</v>
+        <v>1.9604</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2364</v>
+        <v>0.1825</v>
       </c>
       <c r="J197" t="n">
-        <v>6.1464</v>
+        <v>4.745</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.07</v>
       </c>
       <c r="I198" t="n">
-        <v>0.2186</v>
+        <v>0.1655</v>
       </c>
       <c r="J198" t="n">
-        <v>5.6836</v>
+        <v>4.303</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.87</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2338</v>
+        <v>-0.1545</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.0788</v>
+        <v>-4.017</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4117</v>
+        <v>-0.2648</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.7042</v>
+        <v>-6.8848</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.3605</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.2974</v>
+        <v>-9.372999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3525</v>
+        <v>0.3872</v>
       </c>
       <c r="J202" t="n">
-        <v>9.5175</v>
+        <v>10.4544</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.01</v>
       </c>
       <c r="I203" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>2.5704</v>
+        <v>1.7712</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3494</v>
+        <v>-0.2246</v>
       </c>
       <c r="J204" t="n">
-        <v>-9.4338</v>
+        <v>-6.0642</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.8</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3494</v>
+        <v>-0.2246</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.4338</v>
+        <v>-6.0642</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5617</v>
+        <v>-0.3691</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.1659</v>
+        <v>-9.9657</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.49</v>
       </c>
       <c r="I207" t="n">
-        <v>1.2283</v>
+        <v>1.1421</v>
       </c>
       <c r="J207" t="n">
-        <v>33.1641</v>
+        <v>30.8367</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.26</v>
       </c>
       <c r="I208" t="n">
-        <v>0.727</v>
+        <v>0.7149</v>
       </c>
       <c r="J208" t="n">
-        <v>19.629</v>
+        <v>19.3023</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.19</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5481</v>
+        <v>0.5452</v>
       </c>
       <c r="J209" t="n">
-        <v>14.7987</v>
+        <v>14.7204</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.1615</v>
+        <v>-0.0902</v>
       </c>
       <c r="J210" t="n">
-        <v>-4.3605</v>
+        <v>-2.4354</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6924</v>
+        <v>-0.6363</v>
       </c>
       <c r="J211" t="n">
-        <v>-18.6948</v>
+        <v>-17.1801</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.34</v>
       </c>
       <c r="I212" t="n">
-        <v>0.55</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="J212" t="n">
-        <v>15.95</v>
+        <v>19.1922</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.16</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3004</v>
+        <v>0.347</v>
       </c>
       <c r="J213" t="n">
-        <v>8.711600000000001</v>
+        <v>10.063</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0491</v>
+        <v>0.083</v>
       </c>
       <c r="J214" t="n">
-        <v>1.4239</v>
+        <v>2.407</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.96</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.138</v>
+        <v>-0.0699</v>
       </c>
       <c r="J215" t="n">
-        <v>-4.002</v>
+        <v>-2.0271</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3398</v>
+        <v>-0.2058</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.854200000000001</v>
+        <v>-5.9682</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.41</v>
       </c>
       <c r="I217" t="n">
-        <v>1.1152</v>
+        <v>1.0639</v>
       </c>
       <c r="J217" t="n">
-        <v>32.3408</v>
+        <v>30.8531</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.02</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0553</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="J218" t="n">
-        <v>1.6037</v>
+        <v>2.4389</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.01</v>
       </c>
       <c r="I219" t="n">
-        <v>0.01</v>
+        <v>0.0437</v>
       </c>
       <c r="J219" t="n">
-        <v>0.29</v>
+        <v>1.2673</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.01</v>
       </c>
       <c r="I220" t="n">
-        <v>0.01</v>
+        <v>0.0437</v>
       </c>
       <c r="J220" t="n">
-        <v>0.29</v>
+        <v>1.2673</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6622</v>
+        <v>-0.6103</v>
       </c>
       <c r="J221" t="n">
-        <v>-19.2038</v>
+        <v>-17.6987</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.33</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5424</v>
+        <v>0.4631</v>
       </c>
       <c r="J222" t="n">
-        <v>14.1024</v>
+        <v>12.0406</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3516</v>
+        <v>0.289</v>
       </c>
       <c r="J223" t="n">
-        <v>9.1416</v>
+        <v>7.514</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.07</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1512</v>
+        <v>0.1241</v>
       </c>
       <c r="J224" t="n">
-        <v>3.9312</v>
+        <v>3.2266</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.88</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2748</v>
+        <v>-0.1617</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.1448</v>
+        <v>-4.2042</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.78</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4224</v>
+        <v>-0.2646</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.9824</v>
+        <v>-6.8796</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.54</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7884</v>
+        <v>0.7557</v>
       </c>
       <c r="J227" t="n">
-        <v>20.4984</v>
+        <v>19.6482</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0723</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J228" t="n">
-        <v>1.8798</v>
+        <v>2.1346</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.01</v>
       </c>
       <c r="I229" t="n">
-        <v>0.0009</v>
+        <v>0.022</v>
       </c>
       <c r="J229" t="n">
-        <v>0.0234</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.92</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2119</v>
+        <v>-0.1186</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.5094</v>
+        <v>-3.0836</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.383</v>
+        <v>-0.2362</v>
       </c>
       <c r="J231" t="n">
-        <v>-9.958</v>
+        <v>-6.1412</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.26</v>
       </c>
       <c r="I232" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.6938</v>
       </c>
       <c r="J232" t="n">
-        <v>13.1123</v>
+        <v>15.9574</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.71</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.426</v>
+        <v>-0.2925</v>
       </c>
       <c r="J233" t="n">
-        <v>-9.798</v>
+        <v>-6.7275</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.65</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.519</v>
+        <v>-0.3485</v>
       </c>
       <c r="J234" t="n">
-        <v>-11.937</v>
+        <v>-8.015499999999999</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.6</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5898</v>
+        <v>-0.3954</v>
       </c>
       <c r="J235" t="n">
-        <v>-13.5654</v>
+        <v>-9.094200000000001</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7592</v>
+        <v>-0.5165</v>
       </c>
       <c r="J236" t="n">
-        <v>-17.4616</v>
+        <v>-11.8795</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.5</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1551</v>
+        <v>1.1134</v>
       </c>
       <c r="J237" t="n">
-        <v>26.5673</v>
+        <v>25.6082</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9638</v>
+        <v>0.9918</v>
       </c>
       <c r="J238" t="n">
-        <v>22.1674</v>
+        <v>22.8114</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.31</v>
       </c>
       <c r="I239" t="n">
-        <v>0.7074</v>
+        <v>0.7896</v>
       </c>
       <c r="J239" t="n">
-        <v>16.2702</v>
+        <v>18.1608</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.31</v>
       </c>
       <c r="I240" t="n">
-        <v>0.7074</v>
+        <v>0.7896</v>
       </c>
       <c r="J240" t="n">
-        <v>16.2702</v>
+        <v>18.1608</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.16</v>
       </c>
       <c r="I241" t="n">
-        <v>0.3398</v>
+        <v>0.4325</v>
       </c>
       <c r="J241" t="n">
-        <v>7.8154</v>
+        <v>9.9475</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.83</v>
       </c>
       <c r="I242" t="n">
-        <v>1.8159</v>
+        <v>1.5378</v>
       </c>
       <c r="J242" t="n">
-        <v>47.2134</v>
+        <v>39.9828</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.31</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7917</v>
+        <v>0.806</v>
       </c>
       <c r="J243" t="n">
-        <v>20.5842</v>
+        <v>20.956</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4357</v>
+        <v>0.5048</v>
       </c>
       <c r="J244" t="n">
-        <v>11.3282</v>
+        <v>13.1248</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.98</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.237</v>
+        <v>-0.1546</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.162</v>
+        <v>-4.0196</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4875</v>
+        <v>-0.4133</v>
       </c>
       <c r="J246" t="n">
-        <v>-12.675</v>
+        <v>-10.7458</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0639</v>
+        <v>0.0287</v>
       </c>
       <c r="J247" t="n">
-        <v>1.6614</v>
+        <v>0.7462</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0038</v>
+        <v>-0.022</v>
       </c>
       <c r="J248" t="n">
-        <v>0.0988</v>
+        <v>-0.572</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.89</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1778</v>
+        <v>-0.1329</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.6228</v>
+        <v>-3.4554</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.3924</v>
+        <v>-0.2532</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.2024</v>
+        <v>-6.5832</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.73</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4507</v>
+        <v>-0.292</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.7182</v>
+        <v>-7.592</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.15</v>
       </c>
       <c r="I252" t="n">
-        <v>0.3047</v>
+        <v>0.2614</v>
       </c>
       <c r="J252" t="n">
-        <v>8.226900000000001</v>
+        <v>7.0578</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.06</v>
       </c>
       <c r="I253" t="n">
-        <v>0.15</v>
+        <v>0.1219</v>
       </c>
       <c r="J253" t="n">
-        <v>4.05</v>
+        <v>3.2913</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.99</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0474</v>
+        <v>-0.0215</v>
       </c>
       <c r="J254" t="n">
-        <v>-1.2798</v>
+        <v>-0.5805</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0977</v>
+        <v>-0.0511</v>
       </c>
       <c r="J255" t="n">
-        <v>-2.6379</v>
+        <v>-1.3797</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.89</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2484</v>
+        <v>-0.1466</v>
       </c>
       <c r="J256" t="n">
-        <v>-6.7068</v>
+        <v>-3.9582</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.56</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7984</v>
+        <v>0.7135</v>
       </c>
       <c r="J257" t="n">
-        <v>21.5568</v>
+        <v>19.2645</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.09</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1539</v>
+        <v>0.1484</v>
       </c>
       <c r="J258" t="n">
-        <v>4.1553</v>
+        <v>4.0068</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.0762</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="J259" t="n">
-        <v>2.0574</v>
+        <v>2.3868</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.98</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.106</v>
+        <v>-0.0461</v>
       </c>
       <c r="J260" t="n">
-        <v>-2.862</v>
+        <v>-1.2447</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3475</v>
+        <v>-0.2098</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.3825</v>
+        <v>-5.6646</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.96</v>
       </c>
       <c r="I262" t="n">
-        <v>1.8816</v>
+        <v>1.5981</v>
       </c>
       <c r="J262" t="n">
-        <v>35.7504</v>
+        <v>30.3639</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.8</v>
       </c>
       <c r="I263" t="n">
-        <v>1.6088</v>
+        <v>1.4223</v>
       </c>
       <c r="J263" t="n">
-        <v>30.5672</v>
+        <v>27.0237</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.5</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9938</v>
+        <v>1.085</v>
       </c>
       <c r="J264" t="n">
-        <v>18.8822</v>
+        <v>20.615</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.41</v>
       </c>
       <c r="I265" t="n">
-        <v>0.8106</v>
+        <v>0.954</v>
       </c>
       <c r="J265" t="n">
-        <v>15.4014</v>
+        <v>18.126</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.36</v>
       </c>
       <c r="I266" t="n">
-        <v>0.7075</v>
+        <v>0.8496</v>
       </c>
       <c r="J266" t="n">
-        <v>13.4425</v>
+        <v>16.1424</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.1</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4614</v>
+        <v>0.6017</v>
       </c>
       <c r="J267" t="n">
-        <v>8.7666</v>
+        <v>11.4323</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.64</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3798</v>
+        <v>-0.3136</v>
       </c>
       <c r="J268" t="n">
-        <v>-7.2162</v>
+        <v>-5.9584</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.45</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.7107</v>
+        <v>-0.4943</v>
       </c>
       <c r="J269" t="n">
-        <v>-13.5033</v>
+        <v>-9.3917</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.22</v>
       </c>
       <c r="I270" t="n">
-        <v>-1.0239</v>
+        <v>-0.7216</v>
       </c>
       <c r="J270" t="n">
-        <v>-19.4541</v>
+        <v>-13.7104</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.16</v>
       </c>
       <c r="I271" t="n">
-        <v>-1.0979</v>
+        <v>-0.7826</v>
       </c>
       <c r="J271" t="n">
-        <v>-20.8601</v>
+        <v>-14.8694</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>1.5699</v>
+        <v>1.3707</v>
       </c>
       <c r="J272" t="n">
-        <v>37.6776</v>
+        <v>32.8968</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.49</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1863</v>
+        <v>1.1212</v>
       </c>
       <c r="J273" t="n">
-        <v>28.4712</v>
+        <v>26.9088</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1926</v>
+        <v>0.2664</v>
       </c>
       <c r="J274" t="n">
-        <v>4.6224</v>
+        <v>6.3936</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.08</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1633</v>
+        <v>0.2371</v>
       </c>
       <c r="J275" t="n">
-        <v>3.9192</v>
+        <v>5.6904</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.7138</v>
+        <v>-0.6567</v>
       </c>
       <c r="J276" t="n">
-        <v>-17.1312</v>
+        <v>-15.7608</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.06</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2226</v>
+        <v>0.2157</v>
       </c>
       <c r="J277" t="n">
-        <v>5.3424</v>
+        <v>5.1768</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0814</v>
+        <v>0.0436</v>
       </c>
       <c r="J278" t="n">
-        <v>1.9536</v>
+        <v>1.0464</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.85</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.227</v>
+        <v>-0.1701</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.448</v>
+        <v>-4.0824</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.71</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.4662</v>
+        <v>-0.3055</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.1888</v>
+        <v>-7.332</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.54</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6913</v>
+        <v>-0.4648</v>
       </c>
       <c r="J281" t="n">
-        <v>-16.5912</v>
+        <v>-11.1552</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.11</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2509</v>
+        <v>0.2073</v>
       </c>
       <c r="J282" t="n">
-        <v>7.2761</v>
+        <v>6.0117</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.06</v>
       </c>
       <c r="I283" t="n">
-        <v>0.162</v>
+        <v>0.1265</v>
       </c>
       <c r="J283" t="n">
-        <v>4.698</v>
+        <v>3.6685</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.97</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0837</v>
+        <v>-0.0487</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.4273</v>
+        <v>-1.4123</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.89</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2397</v>
+        <v>-0.1435</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.9513</v>
+        <v>-4.1615</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.89</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2397</v>
+        <v>-0.1435</v>
       </c>
       <c r="J286" t="n">
-        <v>-6.9513</v>
+        <v>-4.1615</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.2</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3614</v>
+        <v>0.2993</v>
       </c>
       <c r="J287" t="n">
-        <v>10.4806</v>
+        <v>8.6797</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.2013</v>
+        <v>0.1658</v>
       </c>
       <c r="J288" t="n">
-        <v>5.8377</v>
+        <v>4.8082</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.09</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1829</v>
+        <v>0.1517</v>
       </c>
       <c r="J289" t="n">
-        <v>5.3041</v>
+        <v>4.3993</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.97</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1165</v>
+        <v>-0.0563</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.3785</v>
+        <v>-1.6327</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.96</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.1374</v>
+        <v>-0.0697</v>
       </c>
       <c r="J291" t="n">
-        <v>-3.9846</v>
+        <v>-2.0213</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.51</v>
       </c>
       <c r="I292" t="n">
-        <v>1.2372</v>
+        <v>1.1518</v>
       </c>
       <c r="J292" t="n">
-        <v>29.6928</v>
+        <v>27.6432</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.37</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9453</v>
+        <v>0.9468</v>
       </c>
       <c r="J293" t="n">
-        <v>22.6872</v>
+        <v>22.7232</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.455</v>
+        <v>0.5107</v>
       </c>
       <c r="J294" t="n">
-        <v>10.92</v>
+        <v>12.2568</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.05</v>
       </c>
       <c r="I295" t="n">
-        <v>0.0793</v>
+        <v>0.1498</v>
       </c>
       <c r="J295" t="n">
-        <v>1.9032</v>
+        <v>3.5952</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3631</v>
+        <v>-0.2852</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.714399999999999</v>
+        <v>-6.8448</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.05</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1916</v>
+        <v>0.1795</v>
       </c>
       <c r="J297" t="n">
-        <v>4.5984</v>
+        <v>4.308</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.03</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1509</v>
+        <v>0.1294</v>
       </c>
       <c r="J298" t="n">
-        <v>3.6216</v>
+        <v>3.1056</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0689</v>
+        <v>0.0327</v>
       </c>
       <c r="J299" t="n">
-        <v>1.6536</v>
+        <v>0.7848000000000001</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.73</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4471</v>
+        <v>-0.2904</v>
       </c>
       <c r="J300" t="n">
-        <v>-10.7304</v>
+        <v>-6.9696</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.7453</v>
+        <v>-0.5051</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.8872</v>
+        <v>-12.1224</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3985/event_3985_evp_summary.xlsx
+++ b/database/event/3985/event_3985_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6094</v>
+        <v>7.605</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9834</v>
+        <v>1.9823</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7973</v>
+        <v>2.8377</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6094</v>
+        <v>7.605</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8335</v>
+        <v>2.4779</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7759</v>
+        <v>5.1271</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8621</v>
+        <v>2.6984</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8621</v>
+        <v>2.6984</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7759</v>
+        <v>5.1271</v>
       </c>
       <c r="K2" t="n">
         <v>127</v>
@@ -529,7 +529,7 @@
         <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>7.638</v>
+        <v>7.8255</v>
       </c>
       <c r="N2" t="n">
         <v>278</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9498</v>
+        <v>7.1733</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8115</v>
+        <v>1.8698</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4995</v>
+        <v>2.6412</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9498</v>
+        <v>7.1733</v>
       </c>
       <c r="F3" t="n">
-        <v>4.4518</v>
+        <v>4.5807</v>
       </c>
       <c r="G3" t="n">
-        <v>2.498</v>
+        <v>2.5926</v>
       </c>
       <c r="H3" t="n">
-        <v>10.8107</v>
+        <v>10.2892</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6211</v>
+        <v>5.5561</v>
       </c>
       <c r="J3" t="n">
-        <v>2.498</v>
+        <v>2.5926</v>
       </c>
       <c r="K3" t="n">
         <v>122</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1191</v>
+        <v>8.1487</v>
       </c>
       <c r="N3" t="n">
         <v>224</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0106</v>
+        <v>3.9889</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0454</v>
+        <v>1.0397</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1726</v>
+        <v>1.1916</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0106</v>
+        <v>3.9889</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7276</v>
+        <v>3.7103</v>
       </c>
       <c r="G4" t="n">
-        <v>0.283</v>
+        <v>0.2786</v>
       </c>
       <c r="H4" t="n">
-        <v>7.6474</v>
+        <v>7.3473</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9763</v>
+        <v>3.9675</v>
       </c>
       <c r="J4" t="n">
-        <v>0.283</v>
+        <v>0.2786</v>
       </c>
       <c r="K4" t="n">
         <v>87</v>
@@ -621,7 +621,7 @@
         <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.259300000000001</v>
+        <v>4.2461</v>
       </c>
       <c r="N4" t="n">
         <v>140</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7038</v>
+        <v>3.9798</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9654</v>
+        <v>1.0374</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0341</v>
+        <v>1.1875</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7038</v>
+        <v>3.9798</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4544</v>
+        <v>0.4074</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2494</v>
+        <v>3.5724</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4544</v>
+        <v>0.4074</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4544</v>
+        <v>0.4074</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2494</v>
+        <v>3.5724</v>
       </c>
       <c r="K5" t="n">
         <v>127</v>
@@ -667,7 +667,7 @@
         <v>151</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7038</v>
+        <v>3.9798</v>
       </c>
       <c r="N5" t="n">
         <v>278</v>
@@ -676,81 +676,81 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5738</v>
+        <v>3.4861</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9315</v>
+        <v>0.9087</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9754</v>
+        <v>0.9627</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5738</v>
+        <v>3.4861</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9546</v>
+        <v>3.6178</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6192</v>
+        <v>-0.1317</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1281</v>
+        <v>7.0423</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2567</v>
+        <v>3.8028</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6192</v>
+        <v>-0.1317</v>
       </c>
       <c r="K6" t="n">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="L6" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8759</v>
+        <v>3.6711</v>
       </c>
       <c r="N6" t="n">
-        <v>201</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5462</v>
+        <v>3.3753</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9243</v>
+        <v>0.8798</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9629</v>
+        <v>0.9123</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5462</v>
+        <v>3.3753</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6638</v>
+        <v>3.4339</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1176</v>
+        <v>-0.0586</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4228</v>
+        <v>6.4355</v>
       </c>
       <c r="I7" t="n">
-        <v>3.8595</v>
+        <v>3.4751</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1176</v>
+        <v>-0.0586</v>
       </c>
       <c r="K7" t="n">
         <v>87</v>
@@ -759,7 +759,7 @@
         <v>53</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7419</v>
+        <v>3.4165</v>
       </c>
       <c r="N7" t="n">
         <v>140</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4303</v>
+        <v>3.307</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8941</v>
+        <v>0.862</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9106</v>
+        <v>0.8812</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4303</v>
+        <v>3.307</v>
       </c>
       <c r="F8" t="n">
-        <v>3.482</v>
+        <v>2.6278</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0517</v>
+        <v>0.6792</v>
       </c>
       <c r="H8" t="n">
-        <v>6.7821</v>
+        <v>3.0265</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5264</v>
+        <v>3.1045</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0517</v>
+        <v>0.6792</v>
       </c>
       <c r="K8" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4747</v>
+        <v>3.7837</v>
       </c>
       <c r="N8" t="n">
-        <v>140</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.3507</v>
+        <v>3.2823</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8734</v>
+        <v>0.8555</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8747</v>
+        <v>0.87</v>
       </c>
       <c r="E9" t="n">
-        <v>3.3507</v>
+        <v>3.2823</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6831</v>
+        <v>3.6189</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3324</v>
+        <v>-0.3366</v>
       </c>
       <c r="H9" t="n">
-        <v>7.4905</v>
+        <v>7.0458</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8947</v>
+        <v>3.8047</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3324</v>
+        <v>-0.3366</v>
       </c>
       <c r="K9" t="n">
         <v>122</v>
@@ -851,7 +851,7 @@
         <v>102</v>
       </c>
       <c r="M9" t="n">
-        <v>3.5623</v>
+        <v>3.4681</v>
       </c>
       <c r="N9" t="n">
         <v>224</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1383</v>
+        <v>3.1137</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8116</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7788</v>
+        <v>0.7932</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1383</v>
+        <v>3.1137</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7936</v>
+        <v>2.7647</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3447</v>
+        <v>0.349</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3565</v>
+        <v>4.2275</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2652</v>
+        <v>2.2828</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3447</v>
+        <v>0.349</v>
       </c>
       <c r="K10" t="n">
         <v>87</v>
@@ -897,7 +897,7 @@
         <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6099</v>
+        <v>2.6318</v>
       </c>
       <c r="N10" t="n">
         <v>140</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8343</v>
+        <v>2.9935</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7388</v>
+        <v>0.7803</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6415</v>
+        <v>0.7385</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8343</v>
+        <v>2.9935</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7889</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0454</v>
+        <v>2.2249</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7889</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7889</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0454</v>
+        <v>2.2249</v>
       </c>
       <c r="K11" t="n">
         <v>127</v>
@@ -943,7 +943,7 @@
         <v>106</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8343</v>
+        <v>2.9935</v>
       </c>
       <c r="N11" t="n">
         <v>233</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5611</v>
+        <v>2.664</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6676</v>
+        <v>0.6944</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5182</v>
+        <v>0.5885</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5611</v>
+        <v>2.664</v>
       </c>
       <c r="F12" t="n">
-        <v>3.088</v>
+        <v>1.024</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5269</v>
+        <v>1.64</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3937</v>
+        <v>1.024</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8045</v>
+        <v>1.024</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5269</v>
+        <v>1.64</v>
       </c>
       <c r="K12" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="L12" t="n">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="M12" t="n">
-        <v>2.2776</v>
+        <v>2.664</v>
       </c>
       <c r="N12" t="n">
-        <v>140</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.453</v>
+        <v>2.472</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6394</v>
+        <v>0.6443</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4694</v>
+        <v>0.5011</v>
       </c>
       <c r="E13" t="n">
-        <v>2.453</v>
+        <v>2.472</v>
       </c>
       <c r="F13" t="n">
-        <v>1.071</v>
+        <v>3.0237</v>
       </c>
       <c r="G13" t="n">
-        <v>1.382</v>
+        <v>-0.5517</v>
       </c>
       <c r="H13" t="n">
-        <v>1.071</v>
+        <v>5.0821</v>
       </c>
       <c r="I13" t="n">
-        <v>1.071</v>
+        <v>2.7443</v>
       </c>
       <c r="J13" t="n">
-        <v>1.382</v>
+        <v>-0.5517</v>
       </c>
       <c r="K13" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="L13" t="n">
-        <v>151</v>
+        <v>53</v>
       </c>
       <c r="M13" t="n">
-        <v>2.453</v>
+        <v>2.1926</v>
       </c>
       <c r="N13" t="n">
-        <v>278</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3579</v>
+        <v>2.3195</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6146</v>
+        <v>0.6046</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4265</v>
+        <v>0.4317</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3579</v>
+        <v>2.3195</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5183</v>
+        <v>2.4428</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1604</v>
+        <v>-0.1233</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3866</v>
+        <v>3.1654</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7609</v>
+        <v>1.7093</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1604</v>
+        <v>-0.1233</v>
       </c>
       <c r="K14" t="n">
         <v>122</v>
@@ -1081,7 +1081,7 @@
         <v>102</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6005</v>
+        <v>1.586</v>
       </c>
       <c r="N14" t="n">
         <v>224</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2169</v>
+        <v>2.2492</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5778</v>
+        <v>0.5863</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3628</v>
+        <v>0.3997</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2169</v>
+        <v>2.2492</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1741</v>
+        <v>1.1132</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0428</v>
+        <v>1.136</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1741</v>
+        <v>1.1132</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1741</v>
+        <v>1.1132</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0428</v>
+        <v>1.136</v>
       </c>
       <c r="K15" t="n">
         <v>127</v>
@@ -1127,7 +1127,7 @@
         <v>106</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2169</v>
+        <v>2.2492</v>
       </c>
       <c r="N15" t="n">
         <v>233</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0583</v>
+        <v>1.9955</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5365</v>
+        <v>0.5201</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2912</v>
+        <v>0.2842</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0583</v>
+        <v>1.9955</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2356</v>
+        <v>2.2014</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1773</v>
+        <v>-0.2059</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2356</v>
+        <v>2.2014</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3275</v>
+        <v>2.2581</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1773</v>
+        <v>-0.2059</v>
       </c>
       <c r="K16" t="n">
         <v>134</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1502</v>
+        <v>2.0522</v>
       </c>
       <c r="N16" t="n">
         <v>185</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8204</v>
+        <v>1.8525</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4745</v>
+        <v>0.4829</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1838</v>
+        <v>0.2191</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8204</v>
+        <v>1.8525</v>
       </c>
       <c r="F17" t="n">
-        <v>2.7737</v>
+        <v>2.721</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9533</v>
+        <v>-0.8685</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2863</v>
+        <v>4.0834</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2287</v>
+        <v>2.205</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9533</v>
+        <v>-0.8685</v>
       </c>
       <c r="K17" t="n">
         <v>122</v>
@@ -1219,7 +1219,7 @@
         <v>102</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2754</v>
+        <v>1.3365</v>
       </c>
       <c r="N17" t="n">
         <v>224</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4399</v>
+        <v>1.413</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3753</v>
+        <v>0.3683</v>
       </c>
       <c r="D18" t="n">
-        <v>0.012</v>
+        <v>0.019</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4399</v>
+        <v>1.413</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3367</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1032</v>
+        <v>1.9831</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3367</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3917</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1032</v>
+        <v>1.9831</v>
       </c>
       <c r="K18" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="L18" t="n">
-        <v>51</v>
+        <v>151</v>
       </c>
       <c r="M18" t="n">
-        <v>1.4949</v>
+        <v>1.413</v>
       </c>
       <c r="N18" t="n">
-        <v>201</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3443</v>
+        <v>1.3349</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3504</v>
+        <v>0.3479</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0311</v>
+        <v>-0.0165</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3443</v>
+        <v>1.3349</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3315</v>
+        <v>0.24</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0128</v>
+        <v>1.0949</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3315</v>
+        <v>0.24</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3315</v>
+        <v>0.24</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0128</v>
+        <v>1.0949</v>
       </c>
       <c r="K19" t="n">
         <v>127</v>
@@ -1311,7 +1311,7 @@
         <v>106</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3443</v>
+        <v>1.3349</v>
       </c>
       <c r="N19" t="n">
         <v>233</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.192</v>
+        <v>1.2851</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3107</v>
+        <v>0.335</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0999</v>
+        <v>-0.0392</v>
       </c>
       <c r="E20" t="n">
-        <v>1.192</v>
+        <v>1.2851</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5627</v>
+        <v>1.1957</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7547</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5627</v>
+        <v>1.1957</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5627</v>
+        <v>1.2265</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7547</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="L20" t="n">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>1.192</v>
+        <v>1.3159</v>
       </c>
       <c r="N20" t="n">
-        <v>278</v>
+        <v>201</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0452</v>
+        <v>1.2205</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2724</v>
+        <v>0.3181</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1662</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0452</v>
+        <v>1.2205</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2368</v>
+        <v>-0.2474</v>
       </c>
       <c r="G21" t="n">
-        <v>1.282</v>
+        <v>1.4679</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2368</v>
+        <v>-0.2474</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2368</v>
+        <v>-0.2474</v>
       </c>
       <c r="J21" t="n">
-        <v>1.282</v>
+        <v>1.4679</v>
       </c>
       <c r="K21" t="n">
         <v>127</v>
@@ -1403,7 +1403,7 @@
         <v>151</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0452</v>
+        <v>1.2205</v>
       </c>
       <c r="N21" t="n">
         <v>278</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8403</v>
+        <v>0.8446</v>
       </c>
       <c r="C22" t="n">
-        <v>0.219</v>
+        <v>0.2201</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2587</v>
+        <v>-0.2397</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8403</v>
+        <v>0.8446</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8403</v>
+        <v>0.8446</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8403</v>
+        <v>0.8446</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8403</v>
+        <v>0.8446</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8403</v>
+        <v>0.8446</v>
       </c>
       <c r="N22" t="n">
         <v>155</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7105</v>
+        <v>0.6625</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1852</v>
+        <v>0.1727</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3173</v>
+        <v>-0.3226</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7105</v>
+        <v>0.6625</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2775</v>
+        <v>1.2569</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5944</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2775</v>
+        <v>1.2569</v>
       </c>
       <c r="I23" t="n">
-        <v>1.33</v>
+        <v>1.2893</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5669999999999999</v>
+        <v>-0.5944</v>
       </c>
       <c r="K23" t="n">
         <v>134</v>
@@ -1495,7 +1495,7 @@
         <v>51</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7630000000000001</v>
+        <v>0.6948999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>185</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4313</v>
+        <v>0.5544</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1124</v>
+        <v>0.1445</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4433</v>
+        <v>-0.3718</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4313</v>
+        <v>0.5544</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2291</v>
+        <v>1.2582</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7978</v>
+        <v>-0.7038</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2291</v>
+        <v>1.2582</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6391</v>
+        <v>0.6794</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7978</v>
+        <v>-0.7038</v>
       </c>
       <c r="K24" t="n">
         <v>122</v>
@@ -1541,7 +1541,7 @@
         <v>102</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1587</v>
+        <v>-0.02439999999999998</v>
       </c>
       <c r="N24" t="n">
         <v>224</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2918</v>
+        <v>0.2749</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0761</v>
+        <v>0.0717</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5063</v>
+        <v>-0.4991</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2918</v>
+        <v>0.2749</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8565</v>
+        <v>0.8726</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5647</v>
+        <v>-0.5977</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8565</v>
+        <v>0.8726</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8917</v>
+        <v>0.8951</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5647</v>
+        <v>-0.5977</v>
       </c>
       <c r="K25" t="n">
         <v>134</v>
@@ -1587,7 +1587,7 @@
         <v>51</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3270000000000001</v>
+        <v>0.2974</v>
       </c>
       <c r="N25" t="n">
         <v>185</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2565</v>
+        <v>0.237</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0669</v>
+        <v>0.0618</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5222</v>
+        <v>-0.5163</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2565</v>
+        <v>0.237</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7664</v>
+        <v>0.7657</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5099</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7664</v>
+        <v>0.7657</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.7854</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5099</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="K26" t="n">
         <v>134</v>
@@ -1633,7 +1633,7 @@
         <v>51</v>
       </c>
       <c r="M26" t="n">
-        <v>0.288</v>
+        <v>0.2567</v>
       </c>
       <c r="N26" t="n">
         <v>185</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2152</v>
+        <v>0.1742</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0561</v>
+        <v>0.0454</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5409</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2152</v>
+        <v>0.1742</v>
       </c>
       <c r="F27" t="n">
-        <v>0.304</v>
+        <v>0.2719</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0888</v>
+        <v>-0.0977</v>
       </c>
       <c r="H27" t="n">
-        <v>0.304</v>
+        <v>0.2719</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3165</v>
+        <v>0.2789</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0888</v>
+        <v>-0.0977</v>
       </c>
       <c r="K27" t="n">
         <v>150</v>
@@ -1679,7 +1679,7 @@
         <v>51</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2277</v>
+        <v>0.1812</v>
       </c>
       <c r="N27" t="n">
         <v>201</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0238</v>
+        <v>-0.0115</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0062</v>
+        <v>-0.003</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6273</v>
+        <v>-0.6294</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0238</v>
+        <v>-0.0115</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0238</v>
+        <v>-0.0115</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0238</v>
+        <v>-0.0115</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0238</v>
+        <v>-0.0115</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0238</v>
+        <v>-0.0115</v>
       </c>
       <c r="N28" t="n">
         <v>155</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0776</v>
+        <v>-0.0365</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0202</v>
+        <v>-0.0095</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.673</v>
+        <v>-0.6408</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0776</v>
+        <v>-0.0365</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4433</v>
+        <v>-0.4246</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3657</v>
+        <v>0.3881</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4433</v>
+        <v>-0.4246</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4615</v>
+        <v>-0.4355</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3657</v>
+        <v>0.3881</v>
       </c>
       <c r="K29" t="n">
         <v>134</v>
@@ -1771,7 +1771,7 @@
         <v>51</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0958</v>
+        <v>-0.0474</v>
       </c>
       <c r="N29" t="n">
         <v>185</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1607</v>
+        <v>-0.1933</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0419</v>
+        <v>-0.0504</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7106</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1607</v>
+        <v>-0.1933</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1607</v>
+        <v>-0.1933</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1607</v>
+        <v>-0.1933</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1607</v>
+        <v>-0.1933</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1607</v>
+        <v>-0.1933</v>
       </c>
       <c r="N30" t="n">
         <v>155</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2175</v>
+        <v>-0.3026</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0567</v>
+        <v>-0.0789</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7362</v>
+        <v>-0.762</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2175</v>
+        <v>-0.3026</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2175</v>
+        <v>-0.3026</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2175</v>
+        <v>-0.3026</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2175</v>
+        <v>-0.3026</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2175</v>
+        <v>-0.3026</v>
       </c>
       <c r="N31" t="n">
         <v>94</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>KrizzeN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4133</v>
+        <v>-0.4628</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1077</v>
+        <v>-0.1206</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8246</v>
+        <v>-0.8349</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4133</v>
+        <v>-0.4628</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4133</v>
+        <v>0.2018</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.6646</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4133</v>
+        <v>0.2018</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4133</v>
+        <v>0.2018</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.6646</v>
       </c>
       <c r="K32" t="n">
-        <v>155</v>
+        <v>127</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4133</v>
+        <v>-0.4628</v>
       </c>
       <c r="N32" t="n">
-        <v>155</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KrizzeN</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4815</v>
+        <v>-0.4717</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1255</v>
+        <v>-0.123</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8554</v>
+        <v>-0.8389</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4815</v>
+        <v>-0.4717</v>
       </c>
       <c r="F33" t="n">
-        <v>0.303</v>
+        <v>-0.4717</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.7845</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.303</v>
+        <v>-0.4717</v>
       </c>
       <c r="I33" t="n">
-        <v>0.303</v>
+        <v>-0.4717</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7845</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="L33" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4815</v>
+        <v>-0.4717</v>
       </c>
       <c r="N33" t="n">
-        <v>233</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4878</v>
+        <v>-0.5405</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1271</v>
+        <v>-0.1409</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8582</v>
+        <v>-0.8702</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4878</v>
+        <v>-0.5405</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4878</v>
+        <v>-0.5405</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4878</v>
+        <v>-0.5405</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4878</v>
+        <v>-0.5405</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4878</v>
+        <v>-0.5405</v>
       </c>
       <c r="N34" t="n">
         <v>155</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7045</v>
+        <v>-0.784</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1836</v>
+        <v>-0.2044</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9560999999999999</v>
+        <v>-0.9811</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7045</v>
+        <v>-0.784</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7045</v>
+        <v>-0.784</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7045</v>
+        <v>-0.784</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7045</v>
+        <v>-0.784</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7045</v>
+        <v>-0.784</v>
       </c>
       <c r="N35" t="n">
         <v>94</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>Zellsis</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.747</v>
+        <v>-0.8155</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1947</v>
+        <v>-0.2126</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9752</v>
+        <v>-0.9954</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.747</v>
+        <v>-0.8155</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.747</v>
+        <v>-0.8155</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.747</v>
+        <v>-0.8155</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.747</v>
+        <v>-0.8155</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.747</v>
+        <v>-0.8155</v>
       </c>
       <c r="N36" t="n">
         <v>94</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zellsis</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2006</v>
+        <v>-0.2153</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9855</v>
+        <v>-1.0003</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>94</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9821</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2505</v>
+        <v>-0.256</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0719</v>
+        <v>-1.0713</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9821</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9821</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9821</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9821</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9821</v>
       </c>
       <c r="N38" t="n">
         <v>94</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1463</v>
+        <v>-1.1777</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2988</v>
+        <v>-0.307</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1555</v>
+        <v>-1.1603</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1463</v>
+        <v>-1.1777</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7094</v>
+        <v>-0.7091</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4369</v>
+        <v>-0.4686</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7094</v>
+        <v>-0.7091</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7386</v>
+        <v>-0.7274</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4369</v>
+        <v>-0.4686</v>
       </c>
       <c r="K39" t="n">
         <v>150</v>
@@ -2231,7 +2231,7 @@
         <v>51</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1755</v>
+        <v>-1.196</v>
       </c>
       <c r="N39" t="n">
         <v>201</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3623</v>
+        <v>-1.3865</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3551</v>
+        <v>-0.3614</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.253</v>
+        <v>-1.2554</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3623</v>
+        <v>-1.3865</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.6203</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.742</v>
+        <v>-0.767</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6203</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6458</v>
+        <v>-0.6355</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.742</v>
+        <v>-0.767</v>
       </c>
       <c r="K40" t="n">
         <v>150</v>
@@ -2277,7 +2277,7 @@
         <v>51</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3878</v>
+        <v>-1.4025</v>
       </c>
       <c r="N40" t="n">
         <v>201</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.965</v>
+        <v>-1.8802</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5122</v>
+        <v>-0.4901</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5251</v>
+        <v>-1.4801</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.965</v>
+        <v>-1.8802</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2516</v>
+        <v>-1.2758</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.7134</v>
+        <v>-0.6044</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2516</v>
+        <v>-1.2758</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2516</v>
+        <v>-1.2758</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.7134</v>
+        <v>-0.6044</v>
       </c>
       <c r="K41" t="n">
         <v>127</v>
@@ -2323,7 +2323,7 @@
         <v>106</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.965</v>
+        <v>-1.8802</v>
       </c>
       <c r="N41" t="n">
         <v>233</v>
@@ -2429,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9133</v>
+        <v>0.8645</v>
       </c>
       <c r="J2" t="n">
-        <v>25.5724</v>
+        <v>24.206</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0008</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0224</v>
+        <v>-0.0168</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1358</v>
+        <v>-0.1481</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.8024</v>
+        <v>-4.1468</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.9</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1358</v>
+        <v>-0.1481</v>
       </c>
       <c r="J5" t="n">
-        <v>-3.8024</v>
+        <v>-4.1468</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2506</v>
+        <v>-0.2636</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.0168</v>
+        <v>-7.3808</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.25</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7279</v>
+        <v>0.6854</v>
       </c>
       <c r="J7" t="n">
-        <v>20.3812</v>
+        <v>19.1912</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4979</v>
+        <v>0.4809</v>
       </c>
       <c r="J8" t="n">
-        <v>13.9412</v>
+        <v>13.4652</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4175</v>
+        <v>0.4082</v>
       </c>
       <c r="J9" t="n">
-        <v>11.69</v>
+        <v>11.4296</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.86</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4747</v>
+        <v>-0.4537</v>
       </c>
       <c r="J10" t="n">
-        <v>-13.2916</v>
+        <v>-12.7036</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.83</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5558</v>
+        <v>-0.5266</v>
       </c>
       <c r="J11" t="n">
-        <v>-15.5624</v>
+        <v>-14.7448</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.68</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2792</v>
+        <v>-0.307</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.3048</v>
+        <v>-5.833</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.3995</v>
+        <v>-0.4203</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.5905</v>
+        <v>-7.9857</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.54</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4172</v>
+        <v>-0.4371</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.9268</v>
+        <v>-8.3049</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.49</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4615</v>
+        <v>-0.4789</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.7685</v>
+        <v>-9.0991</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.41</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5376</v>
+        <v>-0.5494</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.2144</v>
+        <v>-10.4386</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.84</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4735</v>
+        <v>1.6094</v>
       </c>
       <c r="J17" t="n">
-        <v>27.9965</v>
+        <v>30.5786</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.82</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4512</v>
+        <v>1.584</v>
       </c>
       <c r="J18" t="n">
-        <v>27.5728</v>
+        <v>30.096</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.74</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3616</v>
+        <v>1.4718</v>
       </c>
       <c r="J19" t="n">
-        <v>25.8704</v>
+        <v>27.9642</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.35</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8363</v>
+        <v>0.8037</v>
       </c>
       <c r="J20" t="n">
-        <v>15.8897</v>
+        <v>15.2703</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.05</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0741</v>
+        <v>0.1147</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4079</v>
+        <v>2.1793</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3365</v>
+        <v>0.3437</v>
       </c>
       <c r="J22" t="n">
-        <v>8.4125</v>
+        <v>8.592499999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2835</v>
+        <v>0.2887</v>
       </c>
       <c r="J23" t="n">
-        <v>7.0875</v>
+        <v>7.2175</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1139</v>
+        <v>0.1231</v>
       </c>
       <c r="J24" t="n">
-        <v>2.8475</v>
+        <v>3.0775</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.89</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1466</v>
+        <v>-0.1593</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.665</v>
+        <v>-3.9825</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1788</v>
+        <v>-0.192</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.47</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5876</v>
+        <v>0.6466</v>
       </c>
       <c r="J27" t="n">
-        <v>14.69</v>
+        <v>16.165</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.15</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4094</v>
+        <v>0.4459</v>
       </c>
       <c r="J28" t="n">
-        <v>10.235</v>
+        <v>11.1475</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1494</v>
+        <v>0.1587</v>
       </c>
       <c r="J29" t="n">
-        <v>3.735</v>
+        <v>3.9675</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0711</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.785</v>
+        <v>-1.7775</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.93</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.281</v>
+        <v>-0.2741</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.025</v>
+        <v>-6.8525</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.01</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0612</v>
+        <v>0.0603</v>
       </c>
       <c r="J32" t="n">
-        <v>1.7136</v>
+        <v>1.6884</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0612</v>
+        <v>0.0603</v>
       </c>
       <c r="J33" t="n">
-        <v>1.7136</v>
+        <v>1.6884</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.0535</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.498</v>
+        <v>-1.8228</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.86</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1656</v>
+        <v>-0.1817</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.6368</v>
+        <v>-5.0876</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.64</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3803</v>
+        <v>-0.3924</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.6484</v>
+        <v>-10.9872</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.56</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9359</v>
+        <v>1.0314</v>
       </c>
       <c r="J37" t="n">
-        <v>26.2052</v>
+        <v>28.8792</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.37</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6926</v>
+        <v>0.7688</v>
       </c>
       <c r="J38" t="n">
-        <v>19.3928</v>
+        <v>21.5264</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5461</v>
+        <v>0.6071</v>
       </c>
       <c r="J39" t="n">
-        <v>15.2908</v>
+        <v>16.9988</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.03</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0766</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>2.1448</v>
+        <v>2.7608</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2906</v>
+        <v>-0.2733</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.136799999999999</v>
+        <v>-7.6524</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6663</v>
+        <v>0.74</v>
       </c>
       <c r="J42" t="n">
-        <v>17.9901</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.34</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6531</v>
+        <v>0.7255</v>
       </c>
       <c r="J43" t="n">
-        <v>17.6337</v>
+        <v>19.5885</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4785</v>
+        <v>0.5309</v>
       </c>
       <c r="J44" t="n">
-        <v>12.9195</v>
+        <v>14.3343</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.2</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4644</v>
+        <v>0.515</v>
       </c>
       <c r="J45" t="n">
-        <v>12.5388</v>
+        <v>13.905</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.06</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1763</v>
+        <v>0.1943</v>
       </c>
       <c r="J46" t="n">
-        <v>4.7601</v>
+        <v>5.2461</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3952</v>
+        <v>0.4175</v>
       </c>
       <c r="J47" t="n">
-        <v>10.6704</v>
+        <v>11.2725</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.02</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1187</v>
+        <v>0.1116</v>
       </c>
       <c r="J48" t="n">
-        <v>3.2049</v>
+        <v>3.0132</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.77</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2462</v>
+        <v>-0.2643</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.6474</v>
+        <v>-7.1361</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.58</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4262</v>
+        <v>-0.4378</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.5074</v>
+        <v>-11.8206</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4355</v>
+        <v>-0.4467</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.7585</v>
+        <v>-12.0609</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1977</v>
+        <v>1.2963</v>
       </c>
       <c r="J52" t="n">
-        <v>33.5356</v>
+        <v>36.2964</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0886</v>
+        <v>0.0961</v>
       </c>
       <c r="J53" t="n">
-        <v>2.4808</v>
+        <v>2.6908</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.98</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1005</v>
+        <v>-0.1042</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.814</v>
+        <v>-2.9176</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.7831</v>
+        <v>-0.7286</v>
       </c>
       <c r="J55" t="n">
-        <v>-21.9268</v>
+        <v>-20.4008</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8824</v>
+        <v>-0.8151</v>
       </c>
       <c r="J56" t="n">
-        <v>-24.7072</v>
+        <v>-22.8228</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.3765</v>
+        <v>0.4024</v>
       </c>
       <c r="J57" t="n">
-        <v>10.542</v>
+        <v>11.2672</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.08</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2083</v>
+        <v>0.2148</v>
       </c>
       <c r="J58" t="n">
-        <v>5.8324</v>
+        <v>6.0144</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1102</v>
+        <v>-0.1225</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.0856</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.88</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1545</v>
+        <v>-0.1681</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.326</v>
+        <v>-4.7068</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1653</v>
+        <v>-0.1789</v>
       </c>
       <c r="J61" t="n">
-        <v>-4.6284</v>
+        <v>-5.0092</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.98</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0175</v>
+        <v>-0.0285</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.42</v>
+        <v>-0.6840000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0175</v>
+        <v>-0.0285</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.42</v>
+        <v>-0.6840000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0994</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.0184</v>
+        <v>-2.3856</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2401</v>
+        <v>-0.2574</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.7624</v>
+        <v>-6.1776</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.57</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4392</v>
+        <v>-0.4496</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.5408</v>
+        <v>-10.7904</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.94</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3859</v>
+        <v>1.5073</v>
       </c>
       <c r="J67" t="n">
-        <v>33.2616</v>
+        <v>36.1752</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.57</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9403</v>
+        <v>1.0376</v>
       </c>
       <c r="J68" t="n">
-        <v>22.5672</v>
+        <v>24.9024</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.11</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3143</v>
+        <v>0.3253</v>
       </c>
       <c r="J69" t="n">
-        <v>7.5432</v>
+        <v>7.8072</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4763</v>
+        <v>-0.4434</v>
       </c>
       <c r="J70" t="n">
-        <v>-11.4312</v>
+        <v>-10.6416</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.83</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.612</v>
+        <v>-0.5662</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.688</v>
+        <v>-13.5888</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.21</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4498</v>
+        <v>0.4875</v>
       </c>
       <c r="J72" t="n">
-        <v>12.1446</v>
+        <v>13.1625</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.89</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1278</v>
+        <v>-0.1448</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.4506</v>
+        <v>-3.9096</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.86</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1598</v>
+        <v>-0.1774</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.3146</v>
+        <v>-4.7898</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3246</v>
+        <v>-0.3403</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.764200000000001</v>
+        <v>-9.1881</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.51</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4924</v>
+        <v>-0.5002</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.2948</v>
+        <v>-13.5054</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.7</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0928</v>
+        <v>1.2009</v>
       </c>
       <c r="J77" t="n">
-        <v>29.5056</v>
+        <v>32.4243</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.44</v>
       </c>
       <c r="I78" t="n">
-        <v>0.7724</v>
+        <v>0.8579</v>
       </c>
       <c r="J78" t="n">
-        <v>20.8548</v>
+        <v>23.1633</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.3</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5931</v>
+        <v>0.6611</v>
       </c>
       <c r="J79" t="n">
-        <v>16.0137</v>
+        <v>17.8497</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.09</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2522</v>
+        <v>0.2687</v>
       </c>
       <c r="J80" t="n">
-        <v>6.8094</v>
+        <v>7.2549</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.336</v>
+        <v>-0.3126</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.071999999999999</v>
+        <v>-8.440200000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6531</v>
+        <v>0.7291</v>
       </c>
       <c r="J82" t="n">
-        <v>16.9806</v>
+        <v>18.9566</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.14</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3178</v>
+        <v>0.323</v>
       </c>
       <c r="J83" t="n">
-        <v>8.2628</v>
+        <v>8.398</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.09</v>
       </c>
       <c r="I84" t="n">
-        <v>0.22</v>
+        <v>0.2285</v>
       </c>
       <c r="J84" t="n">
-        <v>5.72</v>
+        <v>5.941</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.252</v>
+        <v>-0.2646</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.552</v>
+        <v>-6.8796</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.65</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3859</v>
+        <v>-0.3952</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.0334</v>
+        <v>-10.2752</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.42</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7994</v>
+        <v>0.8764</v>
       </c>
       <c r="J87" t="n">
-        <v>20.7844</v>
+        <v>22.7864</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6471</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>16.8246</v>
+        <v>18.4912</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.16</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4267</v>
+        <v>0.4663</v>
       </c>
       <c r="J89" t="n">
-        <v>11.0942</v>
+        <v>12.1238</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.74</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.7932</v>
+        <v>-0.7357</v>
       </c>
       <c r="J90" t="n">
-        <v>-20.6232</v>
+        <v>-19.1282</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.7</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8922</v>
+        <v>-0.8221000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>-23.1972</v>
+        <v>-21.3746</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.96</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0339</v>
+        <v>-0.0499</v>
       </c>
       <c r="J92" t="n">
-        <v>-0.8475</v>
+        <v>-1.2475</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.83</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.1849</v>
+        <v>-0.204</v>
       </c>
       <c r="J93" t="n">
-        <v>-4.6225</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2146</v>
+        <v>-0.2336</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.365</v>
+        <v>-5.84</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.7</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3088</v>
+        <v>-0.3262</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.72</v>
+        <v>-8.154999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3561</v>
+        <v>-0.3718</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.9025</v>
+        <v>-9.295</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.847</v>
+        <v>0.9387</v>
       </c>
       <c r="J97" t="n">
-        <v>21.175</v>
+        <v>23.4675</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.36</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6698</v>
+        <v>0.7461</v>
       </c>
       <c r="J98" t="n">
-        <v>16.745</v>
+        <v>18.6525</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.34</v>
       </c>
       <c r="I99" t="n">
-        <v>0.6441</v>
+        <v>0.7178</v>
       </c>
       <c r="J99" t="n">
-        <v>16.1025</v>
+        <v>17.945</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4423</v>
+        <v>0.4921</v>
       </c>
       <c r="J100" t="n">
-        <v>11.0575</v>
+        <v>12.3025</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.09</v>
       </c>
       <c r="I101" t="n">
-        <v>0.2513</v>
+        <v>0.268</v>
       </c>
       <c r="J101" t="n">
-        <v>6.2825</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.89</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.1133</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.8354</v>
+        <v>-2.3793</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.68</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3108</v>
+        <v>-0.3316</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.5268</v>
+        <v>-6.9636</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.68</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3108</v>
+        <v>-0.3316</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.5268</v>
+        <v>-6.9636</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3734</v>
+        <v>-0.3919</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.8414</v>
+        <v>-8.229900000000001</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.44</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5325</v>
+        <v>-0.5414</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.1825</v>
+        <v>-11.3694</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.59</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2078</v>
+        <v>1.1841</v>
       </c>
       <c r="J107" t="n">
-        <v>25.3638</v>
+        <v>24.8661</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.52</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1245</v>
+        <v>1.0944</v>
       </c>
       <c r="J108" t="n">
-        <v>23.6145</v>
+        <v>22.9824</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.48</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0766</v>
+        <v>1.0409</v>
       </c>
       <c r="J109" t="n">
-        <v>22.6086</v>
+        <v>21.8589</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.33</v>
       </c>
       <c r="I110" t="n">
-        <v>0.8176</v>
+        <v>0.7826</v>
       </c>
       <c r="J110" t="n">
-        <v>17.1696</v>
+        <v>16.4346</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.22</v>
       </c>
       <c r="I111" t="n">
-        <v>0.5631</v>
+        <v>0.5573</v>
       </c>
       <c r="J111" t="n">
-        <v>11.8251</v>
+        <v>11.7033</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.12</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3569</v>
+        <v>0.3425</v>
       </c>
       <c r="J112" t="n">
-        <v>8.5656</v>
+        <v>8.220000000000001</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1784</v>
+        <v>-0.1966</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.2816</v>
+        <v>-4.7184</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.84</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1784</v>
+        <v>-0.1966</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.2816</v>
+        <v>-4.7184</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2746</v>
+        <v>-0.2922</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.5904</v>
+        <v>-7.0128</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4627</v>
+        <v>-0.4725</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.1048</v>
+        <v>-11.34</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0924</v>
+        <v>1.0527</v>
       </c>
       <c r="J117" t="n">
-        <v>26.2176</v>
+        <v>25.2648</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7365</v>
+        <v>0.7049</v>
       </c>
       <c r="J118" t="n">
-        <v>17.676</v>
+        <v>16.9176</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6466</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>15.5184</v>
+        <v>14.988</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.13</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3738</v>
+        <v>0.3783</v>
       </c>
       <c r="J120" t="n">
-        <v>8.9712</v>
+        <v>9.0792</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.12</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3468</v>
+        <v>0.3535</v>
       </c>
       <c r="J121" t="n">
-        <v>8.3232</v>
+        <v>8.484</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.45</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8973</v>
+        <v>0.8451</v>
       </c>
       <c r="J122" t="n">
-        <v>26.0217</v>
+        <v>24.5079</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0949</v>
+        <v>-0.1076</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.7521</v>
+        <v>-3.1204</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.82</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2127</v>
+        <v>-0.2276</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.1683</v>
+        <v>-6.6004</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.8</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2328</v>
+        <v>-0.2476</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.7512</v>
+        <v>-7.1804</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.74</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2918</v>
+        <v>-0.3056</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.462199999999999</v>
+        <v>-8.862399999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2424</v>
+        <v>1.21</v>
       </c>
       <c r="J127" t="n">
-        <v>36.0296</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.56</v>
       </c>
       <c r="I128" t="n">
-        <v>1.2296</v>
+        <v>1.1964</v>
       </c>
       <c r="J128" t="n">
-        <v>35.6584</v>
+        <v>34.6956</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.095</v>
+        <v>0.1115</v>
       </c>
       <c r="J129" t="n">
-        <v>2.755</v>
+        <v>3.2335</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.95</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2397</v>
+        <v>-0.2297</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.9513</v>
+        <v>-6.6613</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9634</v>
+        <v>-0.8803</v>
       </c>
       <c r="J131" t="n">
-        <v>-27.9386</v>
+        <v>-25.5287</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.83</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1783</v>
+        <v>-0.1989</v>
       </c>
       <c r="J132" t="n">
-        <v>-3.7443</v>
+        <v>-4.1769</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.8</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2092</v>
+        <v>-0.2295</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.3932</v>
+        <v>-4.8195</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.73</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2753</v>
+        <v>-0.2947</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.7813</v>
+        <v>-6.1887</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3125</v>
+        <v>-0.3309</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.5625</v>
+        <v>-6.9489</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3125</v>
+        <v>-0.3309</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.5625</v>
+        <v>-6.9489</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.3067</v>
+        <v>1.289</v>
       </c>
       <c r="J137" t="n">
-        <v>27.4407</v>
+        <v>27.069</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.56</v>
       </c>
       <c r="I138" t="n">
-        <v>1.176</v>
+        <v>1.1492</v>
       </c>
       <c r="J138" t="n">
-        <v>24.696</v>
+        <v>24.1332</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.36</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8875</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="J139" t="n">
-        <v>18.6375</v>
+        <v>17.7072</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.32</v>
       </c>
       <c r="I140" t="n">
-        <v>0.8004</v>
+        <v>0.7665</v>
       </c>
       <c r="J140" t="n">
-        <v>16.8084</v>
+        <v>16.0965</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.1</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2562</v>
+        <v>0.278</v>
       </c>
       <c r="J141" t="n">
-        <v>5.3802</v>
+        <v>5.838</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.78</v>
       </c>
       <c r="I142" t="n">
-        <v>1.458</v>
+        <v>1.4455</v>
       </c>
       <c r="J142" t="n">
-        <v>32.076</v>
+        <v>31.801</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.62</v>
       </c>
       <c r="I143" t="n">
-        <v>1.266</v>
+        <v>1.2421</v>
       </c>
       <c r="J143" t="n">
-        <v>27.852</v>
+        <v>27.3262</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.34</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8582</v>
+        <v>0.8146</v>
       </c>
       <c r="J144" t="n">
-        <v>18.8804</v>
+        <v>17.9212</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.91</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3998</v>
+        <v>-0.3711</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.7956</v>
+        <v>-8.164199999999999</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4575</v>
+        <v>-0.4243</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.065</v>
+        <v>-9.3346</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.93</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0718</v>
+        <v>-0.0897</v>
       </c>
       <c r="J147" t="n">
-        <v>-1.5796</v>
+        <v>-1.9734</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.92</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.1024</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.8502</v>
+        <v>-2.2528</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.78</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2326</v>
+        <v>-0.2517</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.1172</v>
+        <v>-5.5374</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.74</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2701</v>
+        <v>-0.2887</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.9422</v>
+        <v>-6.3514</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.54</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.458</v>
+        <v>-0.4688</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.076</v>
+        <v>-10.3136</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.46</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1072</v>
+        <v>1.0637</v>
       </c>
       <c r="J152" t="n">
-        <v>33.216</v>
+        <v>31.911</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.32</v>
       </c>
       <c r="I153" t="n">
-        <v>0.862</v>
+        <v>0.8089</v>
       </c>
       <c r="J153" t="n">
-        <v>25.86</v>
+        <v>24.267</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2608</v>
+        <v>0.2677</v>
       </c>
       <c r="J154" t="n">
-        <v>7.824</v>
+        <v>8.031000000000001</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3566</v>
+        <v>-0.3408</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.698</v>
+        <v>-10.224</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4147</v>
+        <v>-0.3942</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.441</v>
+        <v>-11.826</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4968</v>
+        <v>0.4867</v>
       </c>
       <c r="J157" t="n">
-        <v>14.904</v>
+        <v>14.601</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="J158" t="n">
-        <v>11.58</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.01</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0392</v>
+        <v>0.0444</v>
       </c>
       <c r="J159" t="n">
-        <v>1.176</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.87</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1657</v>
+        <v>-0.1793</v>
       </c>
       <c r="J160" t="n">
-        <v>-4.971</v>
+        <v>-5.379</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.67</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3634</v>
+        <v>-0.3742</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.902</v>
+        <v>-11.226</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.98</v>
       </c>
       <c r="I162" t="n">
-        <v>1.6559</v>
+        <v>1.6583</v>
       </c>
       <c r="J162" t="n">
-        <v>34.7739</v>
+        <v>34.8243</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.94</v>
       </c>
       <c r="I163" t="n">
-        <v>1.6108</v>
+        <v>1.6112</v>
       </c>
       <c r="J163" t="n">
-        <v>33.8268</v>
+        <v>33.8352</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.32</v>
       </c>
       <c r="I164" t="n">
-        <v>0.7938</v>
+        <v>0.762</v>
       </c>
       <c r="J164" t="n">
-        <v>16.6698</v>
+        <v>16.002</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6801</v>
+        <v>0.6616</v>
       </c>
       <c r="J165" t="n">
-        <v>14.2821</v>
+        <v>13.8936</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.67</v>
       </c>
       <c r="I166" t="n">
-        <v>-1.0397</v>
+        <v>-0.9382</v>
       </c>
       <c r="J166" t="n">
-        <v>-21.8337</v>
+        <v>-19.7022</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.97</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0599</v>
+        <v>0.0112</v>
       </c>
       <c r="J167" t="n">
-        <v>1.2579</v>
+        <v>0.2352</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2141</v>
+        <v>-0.2395</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.4961</v>
+        <v>-5.0295</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.67</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3152</v>
+        <v>-0.3367</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.6192</v>
+        <v>-7.0707</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.51</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4612</v>
+        <v>-0.4757</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.6852</v>
+        <v>-9.989699999999999</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.23</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7271</v>
+        <v>-0.7209</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.2691</v>
+        <v>-15.1389</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.76</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3949</v>
+        <v>1.3857</v>
       </c>
       <c r="J172" t="n">
-        <v>29.2929</v>
+        <v>29.0997</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.75</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3835</v>
+        <v>1.3736</v>
       </c>
       <c r="J173" t="n">
-        <v>29.0535</v>
+        <v>28.8456</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.67</v>
       </c>
       <c r="I174" t="n">
-        <v>1.2917</v>
+        <v>1.2759</v>
       </c>
       <c r="J174" t="n">
-        <v>27.1257</v>
+        <v>26.7939</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.21</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5255</v>
+        <v>0.5262</v>
       </c>
       <c r="J175" t="n">
-        <v>11.0355</v>
+        <v>11.0502</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.07</v>
       </c>
       <c r="I176" t="n">
-        <v>0.1497</v>
+        <v>0.183</v>
       </c>
       <c r="J176" t="n">
-        <v>3.1437</v>
+        <v>3.843</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.07</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3477</v>
+        <v>0.3125</v>
       </c>
       <c r="J177" t="n">
-        <v>7.3017</v>
+        <v>6.5625</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.76</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2325</v>
+        <v>-0.2558</v>
       </c>
       <c r="J178" t="n">
-        <v>-4.8825</v>
+        <v>-5.3718</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.74</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2529</v>
+        <v>-0.2755</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.3109</v>
+        <v>-5.7855</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.37</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5984</v>
+        <v>-0.6024</v>
       </c>
       <c r="J180" t="n">
-        <v>-12.5664</v>
+        <v>-12.6504</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.36</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6079</v>
+        <v>-0.6111</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.7659</v>
+        <v>-12.8331</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.02</v>
       </c>
       <c r="I182" t="n">
-        <v>0.08160000000000001</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="J182" t="n">
-        <v>2.3664</v>
+        <v>2.4534</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0133</v>
+        <v>0.0095</v>
       </c>
       <c r="J183" t="n">
-        <v>0.3857</v>
+        <v>0.2755</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.95</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.03</v>
+        <v>-2.3664</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.91</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1156</v>
+        <v>-0.1297</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.3524</v>
+        <v>-3.7613</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2699</v>
+        <v>-0.2846</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.8271</v>
+        <v>-8.253399999999999</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.56</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2136</v>
+        <v>1.1822</v>
       </c>
       <c r="J187" t="n">
-        <v>35.1944</v>
+        <v>34.2838</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.29</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7663</v>
+        <v>0.7298</v>
       </c>
       <c r="J188" t="n">
-        <v>22.2227</v>
+        <v>21.1642</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.29</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7663</v>
+        <v>0.7298</v>
       </c>
       <c r="J189" t="n">
-        <v>22.2227</v>
+        <v>21.1642</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.04</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1153</v>
+        <v>0.1351</v>
       </c>
       <c r="J190" t="n">
-        <v>3.3437</v>
+        <v>3.9179</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4074</v>
+        <v>-0.3829</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.8146</v>
+        <v>-11.1041</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.4</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5112</v>
+        <v>0.52</v>
       </c>
       <c r="J192" t="n">
-        <v>13.2912</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.24</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3279</v>
+        <v>0.3446</v>
       </c>
       <c r="J193" t="n">
-        <v>8.525399999999999</v>
+        <v>8.9596</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.18</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2568</v>
+        <v>0.2747</v>
       </c>
       <c r="J194" t="n">
-        <v>6.6768</v>
+        <v>7.1422</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.18</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2568</v>
+        <v>0.2747</v>
       </c>
       <c r="J195" t="n">
-        <v>6.6768</v>
+        <v>7.1422</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.092</v>
       </c>
       <c r="J196" t="n">
-        <v>1.9604</v>
+        <v>2.392</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1825</v>
+        <v>0.1856</v>
       </c>
       <c r="J197" t="n">
-        <v>4.745</v>
+        <v>4.8256</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.07</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1655</v>
+        <v>0.1687</v>
       </c>
       <c r="J198" t="n">
-        <v>4.303</v>
+        <v>4.3862</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.87</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1545</v>
+        <v>-0.1707</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.017</v>
+        <v>-4.4382</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2648</v>
+        <v>-0.2806</v>
       </c>
       <c r="J200" t="n">
-        <v>-6.8848</v>
+        <v>-7.2956</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3605</v>
+        <v>-0.3736</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.372999999999999</v>
+        <v>-9.7136</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3872</v>
+        <v>0.3771</v>
       </c>
       <c r="J202" t="n">
-        <v>10.4544</v>
+        <v>10.1817</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.01</v>
       </c>
       <c r="I203" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0634</v>
       </c>
       <c r="J203" t="n">
-        <v>1.7712</v>
+        <v>1.7118</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2246</v>
+        <v>-0.2412</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.0642</v>
+        <v>-6.5124</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.8</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2246</v>
+        <v>-0.2412</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.0642</v>
+        <v>-6.5124</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3691</v>
+        <v>-0.382</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.9657</v>
+        <v>-10.314</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.49</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1421</v>
+        <v>1.1024</v>
       </c>
       <c r="J207" t="n">
-        <v>30.8367</v>
+        <v>29.7648</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.26</v>
       </c>
       <c r="I208" t="n">
-        <v>0.7149</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J208" t="n">
-        <v>19.3023</v>
+        <v>18.3843</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.19</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5452</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="J209" t="n">
-        <v>14.7204</v>
+        <v>14.3019</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.0902</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.4354</v>
+        <v>-2.2707</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6363</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.1801</v>
+        <v>-16.0164</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.34</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6618000000000001</v>
+        <v>0.6419</v>
       </c>
       <c r="J212" t="n">
-        <v>19.1922</v>
+        <v>18.6151</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.16</v>
       </c>
       <c r="I213" t="n">
-        <v>0.347</v>
+        <v>0.3517</v>
       </c>
       <c r="J213" t="n">
-        <v>10.063</v>
+        <v>10.1993</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.083</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>2.407</v>
+        <v>2.7202</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.96</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0699</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.0271</v>
+        <v>-2.2533</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2058</v>
+        <v>-0.2177</v>
       </c>
       <c r="J216" t="n">
-        <v>-5.9682</v>
+        <v>-6.3133</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.41</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0639</v>
+        <v>1.0081</v>
       </c>
       <c r="J217" t="n">
-        <v>30.8531</v>
+        <v>29.2349</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.02</v>
       </c>
       <c r="I218" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0931</v>
       </c>
       <c r="J218" t="n">
-        <v>2.4389</v>
+        <v>2.6999</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.01</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0437</v>
+        <v>0.0521</v>
       </c>
       <c r="J219" t="n">
-        <v>1.2673</v>
+        <v>1.5109</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.01</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0437</v>
+        <v>0.0521</v>
       </c>
       <c r="J220" t="n">
-        <v>1.2673</v>
+        <v>1.5109</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.6103</v>
+        <v>-0.575</v>
       </c>
       <c r="J221" t="n">
-        <v>-17.6987</v>
+        <v>-16.675</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.33</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4631</v>
+        <v>0.4686</v>
       </c>
       <c r="J222" t="n">
-        <v>12.0406</v>
+        <v>12.1836</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.289</v>
+        <v>0.3018</v>
       </c>
       <c r="J223" t="n">
-        <v>7.514</v>
+        <v>7.8468</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.07</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1241</v>
+        <v>0.1374</v>
       </c>
       <c r="J224" t="n">
-        <v>3.2266</v>
+        <v>3.5724</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.88</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1617</v>
+        <v>-0.1737</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.2042</v>
+        <v>-4.5162</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.78</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2646</v>
+        <v>-0.2765</v>
       </c>
       <c r="J226" t="n">
-        <v>-6.8796</v>
+        <v>-7.189</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.54</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7557</v>
+        <v>0.7309</v>
       </c>
       <c r="J227" t="n">
-        <v>19.6482</v>
+        <v>19.0034</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>2.1346</v>
+        <v>2.4128</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.01</v>
       </c>
       <c r="I229" t="n">
-        <v>0.022</v>
+        <v>0.029</v>
       </c>
       <c r="J229" t="n">
-        <v>0.572</v>
+        <v>0.754</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.92</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1186</v>
+        <v>-0.129</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.0836</v>
+        <v>-3.354</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2362</v>
+        <v>-0.2481</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.1412</v>
+        <v>-6.4506</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.26</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6938</v>
+        <v>0.6422</v>
       </c>
       <c r="J232" t="n">
-        <v>15.9574</v>
+        <v>14.7706</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.71</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.2925</v>
+        <v>-0.3118</v>
       </c>
       <c r="J233" t="n">
-        <v>-6.7275</v>
+        <v>-7.1714</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.65</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3485</v>
+        <v>-0.3659</v>
       </c>
       <c r="J234" t="n">
-        <v>-8.015499999999999</v>
+        <v>-8.415699999999999</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.6</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3954</v>
+        <v>-0.4106</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.094200000000001</v>
+        <v>-9.4438</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5165</v>
+        <v>-0.5248</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.8795</v>
+        <v>-12.0704</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.5</v>
       </c>
       <c r="I237" t="n">
-        <v>1.1134</v>
+        <v>1.0795</v>
       </c>
       <c r="J237" t="n">
-        <v>25.6082</v>
+        <v>24.8285</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9918</v>
+        <v>0.9409</v>
       </c>
       <c r="J238" t="n">
-        <v>22.8114</v>
+        <v>21.6407</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.31</v>
       </c>
       <c r="I239" t="n">
-        <v>0.7896</v>
+        <v>0.7548</v>
       </c>
       <c r="J239" t="n">
-        <v>18.1608</v>
+        <v>17.3604</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.31</v>
       </c>
       <c r="I240" t="n">
-        <v>0.7896</v>
+        <v>0.7548</v>
       </c>
       <c r="J240" t="n">
-        <v>18.1608</v>
+        <v>17.3604</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.16</v>
       </c>
       <c r="I241" t="n">
-        <v>0.4325</v>
+        <v>0.436</v>
       </c>
       <c r="J241" t="n">
-        <v>9.9475</v>
+        <v>10.028</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.83</v>
       </c>
       <c r="I242" t="n">
-        <v>1.5378</v>
+        <v>1.526</v>
       </c>
       <c r="J242" t="n">
-        <v>39.9828</v>
+        <v>39.676</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.31</v>
       </c>
       <c r="I243" t="n">
-        <v>0.806</v>
+        <v>0.7659</v>
       </c>
       <c r="J243" t="n">
-        <v>20.956</v>
+        <v>19.9134</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.5048</v>
+        <v>0.4967</v>
       </c>
       <c r="J244" t="n">
-        <v>13.1248</v>
+        <v>12.9142</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.98</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1546</v>
+        <v>-0.1418</v>
       </c>
       <c r="J245" t="n">
-        <v>-4.0196</v>
+        <v>-3.6868</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4133</v>
+        <v>-0.387</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.7458</v>
+        <v>-10.062</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0287</v>
+        <v>0.0207</v>
       </c>
       <c r="J247" t="n">
-        <v>0.7462</v>
+        <v>0.5382</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.022</v>
+        <v>-0.032</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.572</v>
+        <v>-0.832</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.89</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1329</v>
+        <v>-0.1488</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.4554</v>
+        <v>-3.8688</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2532</v>
+        <v>-0.2696</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.5832</v>
+        <v>-7.0096</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.73</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.292</v>
+        <v>-0.3076</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.592</v>
+        <v>-7.9976</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.15</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2614</v>
+        <v>0.2692</v>
       </c>
       <c r="J252" t="n">
-        <v>7.0578</v>
+        <v>7.2684</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.06</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1219</v>
+        <v>0.1319</v>
       </c>
       <c r="J253" t="n">
-        <v>3.2913</v>
+        <v>3.5613</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.99</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0215</v>
+        <v>-0.0259</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.5805</v>
+        <v>-0.6993</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.0511</v>
+        <v>-0.059</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.3797</v>
+        <v>-1.593</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.89</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1466</v>
+        <v>-0.1593</v>
       </c>
       <c r="J256" t="n">
-        <v>-3.9582</v>
+        <v>-4.3011</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.56</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7135</v>
+        <v>0.7048</v>
       </c>
       <c r="J257" t="n">
-        <v>19.2645</v>
+        <v>19.0296</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.09</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1484</v>
+        <v>0.1637</v>
       </c>
       <c r="J258" t="n">
-        <v>4.0068</v>
+        <v>4.4199</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1019</v>
       </c>
       <c r="J259" t="n">
-        <v>2.3868</v>
+        <v>2.7513</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.98</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0461</v>
+        <v>-0.0505</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.2447</v>
+        <v>-1.3635</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2098</v>
+        <v>-0.2209</v>
       </c>
       <c r="J261" t="n">
-        <v>-5.6646</v>
+        <v>-5.9643</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.96</v>
       </c>
       <c r="I262" t="n">
-        <v>1.5981</v>
+        <v>1.6037</v>
       </c>
       <c r="J262" t="n">
-        <v>30.3639</v>
+        <v>30.4703</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.8</v>
       </c>
       <c r="I263" t="n">
-        <v>1.4223</v>
+        <v>1.418</v>
       </c>
       <c r="J263" t="n">
-        <v>27.0237</v>
+        <v>26.942</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.5</v>
       </c>
       <c r="I264" t="n">
-        <v>1.085</v>
+        <v>1.0544</v>
       </c>
       <c r="J264" t="n">
-        <v>20.615</v>
+        <v>20.0336</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.41</v>
       </c>
       <c r="I265" t="n">
-        <v>0.954</v>
+        <v>0.911</v>
       </c>
       <c r="J265" t="n">
-        <v>18.126</v>
+        <v>17.309</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.36</v>
       </c>
       <c r="I266" t="n">
-        <v>0.8496</v>
+        <v>0.8169</v>
       </c>
       <c r="J266" t="n">
-        <v>16.1424</v>
+        <v>15.5211</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.1</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6017</v>
+        <v>0.5165</v>
       </c>
       <c r="J267" t="n">
-        <v>11.4323</v>
+        <v>9.813499999999999</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.64</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3136</v>
+        <v>-0.3406</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.9584</v>
+        <v>-6.4714</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.45</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4943</v>
+        <v>-0.5101</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.3917</v>
+        <v>-9.6919</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.22</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.7216</v>
+        <v>-0.7177</v>
       </c>
       <c r="J270" t="n">
-        <v>-13.7104</v>
+        <v>-13.6363</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.16</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7826</v>
+        <v>-0.7726</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.8694</v>
+        <v>-14.6794</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>1.3707</v>
+        <v>1.3498</v>
       </c>
       <c r="J272" t="n">
-        <v>32.8968</v>
+        <v>32.3952</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.49</v>
       </c>
       <c r="I273" t="n">
-        <v>1.1212</v>
+        <v>1.0839</v>
       </c>
       <c r="J273" t="n">
-        <v>26.9088</v>
+        <v>26.0136</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2664</v>
+        <v>0.2785</v>
       </c>
       <c r="J274" t="n">
-        <v>6.3936</v>
+        <v>6.684</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.08</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2371</v>
+        <v>0.2513</v>
       </c>
       <c r="J275" t="n">
-        <v>5.6904</v>
+        <v>6.0312</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6567</v>
+        <v>-0.6076</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.7608</v>
+        <v>-14.5824</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.06</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2157</v>
+        <v>0.2095</v>
       </c>
       <c r="J277" t="n">
-        <v>5.1768</v>
+        <v>5.028</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0436</v>
+        <v>0.0315</v>
       </c>
       <c r="J278" t="n">
-        <v>1.0464</v>
+        <v>0.756</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.85</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1701</v>
+        <v>-0.1877</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.0824</v>
+        <v>-4.5048</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.71</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3055</v>
+        <v>-0.3218</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.332</v>
+        <v>-7.7232</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.54</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4648</v>
+        <v>-0.4742</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.1552</v>
+        <v>-11.3808</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.11</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2073</v>
+        <v>0.2154</v>
       </c>
       <c r="J282" t="n">
-        <v>6.0117</v>
+        <v>6.2466</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.06</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1265</v>
+        <v>0.1353</v>
       </c>
       <c r="J283" t="n">
-        <v>3.6685</v>
+        <v>3.9237</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.97</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0487</v>
+        <v>-0.0572</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.4123</v>
+        <v>-1.6588</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.89</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1435</v>
+        <v>-0.1568</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.1615</v>
+        <v>-4.5472</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.89</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.1435</v>
+        <v>-0.1568</v>
       </c>
       <c r="J286" t="n">
-        <v>-4.1615</v>
+        <v>-4.5472</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.2</v>
       </c>
       <c r="I287" t="n">
-        <v>0.2993</v>
+        <v>0.3123</v>
       </c>
       <c r="J287" t="n">
-        <v>8.6797</v>
+        <v>9.056699999999999</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1658</v>
+        <v>0.1804</v>
       </c>
       <c r="J288" t="n">
-        <v>4.8082</v>
+        <v>5.2316</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.09</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1517</v>
+        <v>0.1661</v>
       </c>
       <c r="J289" t="n">
-        <v>4.3993</v>
+        <v>4.8169</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.97</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.0563</v>
+        <v>-0.063</v>
       </c>
       <c r="J290" t="n">
-        <v>-1.6327</v>
+        <v>-1.827</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.96</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.0697</v>
+        <v>-0.0775</v>
       </c>
       <c r="J291" t="n">
-        <v>-2.0213</v>
+        <v>-2.2475</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.51</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1518</v>
+        <v>1.1158</v>
       </c>
       <c r="J292" t="n">
-        <v>27.6432</v>
+        <v>26.7792</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.37</v>
       </c>
       <c r="I293" t="n">
-        <v>0.9468</v>
+        <v>0.8898</v>
       </c>
       <c r="J293" t="n">
-        <v>22.7232</v>
+        <v>21.3552</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5107</v>
+        <v>0.5008</v>
       </c>
       <c r="J294" t="n">
-        <v>12.2568</v>
+        <v>12.0192</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.05</v>
       </c>
       <c r="I295" t="n">
-        <v>0.1498</v>
+        <v>0.1678</v>
       </c>
       <c r="J295" t="n">
-        <v>3.5952</v>
+        <v>4.0272</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2852</v>
+        <v>-0.2695</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.8448</v>
+        <v>-6.468</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.05</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1795</v>
+        <v>0.1771</v>
       </c>
       <c r="J297" t="n">
-        <v>4.308</v>
+        <v>4.2504</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.03</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1294</v>
+        <v>0.1273</v>
       </c>
       <c r="J298" t="n">
-        <v>3.1056</v>
+        <v>3.0552</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0327</v>
+        <v>0.0236</v>
       </c>
       <c r="J299" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.5664</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.73</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2904</v>
+        <v>-0.3064</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.9696</v>
+        <v>-7.3536</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5051</v>
+        <v>-0.5117</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.1224</v>
+        <v>-12.2808</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3985/event_3985_evp_summary.xlsx
+++ b/database/event/3985/event_3985_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.605</v>
+        <v>7.6142</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9823</v>
+        <v>1.9847</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8377</v>
+        <v>2.8628</v>
       </c>
       <c r="E2" t="n">
-        <v>7.605</v>
+        <v>7.6142</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4779</v>
+        <v>2.4613</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1271</v>
+        <v>5.1529</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6984</v>
+        <v>2.6903</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6984</v>
+        <v>2.6903</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1271</v>
+        <v>5.1529</v>
       </c>
       <c r="K2" t="n">
         <v>127</v>
@@ -529,7 +529,7 @@
         <v>151</v>
       </c>
       <c r="M2" t="n">
-        <v>7.8255</v>
+        <v>7.8432</v>
       </c>
       <c r="N2" t="n">
         <v>278</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.1733</v>
+        <v>6.9702</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8698</v>
+        <v>1.8168</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6412</v>
+        <v>2.5695</v>
       </c>
       <c r="E3" t="n">
-        <v>7.1733</v>
+        <v>6.9702</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5807</v>
+        <v>4.4108</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5926</v>
+        <v>2.5593</v>
       </c>
       <c r="H3" t="n">
-        <v>10.2892</v>
+        <v>10.1176</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5561</v>
+        <v>5.6807</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5926</v>
+        <v>2.5593</v>
       </c>
       <c r="K3" t="n">
         <v>122</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>8.1487</v>
+        <v>8.24</v>
       </c>
       <c r="N3" t="n">
         <v>224</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9889</v>
+        <v>3.9983</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0397</v>
+        <v>1.0422</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1916</v>
+        <v>1.2156</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9889</v>
+        <v>3.9983</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7103</v>
+        <v>0.4743</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2786</v>
+        <v>3.524</v>
       </c>
       <c r="H4" t="n">
-        <v>7.3473</v>
+        <v>0.4743</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9675</v>
+        <v>0.4743</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2786</v>
+        <v>3.524</v>
       </c>
       <c r="K4" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="L4" t="n">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2461</v>
+        <v>3.9983</v>
       </c>
       <c r="N4" t="n">
-        <v>140</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9798</v>
+        <v>3.8392</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0374</v>
+        <v>1.0007</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1875</v>
+        <v>1.1432</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9798</v>
+        <v>3.8392</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4074</v>
+        <v>3.6025</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5724</v>
+        <v>0.2367</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4074</v>
+        <v>7.0827</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4074</v>
+        <v>3.9767</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5724</v>
+        <v>0.2367</v>
       </c>
       <c r="K5" t="n">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="L5" t="n">
-        <v>151</v>
+        <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9798</v>
+        <v>4.2134</v>
       </c>
       <c r="N5" t="n">
-        <v>278</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4861</v>
+        <v>3.387</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9087</v>
+        <v>0.8828</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9627</v>
+        <v>0.9372</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4861</v>
+        <v>3.387</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6178</v>
+        <v>3.5165</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1317</v>
+        <v>-0.1295</v>
       </c>
       <c r="H6" t="n">
-        <v>7.0423</v>
+        <v>6.7599</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8028</v>
+        <v>3.7955</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1317</v>
+        <v>-0.1295</v>
       </c>
       <c r="K6" t="n">
         <v>87</v>
@@ -713,7 +713,7 @@
         <v>53</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6711</v>
+        <v>3.666</v>
       </c>
       <c r="N6" t="n">
         <v>140</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3753</v>
+        <v>3.2871</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8798</v>
+        <v>0.8568</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9123</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3753</v>
+        <v>3.2871</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4339</v>
+        <v>3.3564</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0586</v>
+        <v>-0.0693</v>
       </c>
       <c r="H7" t="n">
-        <v>6.4355</v>
+        <v>6.1588</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4751</v>
+        <v>3.458</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0586</v>
+        <v>-0.0693</v>
       </c>
       <c r="K7" t="n">
         <v>87</v>
@@ -759,7 +759,7 @@
         <v>53</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4165</v>
+        <v>3.3887</v>
       </c>
       <c r="N7" t="n">
         <v>140</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.307</v>
+        <v>3.2598</v>
       </c>
       <c r="C8" t="n">
-        <v>0.862</v>
+        <v>0.8497</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8812</v>
+        <v>0.8792</v>
       </c>
       <c r="E8" t="n">
-        <v>3.307</v>
+        <v>3.2598</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6278</v>
+        <v>2.6082</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6792</v>
+        <v>0.6516</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0265</v>
+        <v>3.0272</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1045</v>
+        <v>3.1081</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6792</v>
+        <v>0.6516</v>
       </c>
       <c r="K8" t="n">
         <v>150</v>
@@ -805,7 +805,7 @@
         <v>51</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7837</v>
+        <v>3.7597</v>
       </c>
       <c r="N8" t="n">
         <v>201</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2823</v>
+        <v>3.1452</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8555</v>
+        <v>0.8198</v>
       </c>
       <c r="D9" t="n">
-        <v>0.87</v>
+        <v>0.827</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2823</v>
+        <v>3.1452</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6189</v>
+        <v>3.5088</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3366</v>
+        <v>-0.3636</v>
       </c>
       <c r="H9" t="n">
-        <v>7.0458</v>
+        <v>6.7311</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8047</v>
+        <v>3.7793</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3366</v>
+        <v>-0.3636</v>
       </c>
       <c r="K9" t="n">
         <v>122</v>
@@ -851,7 +851,7 @@
         <v>102</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4681</v>
+        <v>3.4157</v>
       </c>
       <c r="N9" t="n">
         <v>224</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1137</v>
+        <v>3.087</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8116</v>
+        <v>0.8046</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7932</v>
+        <v>0.8005</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1137</v>
+        <v>3.087</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7647</v>
+        <v>2.8061</v>
       </c>
       <c r="G10" t="n">
-        <v>0.349</v>
+        <v>0.2809</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2275</v>
+        <v>4.0927</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2828</v>
+        <v>2.2979</v>
       </c>
       <c r="J10" t="n">
-        <v>0.349</v>
+        <v>0.2809</v>
       </c>
       <c r="K10" t="n">
         <v>87</v>
@@ -897,7 +897,7 @@
         <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>2.6318</v>
+        <v>2.5788</v>
       </c>
       <c r="N10" t="n">
         <v>140</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9935</v>
+        <v>2.8374</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7803</v>
+        <v>0.7396</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7385</v>
+        <v>0.6868</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9935</v>
+        <v>2.8374</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.7673</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2249</v>
+        <v>2.0701</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.7673</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.7673</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2249</v>
+        <v>2.0701</v>
       </c>
       <c r="K11" t="n">
         <v>127</v>
@@ -943,7 +943,7 @@
         <v>106</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9935</v>
+        <v>2.8374</v>
       </c>
       <c r="N11" t="n">
         <v>233</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.664</v>
+        <v>2.6829</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6944</v>
+        <v>0.6993</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5885</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.664</v>
+        <v>2.6829</v>
       </c>
       <c r="F12" t="n">
-        <v>1.024</v>
+        <v>1.0244</v>
       </c>
       <c r="G12" t="n">
-        <v>1.64</v>
+        <v>1.6585</v>
       </c>
       <c r="H12" t="n">
-        <v>1.024</v>
+        <v>1.0244</v>
       </c>
       <c r="I12" t="n">
-        <v>1.024</v>
+        <v>1.0244</v>
       </c>
       <c r="J12" t="n">
-        <v>1.64</v>
+        <v>1.6585</v>
       </c>
       <c r="K12" t="n">
         <v>127</v>
@@ -989,7 +989,7 @@
         <v>151</v>
       </c>
       <c r="M12" t="n">
-        <v>2.664</v>
+        <v>2.6829</v>
       </c>
       <c r="N12" t="n">
         <v>278</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.472</v>
+        <v>2.4696</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6443</v>
+        <v>0.6437</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5011</v>
+        <v>0.5192</v>
       </c>
       <c r="E13" t="n">
-        <v>2.472</v>
+        <v>2.4696</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0237</v>
+        <v>2.9893</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5517</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>5.0821</v>
+        <v>4.7805</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7443</v>
+        <v>2.6841</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5517</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>87</v>
@@ -1035,7 +1035,7 @@
         <v>53</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1926</v>
+        <v>2.1644</v>
       </c>
       <c r="N13" t="n">
         <v>140</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.3195</v>
+        <v>2.4268</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6046</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4317</v>
+        <v>0.4997</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3195</v>
+        <v>2.4268</v>
       </c>
       <c r="F14" t="n">
-        <v>2.4428</v>
+        <v>2.5355</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1233</v>
+        <v>-0.1087</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1654</v>
+        <v>3.0769</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7093</v>
+        <v>1.7276</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1233</v>
+        <v>-0.1087</v>
       </c>
       <c r="K14" t="n">
         <v>122</v>
@@ -1081,7 +1081,7 @@
         <v>102</v>
       </c>
       <c r="M14" t="n">
-        <v>1.586</v>
+        <v>1.6189</v>
       </c>
       <c r="N14" t="n">
         <v>224</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.2492</v>
+        <v>2.2227</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5863</v>
+        <v>0.5794</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3997</v>
+        <v>0.4068</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2492</v>
+        <v>2.2227</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1132</v>
+        <v>1.1199</v>
       </c>
       <c r="G15" t="n">
-        <v>1.136</v>
+        <v>1.1028</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1132</v>
+        <v>1.1199</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1132</v>
+        <v>1.1199</v>
       </c>
       <c r="J15" t="n">
-        <v>1.136</v>
+        <v>1.1028</v>
       </c>
       <c r="K15" t="n">
         <v>127</v>
@@ -1127,7 +1127,7 @@
         <v>106</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2492</v>
+        <v>2.2227</v>
       </c>
       <c r="N15" t="n">
         <v>233</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9955</v>
+        <v>2.042</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5201</v>
+        <v>0.5323</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2842</v>
+        <v>0.3244</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9955</v>
+        <v>2.042</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2014</v>
+        <v>2.2235</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2059</v>
+        <v>-0.1815</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2014</v>
+        <v>2.2235</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2581</v>
+        <v>2.2829</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2059</v>
+        <v>-0.1815</v>
       </c>
       <c r="K16" t="n">
         <v>134</v>
@@ -1173,7 +1173,7 @@
         <v>51</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0522</v>
+        <v>2.1014</v>
       </c>
       <c r="N16" t="n">
         <v>185</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8525</v>
+        <v>1.9463</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4829</v>
+        <v>0.5073</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2191</v>
+        <v>0.2808</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8525</v>
+        <v>1.9463</v>
       </c>
       <c r="F17" t="n">
-        <v>2.721</v>
+        <v>2.7763</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8685</v>
+        <v>-0.83</v>
       </c>
       <c r="H17" t="n">
-        <v>4.0834</v>
+        <v>3.981</v>
       </c>
       <c r="I17" t="n">
-        <v>2.205</v>
+        <v>2.2352</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8685</v>
+        <v>-0.83</v>
       </c>
       <c r="K17" t="n">
         <v>122</v>
@@ -1219,7 +1219,7 @@
         <v>102</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3365</v>
+        <v>1.4052</v>
       </c>
       <c r="N17" t="n">
         <v>224</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.413</v>
+        <v>1.5006</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3683</v>
+        <v>0.3911</v>
       </c>
       <c r="D18" t="n">
-        <v>0.019</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.413</v>
+        <v>1.5006</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.5181</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9831</v>
+        <v>2.0187</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.5181</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5701000000000001</v>
+        <v>-0.5181</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9831</v>
+        <v>2.0187</v>
       </c>
       <c r="K18" t="n">
         <v>127</v>
@@ -1265,7 +1265,7 @@
         <v>151</v>
       </c>
       <c r="M18" t="n">
-        <v>1.413</v>
+        <v>1.5006</v>
       </c>
       <c r="N18" t="n">
         <v>278</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3349</v>
+        <v>1.2952</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3479</v>
+        <v>0.3376</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0165</v>
+        <v>-0.0158</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3349</v>
+        <v>1.2952</v>
       </c>
       <c r="F19" t="n">
-        <v>0.24</v>
+        <v>1.2409</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0949</v>
+        <v>0.0542</v>
       </c>
       <c r="H19" t="n">
-        <v>0.24</v>
+        <v>1.2409</v>
       </c>
       <c r="I19" t="n">
-        <v>0.24</v>
+        <v>1.2741</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0949</v>
+        <v>0.0542</v>
       </c>
       <c r="K19" t="n">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="L19" t="n">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3349</v>
+        <v>1.3283</v>
       </c>
       <c r="N19" t="n">
-        <v>233</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.2851</v>
+        <v>1.2233</v>
       </c>
       <c r="C20" t="n">
-        <v>0.335</v>
+        <v>0.3189</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0392</v>
+        <v>-0.0485</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2851</v>
+        <v>1.2233</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1957</v>
+        <v>0.1983</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08939999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1957</v>
+        <v>0.1983</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2265</v>
+        <v>0.1983</v>
       </c>
       <c r="J20" t="n">
-        <v>0.08939999999999999</v>
+        <v>1.025</v>
       </c>
       <c r="K20" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3159</v>
+        <v>1.2233</v>
       </c>
       <c r="N20" t="n">
-        <v>201</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2205</v>
+        <v>1.2162</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3181</v>
+        <v>0.317</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0518</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2205</v>
+        <v>1.2162</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2474</v>
+        <v>-0.2599</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4679</v>
+        <v>1.4761</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2474</v>
+        <v>-0.2599</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2474</v>
+        <v>-0.2599</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4679</v>
+        <v>1.4761</v>
       </c>
       <c r="K21" t="n">
         <v>127</v>
@@ -1403,7 +1403,7 @@
         <v>151</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2205</v>
+        <v>1.2162</v>
       </c>
       <c r="N21" t="n">
         <v>278</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8446</v>
+        <v>0.6381</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2201</v>
+        <v>0.1663</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2397</v>
+        <v>-0.3151</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8446</v>
+        <v>0.6381</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8446</v>
+        <v>0.6381</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8446</v>
+        <v>0.6381</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8446</v>
+        <v>0.6381</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8446</v>
+        <v>0.6381</v>
       </c>
       <c r="N22" t="n">
         <v>155</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6625</v>
+        <v>0.5966</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1727</v>
+        <v>0.1555</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3226</v>
+        <v>-0.334</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6625</v>
+        <v>0.5966</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2569</v>
+        <v>1.1685</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5944</v>
+        <v>-0.5719</v>
       </c>
       <c r="H23" t="n">
-        <v>1.2569</v>
+        <v>1.1685</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2893</v>
+        <v>1.1997</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5944</v>
+        <v>-0.5719</v>
       </c>
       <c r="K23" t="n">
         <v>134</v>
@@ -1495,7 +1495,7 @@
         <v>51</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6948999999999999</v>
+        <v>0.6278</v>
       </c>
       <c r="N23" t="n">
         <v>185</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5544</v>
+        <v>0.587</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1445</v>
+        <v>0.153</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3718</v>
+        <v>-0.3384</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5544</v>
+        <v>0.587</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2582</v>
+        <v>1.2506</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7038</v>
+        <v>-0.6636</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2582</v>
+        <v>1.2506</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6794</v>
+        <v>0.7022</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7038</v>
+        <v>-0.6636</v>
       </c>
       <c r="K24" t="n">
         <v>122</v>
@@ -1541,7 +1541,7 @@
         <v>102</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.02439999999999998</v>
+        <v>0.03860000000000008</v>
       </c>
       <c r="N24" t="n">
         <v>224</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2749</v>
+        <v>0.2997</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0717</v>
+        <v>0.0781</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4991</v>
+        <v>-0.4693</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2749</v>
+        <v>0.2997</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8726</v>
+        <v>0.8628</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5977</v>
+        <v>-0.5631</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8726</v>
+        <v>0.8628</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8951</v>
+        <v>0.8859</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5977</v>
+        <v>-0.5631</v>
       </c>
       <c r="K25" t="n">
         <v>134</v>
@@ -1587,7 +1587,7 @@
         <v>51</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2974</v>
+        <v>0.3228</v>
       </c>
       <c r="N25" t="n">
         <v>185</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.237</v>
+        <v>0.1843</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0618</v>
+        <v>0.048</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5163</v>
+        <v>-0.5218</v>
       </c>
       <c r="E26" t="n">
-        <v>0.237</v>
+        <v>0.1843</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7657</v>
+        <v>0.7053</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.521</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7657</v>
+        <v>0.7053</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7854</v>
+        <v>0.7242</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.521</v>
       </c>
       <c r="K26" t="n">
         <v>134</v>
@@ -1633,7 +1633,7 @@
         <v>51</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2567</v>
+        <v>0.2031999999999999</v>
       </c>
       <c r="N26" t="n">
         <v>185</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1742</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0454</v>
+        <v>0.0258</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5449000000000001</v>
+        <v>-0.5606</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1742</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2719</v>
+        <v>0.2245</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.0977</v>
+        <v>-0.1254</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2719</v>
+        <v>0.2245</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2789</v>
+        <v>0.2305</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.0977</v>
+        <v>-0.1254</v>
       </c>
       <c r="K27" t="n">
         <v>150</v>
@@ -1679,7 +1679,7 @@
         <v>51</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1812</v>
+        <v>0.1051</v>
       </c>
       <c r="N27" t="n">
         <v>201</v>
@@ -1688,185 +1688,185 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0115</v>
+        <v>-0.0404</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.003</v>
+        <v>-0.0105</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6294</v>
+        <v>-0.6242</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0115</v>
+        <v>-0.0404</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0115</v>
+        <v>-0.4062</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.3659</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0115</v>
+        <v>-0.4062</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0115</v>
+        <v>-0.4171</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.3659</v>
       </c>
       <c r="K28" t="n">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0115</v>
+        <v>-0.05120000000000002</v>
       </c>
       <c r="N28" t="n">
-        <v>155</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0365</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0095</v>
+        <v>-0.0242</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6408</v>
+        <v>-0.6481</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0365</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4246</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4246</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4355</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="L29" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0474</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>185</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>swag</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1933</v>
+        <v>-0.2581</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0504</v>
+        <v>-0.0673</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7122000000000001</v>
+        <v>-0.7234</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1933</v>
+        <v>-0.2581</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1933</v>
+        <v>-0.2581</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1933</v>
+        <v>-0.2581</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1933</v>
+        <v>-0.2581</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>155</v>
+        <v>94</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1933</v>
+        <v>-0.2581</v>
       </c>
       <c r="N30" t="n">
-        <v>155</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>swag</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3026</v>
+        <v>-0.2957</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0789</v>
+        <v>-0.0771</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.762</v>
+        <v>-0.7405</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3026</v>
+        <v>-0.2957</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3026</v>
+        <v>-0.2957</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3026</v>
+        <v>-0.2957</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3026</v>
+        <v>-0.2957</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3026</v>
+        <v>-0.2957</v>
       </c>
       <c r="N31" t="n">
-        <v>94</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4628</v>
+        <v>-0.4494</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1206</v>
+        <v>-0.1171</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8349</v>
+        <v>-0.8105</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4628</v>
+        <v>-0.4494</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2018</v>
+        <v>0.1786</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.6646</v>
+        <v>-0.628</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2018</v>
+        <v>0.1786</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2018</v>
+        <v>0.1786</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.6646</v>
+        <v>-0.628</v>
       </c>
       <c r="K32" t="n">
         <v>127</v>
@@ -1909,7 +1909,7 @@
         <v>106</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4628</v>
+        <v>-0.4494</v>
       </c>
       <c r="N32" t="n">
         <v>233</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4717</v>
+        <v>-0.4527</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.123</v>
+        <v>-0.118</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8389</v>
+        <v>-0.8120000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4717</v>
+        <v>-0.4527</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4717</v>
+        <v>-0.4527</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4717</v>
+        <v>-0.4527</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4717</v>
+        <v>-0.4527</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4717</v>
+        <v>-0.4527</v>
       </c>
       <c r="N33" t="n">
         <v>155</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5405</v>
+        <v>-0.58</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1409</v>
+        <v>-0.1512</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8702</v>
+        <v>-0.87</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5405</v>
+        <v>-0.58</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5405</v>
+        <v>-0.58</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5405</v>
+        <v>-0.58</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5405</v>
+        <v>-0.58</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5405</v>
+        <v>-0.58</v>
       </c>
       <c r="N34" t="n">
         <v>155</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.784</v>
+        <v>-0.7227</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2044</v>
+        <v>-0.1884</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9811</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.784</v>
+        <v>-0.7227</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.784</v>
+        <v>-0.7227</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.784</v>
+        <v>-0.7227</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.784</v>
+        <v>-0.7227</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.784</v>
+        <v>-0.7227</v>
       </c>
       <c r="N35" t="n">
         <v>94</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Zellsis</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8155</v>
+        <v>-0.8156</v>
       </c>
       <c r="C36" t="n">
         <v>-0.2126</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9954</v>
+        <v>-0.9772999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8155</v>
+        <v>-0.8156</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8155</v>
+        <v>-0.8156</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8155</v>
+        <v>-0.8156</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8155</v>
+        <v>-0.8156</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8155</v>
+        <v>-0.8156</v>
       </c>
       <c r="N36" t="n">
         <v>94</v>
@@ -2102,32 +2102,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>Zellsis</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.8583</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2153</v>
+        <v>-0.2237</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0003</v>
+        <v>-0.9968</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.8583</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.8583</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.8583</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.8583</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.8583</v>
       </c>
       <c r="N37" t="n">
         <v>94</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9821</v>
+        <v>-1.036</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.256</v>
+        <v>-0.27</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0713</v>
+        <v>-1.0777</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9821</v>
+        <v>-1.036</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9821</v>
+        <v>-1.036</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9821</v>
+        <v>-1.036</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9821</v>
+        <v>-1.036</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9821</v>
+        <v>-1.036</v>
       </c>
       <c r="N38" t="n">
         <v>94</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1777</v>
+        <v>-1.1345</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.307</v>
+        <v>-0.2957</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1603</v>
+        <v>-1.1226</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1777</v>
+        <v>-1.1345</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.7091</v>
+        <v>-0.7019</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4686</v>
+        <v>-0.4326</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7091</v>
+        <v>-0.7019</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7274</v>
+        <v>-0.7207</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4686</v>
+        <v>-0.4326</v>
       </c>
       <c r="K39" t="n">
         <v>150</v>
@@ -2231,7 +2231,7 @@
         <v>51</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.196</v>
+        <v>-1.1533</v>
       </c>
       <c r="N39" t="n">
         <v>201</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3865</v>
+        <v>-1.4559</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3614</v>
+        <v>-0.3795</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2554</v>
+        <v>-1.269</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3865</v>
+        <v>-1.4559</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.7129</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.767</v>
+        <v>-0.743</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.7129</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6355</v>
+        <v>-0.7319</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.767</v>
+        <v>-0.743</v>
       </c>
       <c r="K40" t="n">
         <v>150</v>
@@ -2277,7 +2277,7 @@
         <v>51</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4025</v>
+        <v>-1.4749</v>
       </c>
       <c r="N40" t="n">
         <v>201</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8802</v>
+        <v>-1.7264</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4901</v>
+        <v>-0.45</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4801</v>
+        <v>-1.3922</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8802</v>
+        <v>-1.7264</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2758</v>
+        <v>-1.1664</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6044</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2758</v>
+        <v>-1.1664</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2758</v>
+        <v>-1.1664</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6044</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="K41" t="n">
         <v>127</v>
@@ -2323,7 +2323,7 @@
         <v>106</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8802</v>
+        <v>-1.7264</v>
       </c>
       <c r="N41" t="n">
         <v>233</v>
@@ -2429,10 +2429,10 @@
         <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8645</v>
+        <v>0.8165</v>
       </c>
       <c r="J2" t="n">
-        <v>24.206</v>
+        <v>22.862</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0003</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0168</v>
+        <v>-0.008399999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1481</v>
+        <v>-0.1284</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.1468</v>
+        <v>-3.5952</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.9</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1481</v>
+        <v>-0.1284</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.1468</v>
+        <v>-3.5952</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.79</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2636</v>
+        <v>-0.2441</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.3808</v>
+        <v>-6.8348</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.25</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6854</v>
+        <v>0.6509</v>
       </c>
       <c r="J7" t="n">
-        <v>19.1912</v>
+        <v>18.2252</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4809</v>
+        <v>0.4392</v>
       </c>
       <c r="J8" t="n">
-        <v>13.4652</v>
+        <v>12.2976</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4082</v>
+        <v>0.3664</v>
       </c>
       <c r="J9" t="n">
-        <v>11.4296</v>
+        <v>10.2592</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.86</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4537</v>
+        <v>-0.4108</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.7036</v>
+        <v>-11.5024</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.83</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5266</v>
+        <v>-0.4853</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.7448</v>
+        <v>-13.5884</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.68</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.307</v>
+        <v>-0.296</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.833</v>
+        <v>-5.624</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4203</v>
+        <v>-0.4161</v>
       </c>
       <c r="J13" t="n">
-        <v>-7.9857</v>
+        <v>-7.9059</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.54</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.4371</v>
+        <v>-0.4334</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.3049</v>
+        <v>-8.2346</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.49</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4789</v>
+        <v>-0.4766</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.0991</v>
+        <v>-9.055400000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.41</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5494</v>
+        <v>-0.5532</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.4386</v>
+        <v>-10.5108</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.84</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6094</v>
+        <v>1.638</v>
       </c>
       <c r="J17" t="n">
-        <v>30.5786</v>
+        <v>31.122</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.82</v>
       </c>
       <c r="I18" t="n">
-        <v>1.584</v>
+        <v>1.6131</v>
       </c>
       <c r="J18" t="n">
-        <v>30.096</v>
+        <v>30.6489</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.74</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4718</v>
+        <v>1.5092</v>
       </c>
       <c r="J19" t="n">
-        <v>27.9642</v>
+        <v>28.6748</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.35</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8037</v>
+        <v>0.7938</v>
       </c>
       <c r="J20" t="n">
-        <v>15.2703</v>
+        <v>15.0822</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.05</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1147</v>
+        <v>0.0833</v>
       </c>
       <c r="J21" t="n">
-        <v>2.1793</v>
+        <v>1.5827</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3437</v>
+        <v>0.2903</v>
       </c>
       <c r="J22" t="n">
-        <v>8.592499999999999</v>
+        <v>7.2575</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2887</v>
+        <v>0.2391</v>
       </c>
       <c r="J23" t="n">
-        <v>7.2175</v>
+        <v>5.9775</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1231</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>3.0775</v>
+        <v>2.3325</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.89</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1593</v>
+        <v>-0.1392</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.9825</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.86</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.192</v>
+        <v>-0.1713</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.8</v>
+        <v>-4.2825</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.27</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6466</v>
+        <v>0.6322</v>
       </c>
       <c r="J27" t="n">
-        <v>16.165</v>
+        <v>15.805</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.15</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4459</v>
+        <v>0.4096</v>
       </c>
       <c r="J28" t="n">
-        <v>11.1475</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.04</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1587</v>
+        <v>0.1316</v>
       </c>
       <c r="J29" t="n">
-        <v>3.9675</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0711</v>
+        <v>-0.0515</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.7775</v>
+        <v>-1.2875</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.93</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2741</v>
+        <v>-0.234</v>
       </c>
       <c r="J31" t="n">
-        <v>-6.8525</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.01</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0603</v>
+        <v>0.0418</v>
       </c>
       <c r="J32" t="n">
-        <v>1.6884</v>
+        <v>1.1704</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0603</v>
+        <v>0.0418</v>
       </c>
       <c r="J33" t="n">
-        <v>1.6884</v>
+        <v>1.1704</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.96</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0536</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.8228</v>
+        <v>-1.5008</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.86</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1817</v>
+        <v>-0.1626</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.0876</v>
+        <v>-4.5528</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.64</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3924</v>
+        <v>-0.3805</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.9872</v>
+        <v>-10.654</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.56</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0314</v>
+        <v>1.0199</v>
       </c>
       <c r="J37" t="n">
-        <v>28.8792</v>
+        <v>28.5572</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.37</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7688</v>
+        <v>0.7542</v>
       </c>
       <c r="J38" t="n">
-        <v>21.5264</v>
+        <v>21.1176</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.26</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6071</v>
+        <v>0.598</v>
       </c>
       <c r="J39" t="n">
-        <v>16.9988</v>
+        <v>16.744</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.03</v>
       </c>
       <c r="I40" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>2.7608</v>
+        <v>2.1896</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2733</v>
+        <v>-0.2357</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.6524</v>
+        <v>-6.5996</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.35</v>
       </c>
       <c r="I42" t="n">
-        <v>0.74</v>
+        <v>0.7259</v>
       </c>
       <c r="J42" t="n">
-        <v>19.98</v>
+        <v>19.5993</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.34</v>
       </c>
       <c r="I43" t="n">
-        <v>0.7255</v>
+        <v>0.7118</v>
       </c>
       <c r="J43" t="n">
-        <v>19.5885</v>
+        <v>19.2186</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.21</v>
       </c>
       <c r="I44" t="n">
-        <v>0.5309</v>
+        <v>0.5244</v>
       </c>
       <c r="J44" t="n">
-        <v>14.3343</v>
+        <v>14.1588</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.2</v>
       </c>
       <c r="I45" t="n">
-        <v>0.515</v>
+        <v>0.5063</v>
       </c>
       <c r="J45" t="n">
-        <v>13.905</v>
+        <v>13.6701</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.06</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1943</v>
+        <v>0.1664</v>
       </c>
       <c r="J46" t="n">
-        <v>5.2461</v>
+        <v>4.4928</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.16</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4175</v>
+        <v>0.3684</v>
       </c>
       <c r="J47" t="n">
-        <v>11.2725</v>
+        <v>9.9468</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.02</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1116</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>3.0132</v>
+        <v>2.322</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.77</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2643</v>
+        <v>-0.2462</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.1361</v>
+        <v>-6.6474</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.58</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.4378</v>
+        <v>-0.4299</v>
       </c>
       <c r="J50" t="n">
-        <v>-11.8206</v>
+        <v>-11.6073</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.57</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4467</v>
+        <v>-0.4396</v>
       </c>
       <c r="J51" t="n">
-        <v>-12.0609</v>
+        <v>-11.8692</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.71</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2963</v>
+        <v>1.313</v>
       </c>
       <c r="J52" t="n">
-        <v>36.2964</v>
+        <v>36.764</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.02</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0961</v>
+        <v>0.075</v>
       </c>
       <c r="J53" t="n">
-        <v>2.6908</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.98</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1042</v>
+        <v>-0.0796</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.9176</v>
+        <v>-2.2288</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.74</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.7286</v>
+        <v>-0.6979</v>
       </c>
       <c r="J55" t="n">
-        <v>-20.4008</v>
+        <v>-19.5412</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.7</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8151</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="J56" t="n">
-        <v>-22.8228</v>
+        <v>-22.1704</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.18</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4024</v>
+        <v>0.3461</v>
       </c>
       <c r="J57" t="n">
-        <v>11.2672</v>
+        <v>9.690799999999999</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.08</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2148</v>
+        <v>0.172</v>
       </c>
       <c r="J58" t="n">
-        <v>6.0144</v>
+        <v>4.816</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1225</v>
+        <v>-0.1042</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.43</v>
+        <v>-2.9176</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.88</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1681</v>
+        <v>-0.1479</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.7068</v>
+        <v>-4.1412</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1789</v>
+        <v>-0.1586</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.0092</v>
+        <v>-4.4408</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>0.98</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.0285</v>
+        <v>-0.0213</v>
       </c>
       <c r="J62" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.5112</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.98</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0285</v>
+        <v>-0.0213</v>
       </c>
       <c r="J63" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.5112</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.93</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.0994</v>
+        <v>-0.0854</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.3856</v>
+        <v>-2.0496</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.78</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2574</v>
+        <v>-0.2386</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.1776</v>
+        <v>-5.7264</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.57</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4496</v>
+        <v>-0.4431</v>
       </c>
       <c r="J66" t="n">
-        <v>-10.7904</v>
+        <v>-10.6344</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.94</v>
       </c>
       <c r="I67" t="n">
-        <v>1.5073</v>
+        <v>1.5306</v>
       </c>
       <c r="J67" t="n">
-        <v>36.1752</v>
+        <v>36.7344</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.57</v>
       </c>
       <c r="I68" t="n">
-        <v>1.0376</v>
+        <v>1.0263</v>
       </c>
       <c r="J68" t="n">
-        <v>24.9024</v>
+        <v>24.6312</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.11</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3253</v>
+        <v>0.2932</v>
       </c>
       <c r="J69" t="n">
-        <v>7.8072</v>
+        <v>7.0368</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.88</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4434</v>
+        <v>-0.4044</v>
       </c>
       <c r="J70" t="n">
-        <v>-10.6416</v>
+        <v>-9.7056</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.83</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5662</v>
+        <v>-0.531</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.5888</v>
+        <v>-12.744</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.21</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4875</v>
+        <v>0.4538</v>
       </c>
       <c r="J72" t="n">
-        <v>13.1625</v>
+        <v>12.2526</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>0.89</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.1448</v>
+        <v>-0.1288</v>
       </c>
       <c r="J73" t="n">
-        <v>-3.9096</v>
+        <v>-3.4776</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.86</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.1774</v>
+        <v>-0.1602</v>
       </c>
       <c r="J74" t="n">
-        <v>-4.7898</v>
+        <v>-4.3254</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3403</v>
+        <v>-0.3245</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.1881</v>
+        <v>-8.7615</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.51</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5002</v>
+        <v>-0.4997</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.5054</v>
+        <v>-13.4919</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.7</v>
       </c>
       <c r="I77" t="n">
-        <v>1.2009</v>
+        <v>1.1974</v>
       </c>
       <c r="J77" t="n">
-        <v>32.4243</v>
+        <v>32.3298</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.44</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8579</v>
+        <v>0.8439</v>
       </c>
       <c r="J78" t="n">
-        <v>23.1633</v>
+        <v>22.7853</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.3</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6611</v>
+        <v>0.6516</v>
       </c>
       <c r="J79" t="n">
-        <v>17.8497</v>
+        <v>17.5932</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.09</v>
       </c>
       <c r="I80" t="n">
-        <v>0.2687</v>
+        <v>0.2377</v>
       </c>
       <c r="J80" t="n">
-        <v>7.2549</v>
+        <v>6.4179</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.93</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3126</v>
+        <v>-0.2752</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.440200000000001</v>
+        <v>-7.4304</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.46</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7291</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>18.9566</v>
+        <v>18.0726</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.14</v>
       </c>
       <c r="I83" t="n">
-        <v>0.323</v>
+        <v>0.2711</v>
       </c>
       <c r="J83" t="n">
-        <v>8.398</v>
+        <v>7.0486</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.09</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2285</v>
+        <v>0.1849</v>
       </c>
       <c r="J84" t="n">
-        <v>5.941</v>
+        <v>4.8074</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2646</v>
+        <v>-0.2452</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.8796</v>
+        <v>-6.3752</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.65</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3952</v>
+        <v>-0.3848</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.2752</v>
+        <v>-10.0048</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.42</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8764</v>
+        <v>0.8621</v>
       </c>
       <c r="J87" t="n">
-        <v>22.7864</v>
+        <v>22.4146</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.6956</v>
       </c>
       <c r="J88" t="n">
-        <v>18.4912</v>
+        <v>18.0856</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.16</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4663</v>
+        <v>0.4352</v>
       </c>
       <c r="J89" t="n">
-        <v>12.1238</v>
+        <v>11.3152</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.74</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.7357</v>
+        <v>-0.7063</v>
       </c>
       <c r="J90" t="n">
-        <v>-19.1282</v>
+        <v>-18.3638</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.7</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.8002</v>
       </c>
       <c r="J91" t="n">
-        <v>-21.3746</v>
+        <v>-20.8052</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>0.96</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.0499</v>
+        <v>-0.039</v>
       </c>
       <c r="J92" t="n">
-        <v>-1.2475</v>
+        <v>-0.975</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.83</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.204</v>
+        <v>-0.1874</v>
       </c>
       <c r="J93" t="n">
-        <v>-5.1</v>
+        <v>-4.685</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.8</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2336</v>
+        <v>-0.2165</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.84</v>
+        <v>-5.4125</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.7</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3262</v>
+        <v>-0.3103</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.154999999999999</v>
+        <v>-7.7575</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.65</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3718</v>
+        <v>-0.3582</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.295</v>
+        <v>-8.955</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.5</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9387</v>
+        <v>0.9253</v>
       </c>
       <c r="J97" t="n">
-        <v>23.4675</v>
+        <v>23.1325</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.36</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7461</v>
+        <v>0.7338</v>
       </c>
       <c r="J98" t="n">
-        <v>18.6525</v>
+        <v>18.345</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.34</v>
       </c>
       <c r="I99" t="n">
-        <v>0.7178</v>
+        <v>0.7063</v>
       </c>
       <c r="J99" t="n">
-        <v>17.945</v>
+        <v>17.6575</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.19</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4921</v>
+        <v>0.4798</v>
       </c>
       <c r="J100" t="n">
-        <v>12.3025</v>
+        <v>11.995</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.09</v>
       </c>
       <c r="I101" t="n">
-        <v>0.268</v>
+        <v>0.2371</v>
       </c>
       <c r="J101" t="n">
-        <v>6.7</v>
+        <v>5.9275</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>0.89</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.1133</v>
+        <v>-0.0954</v>
       </c>
       <c r="J102" t="n">
-        <v>-2.3793</v>
+        <v>-2.0034</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.68</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.3316</v>
+        <v>-0.3197</v>
       </c>
       <c r="J103" t="n">
-        <v>-6.9636</v>
+        <v>-6.7137</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.68</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3316</v>
+        <v>-0.3197</v>
       </c>
       <c r="J104" t="n">
-        <v>-6.9636</v>
+        <v>-6.7137</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3919</v>
+        <v>-0.3815</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.229900000000001</v>
+        <v>-8.0115</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.44</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5414</v>
+        <v>-0.5446</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.3694</v>
+        <v>-11.4366</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.59</v>
       </c>
       <c r="I107" t="n">
-        <v>1.1841</v>
+        <v>1.2007</v>
       </c>
       <c r="J107" t="n">
-        <v>24.8661</v>
+        <v>25.2147</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.52</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0944</v>
+        <v>1.1093</v>
       </c>
       <c r="J108" t="n">
-        <v>22.9824</v>
+        <v>23.2953</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.48</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0409</v>
+        <v>1.0511</v>
       </c>
       <c r="J109" t="n">
-        <v>21.8589</v>
+        <v>22.0731</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.33</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7826</v>
+        <v>0.7679</v>
       </c>
       <c r="J110" t="n">
-        <v>16.4346</v>
+        <v>16.1259</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.22</v>
       </c>
       <c r="I111" t="n">
-        <v>0.5573</v>
+        <v>0.5305</v>
       </c>
       <c r="J111" t="n">
-        <v>11.7033</v>
+        <v>11.1405</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.12</v>
       </c>
       <c r="I112" t="n">
-        <v>0.3425</v>
+        <v>0.2948</v>
       </c>
       <c r="J112" t="n">
-        <v>8.220000000000001</v>
+        <v>7.0752</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.84</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1966</v>
+        <v>-0.1793</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.7184</v>
+        <v>-4.3032</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.84</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1966</v>
+        <v>-0.1793</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.7184</v>
+        <v>-4.3032</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.74</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2922</v>
+        <v>-0.2746</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.0128</v>
+        <v>-6.5904</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.54</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4725</v>
+        <v>-0.4684</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.34</v>
+        <v>-11.2416</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.47</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0527</v>
+        <v>1.059</v>
       </c>
       <c r="J117" t="n">
-        <v>25.2648</v>
+        <v>25.416</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.28</v>
       </c>
       <c r="I118" t="n">
-        <v>0.7049</v>
+        <v>0.6777</v>
       </c>
       <c r="J118" t="n">
-        <v>16.9176</v>
+        <v>16.2648</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.24</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.5946</v>
       </c>
       <c r="J119" t="n">
-        <v>14.988</v>
+        <v>14.2704</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.13</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3783</v>
+        <v>0.3454</v>
       </c>
       <c r="J120" t="n">
-        <v>9.0792</v>
+        <v>8.2896</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>1.12</v>
       </c>
       <c r="I121" t="n">
-        <v>0.3535</v>
+        <v>0.3209</v>
       </c>
       <c r="J121" t="n">
-        <v>8.484</v>
+        <v>7.7016</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.45</v>
       </c>
       <c r="I122" t="n">
-        <v>0.8451</v>
+        <v>0.8002</v>
       </c>
       <c r="J122" t="n">
-        <v>24.5079</v>
+        <v>23.2058</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.1076</v>
+        <v>-0.091</v>
       </c>
       <c r="J123" t="n">
-        <v>-3.1204</v>
+        <v>-2.639</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.82</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2276</v>
+        <v>-0.2073</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.6004</v>
+        <v>-6.0117</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.8</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2476</v>
+        <v>-0.2276</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.1804</v>
+        <v>-6.6004</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.74</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3056</v>
+        <v>-0.2878</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.862399999999999</v>
+        <v>-8.3462</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.57</v>
       </c>
       <c r="I127" t="n">
-        <v>1.21</v>
+        <v>1.2263</v>
       </c>
       <c r="J127" t="n">
-        <v>35.09</v>
+        <v>35.5627</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.56</v>
       </c>
       <c r="I128" t="n">
-        <v>1.1964</v>
+        <v>1.212</v>
       </c>
       <c r="J128" t="n">
-        <v>34.6956</v>
+        <v>35.148</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.03</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1115</v>
+        <v>0.0906</v>
       </c>
       <c r="J129" t="n">
-        <v>3.2335</v>
+        <v>2.6274</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.95</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2297</v>
+        <v>-0.1928</v>
       </c>
       <c r="J130" t="n">
-        <v>-6.6613</v>
+        <v>-5.5912</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.68</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8803</v>
+        <v>-0.8669</v>
       </c>
       <c r="J131" t="n">
-        <v>-25.5287</v>
+        <v>-25.1401</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>0.83</v>
       </c>
       <c r="I132" t="n">
-        <v>-0.1989</v>
+        <v>-0.1832</v>
       </c>
       <c r="J132" t="n">
-        <v>-4.1769</v>
+        <v>-3.8472</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.8</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.2295</v>
+        <v>-0.2137</v>
       </c>
       <c r="J133" t="n">
-        <v>-4.8195</v>
+        <v>-4.4877</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.73</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2947</v>
+        <v>-0.279</v>
       </c>
       <c r="J134" t="n">
-        <v>-6.1887</v>
+        <v>-5.859</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3309</v>
+        <v>-0.3159</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.9489</v>
+        <v>-6.6339</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3309</v>
+        <v>-0.3159</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.9489</v>
+        <v>-6.6339</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.67</v>
       </c>
       <c r="I137" t="n">
-        <v>1.289</v>
+        <v>1.3084</v>
       </c>
       <c r="J137" t="n">
-        <v>27.069</v>
+        <v>27.4764</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.56</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1492</v>
+        <v>1.1645</v>
       </c>
       <c r="J138" t="n">
-        <v>24.1332</v>
+        <v>24.4545</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.36</v>
       </c>
       <c r="I139" t="n">
-        <v>0.8431999999999999</v>
+        <v>0.8312</v>
       </c>
       <c r="J139" t="n">
-        <v>17.7072</v>
+        <v>17.4552</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.32</v>
       </c>
       <c r="I140" t="n">
-        <v>0.7665</v>
+        <v>0.7498</v>
       </c>
       <c r="J140" t="n">
-        <v>16.0965</v>
+        <v>15.7458</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.1</v>
       </c>
       <c r="I141" t="n">
-        <v>0.278</v>
+        <v>0.2458</v>
       </c>
       <c r="J141" t="n">
-        <v>5.838</v>
+        <v>5.1618</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.78</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4455</v>
+        <v>1.4738</v>
       </c>
       <c r="J142" t="n">
-        <v>31.801</v>
+        <v>32.4236</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.62</v>
       </c>
       <c r="I143" t="n">
-        <v>1.2421</v>
+        <v>1.2587</v>
       </c>
       <c r="J143" t="n">
-        <v>27.3262</v>
+        <v>27.6914</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.34</v>
       </c>
       <c r="I144" t="n">
-        <v>0.8146</v>
+        <v>0.7961</v>
       </c>
       <c r="J144" t="n">
-        <v>17.9212</v>
+        <v>17.5142</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.91</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3711</v>
+        <v>-0.3331</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.164199999999999</v>
+        <v>-7.3282</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.89</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4243</v>
+        <v>-0.3863</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.3346</v>
+        <v>-8.4986</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.93</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0897</v>
+        <v>-0.0762</v>
       </c>
       <c r="J147" t="n">
-        <v>-1.9734</v>
+        <v>-1.6764</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.92</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1024</v>
+        <v>-0.0883</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.2528</v>
+        <v>-1.9426</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.78</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2517</v>
+        <v>-0.2348</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.5374</v>
+        <v>-5.1656</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.74</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2887</v>
+        <v>-0.2718</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.3514</v>
+        <v>-5.9796</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.54</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4688</v>
+        <v>-0.464</v>
       </c>
       <c r="J151" t="n">
-        <v>-10.3136</v>
+        <v>-10.208</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.46</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0637</v>
+        <v>1.0714</v>
       </c>
       <c r="J152" t="n">
-        <v>31.911</v>
+        <v>32.142</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.32</v>
       </c>
       <c r="I153" t="n">
-        <v>0.8089</v>
+        <v>0.7834</v>
       </c>
       <c r="J153" t="n">
-        <v>24.267</v>
+        <v>23.502</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.08</v>
       </c>
       <c r="I154" t="n">
-        <v>0.2677</v>
+        <v>0.2346</v>
       </c>
       <c r="J154" t="n">
-        <v>8.031000000000001</v>
+        <v>7.038</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.91</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3408</v>
+        <v>-0.299</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.224</v>
+        <v>-8.970000000000001</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.89</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3942</v>
+        <v>-0.3518</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.826</v>
+        <v>-10.554</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.23</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4867</v>
+        <v>0.428</v>
       </c>
       <c r="J157" t="n">
-        <v>14.601</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.17</v>
       </c>
       <c r="I158" t="n">
-        <v>0.384</v>
+        <v>0.3284</v>
       </c>
       <c r="J158" t="n">
-        <v>11.52</v>
+        <v>9.852</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.01</v>
       </c>
       <c r="I159" t="n">
-        <v>0.0444</v>
+        <v>0.0298</v>
       </c>
       <c r="J159" t="n">
-        <v>1.332</v>
+        <v>0.894</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.87</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1793</v>
+        <v>-0.1589</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.379</v>
+        <v>-4.767</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.67</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3742</v>
+        <v>-0.3614</v>
       </c>
       <c r="J161" t="n">
-        <v>-11.226</v>
+        <v>-10.842</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.98</v>
       </c>
       <c r="I162" t="n">
-        <v>1.6583</v>
+        <v>1.7028</v>
       </c>
       <c r="J162" t="n">
-        <v>34.8243</v>
+        <v>35.7588</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.94</v>
       </c>
       <c r="I163" t="n">
-        <v>1.6112</v>
+        <v>1.6514</v>
       </c>
       <c r="J163" t="n">
-        <v>33.8352</v>
+        <v>34.6794</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.32</v>
       </c>
       <c r="I164" t="n">
-        <v>0.762</v>
+        <v>0.7462</v>
       </c>
       <c r="J164" t="n">
-        <v>16.002</v>
+        <v>15.6702</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.27</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6616</v>
+        <v>0.64</v>
       </c>
       <c r="J165" t="n">
-        <v>13.8936</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.67</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.9382</v>
+        <v>-0.9397</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.7022</v>
+        <v>-19.7337</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.97</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0112</v>
+        <v>0.0425</v>
       </c>
       <c r="J167" t="n">
-        <v>0.2352</v>
+        <v>0.8925</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.77</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.2395</v>
+        <v>-0.2252</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.0295</v>
+        <v>-4.7292</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.67</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3367</v>
+        <v>-0.3261</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.0707</v>
+        <v>-6.8481</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.51</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4757</v>
+        <v>-0.4714</v>
       </c>
       <c r="J170" t="n">
-        <v>-9.989699999999999</v>
+        <v>-9.8994</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.23</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7209</v>
+        <v>-0.7563</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.1389</v>
+        <v>-15.8823</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.76</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3857</v>
+        <v>1.4107</v>
       </c>
       <c r="J172" t="n">
-        <v>29.0997</v>
+        <v>29.6247</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.75</v>
       </c>
       <c r="I173" t="n">
-        <v>1.3736</v>
+        <v>1.398</v>
       </c>
       <c r="J173" t="n">
-        <v>28.8456</v>
+        <v>29.358</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.67</v>
       </c>
       <c r="I174" t="n">
-        <v>1.2759</v>
+        <v>1.2964</v>
       </c>
       <c r="J174" t="n">
-        <v>26.7939</v>
+        <v>27.2244</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.21</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5262</v>
+        <v>0.4984</v>
       </c>
       <c r="J175" t="n">
-        <v>11.0502</v>
+        <v>10.4664</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>1.07</v>
       </c>
       <c r="I176" t="n">
-        <v>0.183</v>
+        <v>0.1509</v>
       </c>
       <c r="J176" t="n">
-        <v>3.843</v>
+        <v>3.1689</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.07</v>
       </c>
       <c r="I177" t="n">
-        <v>0.3125</v>
+        <v>0.289</v>
       </c>
       <c r="J177" t="n">
-        <v>6.5625</v>
+        <v>6.069</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.76</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.2558</v>
+        <v>-0.2421</v>
       </c>
       <c r="J178" t="n">
-        <v>-5.3718</v>
+        <v>-5.0841</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.74</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2755</v>
+        <v>-0.2624</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.7855</v>
+        <v>-5.5104</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.37</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.6024</v>
+        <v>-0.615</v>
       </c>
       <c r="J180" t="n">
-        <v>-12.6504</v>
+        <v>-12.915</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.36</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6111</v>
+        <v>-0.6252</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.8331</v>
+        <v>-13.1292</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.02</v>
       </c>
       <c r="I182" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0604</v>
       </c>
       <c r="J182" t="n">
-        <v>2.4534</v>
+        <v>1.7516</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0095</v>
+        <v>0.006</v>
       </c>
       <c r="J183" t="n">
-        <v>0.2755</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.95</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0679</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.3664</v>
+        <v>-1.9691</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.91</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1297</v>
+        <v>-0.1121</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.7613</v>
+        <v>-3.2509</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.76</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2846</v>
+        <v>-0.2658</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.253399999999999</v>
+        <v>-7.7082</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.56</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1822</v>
+        <v>1.1965</v>
       </c>
       <c r="J187" t="n">
-        <v>34.2838</v>
+        <v>34.6985</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.29</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7298</v>
+        <v>0.7022</v>
       </c>
       <c r="J188" t="n">
-        <v>21.1642</v>
+        <v>20.3638</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.29</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7298</v>
+        <v>0.7022</v>
       </c>
       <c r="J189" t="n">
-        <v>21.1642</v>
+        <v>20.3638</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.04</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1351</v>
+        <v>0.1115</v>
       </c>
       <c r="J190" t="n">
-        <v>3.9179</v>
+        <v>3.2335</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.9</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3829</v>
+        <v>-0.3423</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.1041</v>
+        <v>-9.9267</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.4</v>
       </c>
       <c r="I192" t="n">
-        <v>0.52</v>
+        <v>0.4513</v>
       </c>
       <c r="J192" t="n">
-        <v>13.52</v>
+        <v>11.7338</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.24</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3446</v>
+        <v>0.2878</v>
       </c>
       <c r="J193" t="n">
-        <v>8.9596</v>
+        <v>7.4828</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.18</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2747</v>
+        <v>0.2252</v>
       </c>
       <c r="J194" t="n">
-        <v>7.1422</v>
+        <v>5.8552</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.18</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2747</v>
+        <v>0.2252</v>
       </c>
       <c r="J195" t="n">
-        <v>7.1422</v>
+        <v>5.8552</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.05</v>
       </c>
       <c r="I196" t="n">
-        <v>0.092</v>
+        <v>0.0684</v>
       </c>
       <c r="J196" t="n">
-        <v>2.392</v>
+        <v>1.7784</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.1856</v>
+        <v>0.1691</v>
       </c>
       <c r="J197" t="n">
-        <v>4.8256</v>
+        <v>4.3966</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.07</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1687</v>
+        <v>0.152</v>
       </c>
       <c r="J198" t="n">
-        <v>4.3862</v>
+        <v>3.952</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.87</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1707</v>
+        <v>-0.152</v>
       </c>
       <c r="J199" t="n">
-        <v>-4.4382</v>
+        <v>-3.952</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.76</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2806</v>
+        <v>-0.2619</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.2956</v>
+        <v>-6.8094</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.66</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3736</v>
+        <v>-0.3601</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.7136</v>
+        <v>-9.3626</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.15</v>
       </c>
       <c r="I202" t="n">
-        <v>0.3771</v>
+        <v>0.3241</v>
       </c>
       <c r="J202" t="n">
-        <v>10.1817</v>
+        <v>8.7507</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.01</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0634</v>
+        <v>0.0446</v>
       </c>
       <c r="J203" t="n">
-        <v>1.7118</v>
+        <v>1.2042</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2412</v>
+        <v>-0.2217</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.5124</v>
+        <v>-5.9859</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.8</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2412</v>
+        <v>-0.2217</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.5124</v>
+        <v>-5.9859</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.65</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.382</v>
+        <v>-0.3692</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.314</v>
+        <v>-9.968400000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.49</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1024</v>
+        <v>1.114</v>
       </c>
       <c r="J207" t="n">
-        <v>29.7648</v>
+        <v>30.078</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.26</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6481</v>
       </c>
       <c r="J208" t="n">
-        <v>18.3843</v>
+        <v>17.4987</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.19</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.4926</v>
       </c>
       <c r="J209" t="n">
-        <v>14.3019</v>
+        <v>13.3002</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.2707</v>
+        <v>-1.7064</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5563</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.0164</v>
+        <v>-15.0201</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.34</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6419</v>
+        <v>0.5825</v>
       </c>
       <c r="J212" t="n">
-        <v>18.6151</v>
+        <v>16.8925</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.16</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3517</v>
+        <v>0.2987</v>
       </c>
       <c r="J213" t="n">
-        <v>10.1993</v>
+        <v>8.6623</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.03</v>
       </c>
       <c r="I214" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="J214" t="n">
-        <v>2.7202</v>
+        <v>2.0503</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.96</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0623</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.2533</v>
+        <v>-1.8067</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2177</v>
+        <v>-0.1973</v>
       </c>
       <c r="J216" t="n">
-        <v>-6.3133</v>
+        <v>-5.7217</v>
       </c>
     </row>
     <row r="217">
@@ -11069,10 +11069,10 @@
         <v>1.02</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0931</v>
+        <v>0.0732</v>
       </c>
       <c r="J218" t="n">
-        <v>2.6999</v>
+        <v>2.1228</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.01</v>
       </c>
       <c r="I219" t="n">
-        <v>0.0521</v>
+        <v>0.0392</v>
       </c>
       <c r="J219" t="n">
-        <v>1.5109</v>
+        <v>1.1368</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.01</v>
       </c>
       <c r="I220" t="n">
-        <v>0.0521</v>
+        <v>0.0392</v>
       </c>
       <c r="J220" t="n">
-        <v>1.5109</v>
+        <v>1.1368</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.575</v>
+        <v>-0.5355</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.675</v>
+        <v>-15.5295</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.33</v>
       </c>
       <c r="I222" t="n">
-        <v>0.4686</v>
+        <v>0.4017</v>
       </c>
       <c r="J222" t="n">
-        <v>12.1836</v>
+        <v>10.4442</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.19</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3018</v>
+        <v>0.246</v>
       </c>
       <c r="J223" t="n">
-        <v>7.8468</v>
+        <v>6.396</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.07</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1374</v>
+        <v>0.1035</v>
       </c>
       <c r="J224" t="n">
-        <v>3.5724</v>
+        <v>2.691</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.88</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1737</v>
+        <v>-0.1532</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.5162</v>
+        <v>-3.9832</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.78</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2765</v>
+        <v>-0.2577</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.189</v>
+        <v>-6.7002</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.54</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7309</v>
+        <v>0.7804</v>
       </c>
       <c r="J227" t="n">
-        <v>19.0034</v>
+        <v>20.2904</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.04</v>
       </c>
       <c r="I228" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0801</v>
       </c>
       <c r="J228" t="n">
-        <v>2.4128</v>
+        <v>2.0826</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.01</v>
       </c>
       <c r="I229" t="n">
-        <v>0.029</v>
+        <v>0.0228</v>
       </c>
       <c r="J229" t="n">
-        <v>0.754</v>
+        <v>0.5928</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.92</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.129</v>
+        <v>-0.1099</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.354</v>
+        <v>-2.8574</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2481</v>
+        <v>-0.2283</v>
       </c>
       <c r="J231" t="n">
-        <v>-6.4506</v>
+        <v>-5.9358</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.26</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6422</v>
+        <v>0.6099</v>
       </c>
       <c r="J232" t="n">
-        <v>14.7706</v>
+        <v>14.0277</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.71</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.3118</v>
+        <v>-0.2966</v>
       </c>
       <c r="J233" t="n">
-        <v>-7.1714</v>
+        <v>-6.8218</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.65</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3659</v>
+        <v>-0.3525</v>
       </c>
       <c r="J234" t="n">
-        <v>-8.415699999999999</v>
+        <v>-8.1075</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.6</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4106</v>
+        <v>-0.4001</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.4438</v>
+        <v>-9.202299999999999</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.47</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5248</v>
+        <v>-0.5265</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.0704</v>
+        <v>-12.1095</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.5</v>
       </c>
       <c r="I237" t="n">
-        <v>1.0795</v>
+        <v>1.0908</v>
       </c>
       <c r="J237" t="n">
-        <v>24.8285</v>
+        <v>25.0884</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.41</v>
       </c>
       <c r="I238" t="n">
-        <v>0.9409</v>
+        <v>0.9334</v>
       </c>
       <c r="J238" t="n">
-        <v>21.6407</v>
+        <v>21.4682</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.31</v>
       </c>
       <c r="I239" t="n">
-        <v>0.7548</v>
+        <v>0.7347</v>
       </c>
       <c r="J239" t="n">
-        <v>17.3604</v>
+        <v>16.8981</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.31</v>
       </c>
       <c r="I240" t="n">
-        <v>0.7548</v>
+        <v>0.7347</v>
       </c>
       <c r="J240" t="n">
-        <v>17.3604</v>
+        <v>16.8981</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>1.16</v>
       </c>
       <c r="I241" t="n">
-        <v>0.436</v>
+        <v>0.4047</v>
       </c>
       <c r="J241" t="n">
-        <v>10.028</v>
+        <v>9.3081</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.83</v>
       </c>
       <c r="I242" t="n">
-        <v>1.526</v>
+        <v>1.5629</v>
       </c>
       <c r="J242" t="n">
-        <v>39.676</v>
+        <v>40.6354</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.31</v>
       </c>
       <c r="I243" t="n">
-        <v>0.7659</v>
+        <v>0.7412</v>
       </c>
       <c r="J243" t="n">
-        <v>19.9134</v>
+        <v>19.2712</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.18</v>
       </c>
       <c r="I244" t="n">
-        <v>0.4967</v>
+        <v>0.464</v>
       </c>
       <c r="J244" t="n">
-        <v>12.9142</v>
+        <v>12.064</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.98</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.1418</v>
+        <v>-0.115</v>
       </c>
       <c r="J245" t="n">
-        <v>-3.6868</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.9</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.387</v>
+        <v>-0.3469</v>
       </c>
       <c r="J246" t="n">
-        <v>-10.062</v>
+        <v>-9.019399999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0207</v>
+        <v>0.0154</v>
       </c>
       <c r="J247" t="n">
-        <v>0.5382</v>
+        <v>0.4004</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.98</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.032</v>
+        <v>-0.0246</v>
       </c>
       <c r="J248" t="n">
-        <v>-0.832</v>
+        <v>-0.6395999999999999</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.89</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.1488</v>
+        <v>-0.1315</v>
       </c>
       <c r="J249" t="n">
-        <v>-3.8688</v>
+        <v>-3.419</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.77</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2696</v>
+        <v>-0.2507</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.0096</v>
+        <v>-6.5182</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.73</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3076</v>
+        <v>-0.29</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.9976</v>
+        <v>-7.54</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.15</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2692</v>
+        <v>0.2552</v>
       </c>
       <c r="J252" t="n">
-        <v>7.2684</v>
+        <v>6.8904</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.06</v>
       </c>
       <c r="I253" t="n">
-        <v>0.1319</v>
+        <v>0.1158</v>
       </c>
       <c r="J253" t="n">
-        <v>3.5613</v>
+        <v>3.1266</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.99</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.0259</v>
+        <v>-0.0185</v>
       </c>
       <c r="J254" t="n">
-        <v>-0.6993</v>
+        <v>-0.4995</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.059</v>
+        <v>-0.0462</v>
       </c>
       <c r="J255" t="n">
-        <v>-1.593</v>
+        <v>-1.2474</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.89</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1593</v>
+        <v>-0.1392</v>
       </c>
       <c r="J256" t="n">
-        <v>-4.3011</v>
+        <v>-3.7584</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.56</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7048</v>
+        <v>0.6345</v>
       </c>
       <c r="J257" t="n">
-        <v>19.0296</v>
+        <v>17.1315</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.09</v>
       </c>
       <c r="I258" t="n">
-        <v>0.1637</v>
+        <v>0.1267</v>
       </c>
       <c r="J258" t="n">
-        <v>4.4199</v>
+        <v>3.4209</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.05</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1019</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="J259" t="n">
-        <v>2.7513</v>
+        <v>2.0466</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.98</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.0505</v>
+        <v>-0.0385</v>
       </c>
       <c r="J260" t="n">
-        <v>-1.3635</v>
+        <v>-1.0395</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.84</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.2209</v>
+        <v>-0.2007</v>
       </c>
       <c r="J261" t="n">
-        <v>-5.9643</v>
+        <v>-5.4189</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.96</v>
       </c>
       <c r="I262" t="n">
-        <v>1.6037</v>
+        <v>1.6436</v>
       </c>
       <c r="J262" t="n">
-        <v>30.4703</v>
+        <v>31.2284</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.8</v>
       </c>
       <c r="I263" t="n">
-        <v>1.418</v>
+        <v>1.4469</v>
       </c>
       <c r="J263" t="n">
-        <v>26.942</v>
+        <v>27.4911</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.5</v>
       </c>
       <c r="I264" t="n">
-        <v>1.0544</v>
+        <v>1.0726</v>
       </c>
       <c r="J264" t="n">
-        <v>20.0336</v>
+        <v>20.3794</v>
       </c>
     </row>
     <row r="265">
@@ -12989,10 +12989,10 @@
         <v>1.36</v>
       </c>
       <c r="I266" t="n">
-        <v>0.8169</v>
+        <v>0.8087</v>
       </c>
       <c r="J266" t="n">
-        <v>15.5211</v>
+        <v>15.3653</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.1</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5165</v>
+        <v>0.5561</v>
       </c>
       <c r="J267" t="n">
-        <v>9.813499999999999</v>
+        <v>10.5659</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.64</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3406</v>
+        <v>-0.3322</v>
       </c>
       <c r="J268" t="n">
-        <v>-6.4714</v>
+        <v>-6.3118</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.45</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5101</v>
+        <v>-0.5105</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.6919</v>
+        <v>-9.6995</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.22</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.7177</v>
+        <v>-0.7501</v>
       </c>
       <c r="J270" t="n">
-        <v>-13.6363</v>
+        <v>-14.2519</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.16</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.7726</v>
+        <v>-0.8182</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.6794</v>
+        <v>-15.5458</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.69</v>
       </c>
       <c r="I272" t="n">
-        <v>1.3498</v>
+        <v>1.3727</v>
       </c>
       <c r="J272" t="n">
-        <v>32.3952</v>
+        <v>32.9448</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.49</v>
       </c>
       <c r="I273" t="n">
-        <v>1.0839</v>
+        <v>1.0938</v>
       </c>
       <c r="J273" t="n">
-        <v>26.0136</v>
+        <v>26.2512</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.09</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2785</v>
+        <v>0.2472</v>
       </c>
       <c r="J274" t="n">
-        <v>6.684</v>
+        <v>5.9328</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.08</v>
       </c>
       <c r="I275" t="n">
-        <v>0.2513</v>
+        <v>0.2209</v>
       </c>
       <c r="J275" t="n">
-        <v>6.0312</v>
+        <v>5.3016</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6076</v>
+        <v>-0.5736</v>
       </c>
       <c r="J276" t="n">
-        <v>-14.5824</v>
+        <v>-13.7664</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.06</v>
       </c>
       <c r="I277" t="n">
-        <v>0.2095</v>
+        <v>0.1699</v>
       </c>
       <c r="J277" t="n">
-        <v>5.028</v>
+        <v>4.0776</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0315</v>
+        <v>0.0257</v>
       </c>
       <c r="J278" t="n">
-        <v>0.756</v>
+        <v>0.6168</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.85</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1877</v>
+        <v>-0.1702</v>
       </c>
       <c r="J279" t="n">
-        <v>-4.5048</v>
+        <v>-4.0848</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.71</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3218</v>
+        <v>-0.3051</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.7232</v>
+        <v>-7.3224</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.54</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4742</v>
+        <v>-0.4704</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.3808</v>
+        <v>-11.2896</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.11</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2154</v>
+        <v>0.1989</v>
       </c>
       <c r="J282" t="n">
-        <v>6.2466</v>
+        <v>5.7681</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.06</v>
       </c>
       <c r="I283" t="n">
-        <v>0.1353</v>
+        <v>0.1186</v>
       </c>
       <c r="J283" t="n">
-        <v>3.9237</v>
+        <v>3.4394</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.97</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0572</v>
+        <v>-0.0451</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.6588</v>
+        <v>-1.3079</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.89</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.1568</v>
+        <v>-0.137</v>
       </c>
       <c r="J285" t="n">
-        <v>-4.5472</v>
+        <v>-3.973</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.89</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.1568</v>
+        <v>-0.137</v>
       </c>
       <c r="J286" t="n">
-        <v>-4.5472</v>
+        <v>-3.973</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.2</v>
       </c>
       <c r="I287" t="n">
-        <v>0.3123</v>
+        <v>0.2557</v>
       </c>
       <c r="J287" t="n">
-        <v>9.056699999999999</v>
+        <v>7.4153</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.1</v>
       </c>
       <c r="I288" t="n">
-        <v>0.1804</v>
+        <v>0.1398</v>
       </c>
       <c r="J288" t="n">
-        <v>5.2316</v>
+        <v>4.0542</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.09</v>
       </c>
       <c r="I289" t="n">
-        <v>0.1661</v>
+        <v>0.1277</v>
       </c>
       <c r="J289" t="n">
-        <v>4.8169</v>
+        <v>3.7033</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.97</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.063</v>
+        <v>-0.0493</v>
       </c>
       <c r="J290" t="n">
-        <v>-1.827</v>
+        <v>-1.4297</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.96</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.0775</v>
+        <v>-0.0621</v>
       </c>
       <c r="J291" t="n">
-        <v>-2.2475</v>
+        <v>-1.8009</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.51</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1158</v>
+        <v>1.1278</v>
       </c>
       <c r="J292" t="n">
-        <v>26.7792</v>
+        <v>27.0672</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.37</v>
       </c>
       <c r="I293" t="n">
-        <v>0.8898</v>
+        <v>0.8722</v>
       </c>
       <c r="J293" t="n">
-        <v>21.3552</v>
+        <v>20.9328</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.18</v>
       </c>
       <c r="I294" t="n">
-        <v>0.5008</v>
+        <v>0.4667</v>
       </c>
       <c r="J294" t="n">
-        <v>12.0192</v>
+        <v>11.2008</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.05</v>
       </c>
       <c r="I295" t="n">
-        <v>0.1678</v>
+        <v>0.1417</v>
       </c>
       <c r="J295" t="n">
-        <v>4.0272</v>
+        <v>3.4008</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2695</v>
+        <v>-0.2315</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.468</v>
+        <v>-5.556</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.05</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1771</v>
+        <v>0.1397</v>
       </c>
       <c r="J297" t="n">
-        <v>4.2504</v>
+        <v>3.3528</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.03</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1273</v>
+        <v>0.0968</v>
       </c>
       <c r="J298" t="n">
-        <v>3.0552</v>
+        <v>2.3232</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0236</v>
+        <v>0.0181</v>
       </c>
       <c r="J299" t="n">
-        <v>0.5664</v>
+        <v>0.4344</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.73</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3064</v>
+        <v>-0.2888</v>
       </c>
       <c r="J300" t="n">
-        <v>-7.3536</v>
+        <v>-6.9312</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.5117</v>
+        <v>-0.5131</v>
       </c>
       <c r="J301" t="n">
-        <v>-12.2808</v>
+        <v>-12.3144</v>
       </c>
     </row>
   </sheetData>
